--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -27949,6 +27949,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>5750</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>8.27999973297119</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>8.31999969482422</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="G1200" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -27972,6 +27972,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>8.11999988555908</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>8.23999977111816</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -27995,6 +27995,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>8.27999973297119</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>8.15999984741211</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>8.27999973297119</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -28018,6 +28018,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>8.31999969482422</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>8.22000026702881</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>8.31999969482422</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>8.22000026702881</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -27859,22 +27859,22 @@
     </row>
     <row r="1196">
       <c r="A1196" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1196" t="n">
-        <v>14500</v>
+        <v>13000</v>
       </c>
       <c r="C1196" t="n">
-        <v>8.30000019073486</v>
+        <v>8.26000022888184</v>
       </c>
       <c r="D1196" t="n">
-        <v>8.19999980926514</v>
+        <v>8.10000038146973</v>
       </c>
       <c r="E1196" t="n">
-        <v>8.19999980926514</v>
+        <v>8.14000034332275</v>
       </c>
       <c r="F1196" t="n">
-        <v>8.30000019073486</v>
+        <v>8.26000022888184</v>
       </c>
       <c r="G1196" t="s">
         <v>7</v>
@@ -27882,22 +27882,22 @@
     </row>
     <row r="1197">
       <c r="A1197" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1197" t="n">
-        <v>2750</v>
+        <v>14500</v>
       </c>
       <c r="C1197" t="n">
         <v>8.30000019073486</v>
       </c>
       <c r="D1197" t="n">
-        <v>8.26000022888184</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="E1197" t="n">
-        <v>8.27999973297119</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="F1197" t="n">
-        <v>8.26000022888184</v>
+        <v>8.30000019073486</v>
       </c>
       <c r="G1197" t="s">
         <v>7</v>
@@ -27905,22 +27905,22 @@
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1198" t="n">
-        <v>2250</v>
+        <v>2750</v>
       </c>
       <c r="C1198" t="n">
-        <v>8.34000015258789</v>
+        <v>8.30000019073486</v>
       </c>
       <c r="D1198" t="n">
-        <v>8.19999980926514</v>
+        <v>8.26000022888184</v>
       </c>
       <c r="E1198" t="n">
-        <v>8.30000019073486</v>
+        <v>8.27999973297119</v>
       </c>
       <c r="F1198" t="n">
-        <v>8.34000015258789</v>
+        <v>8.26000022888184</v>
       </c>
       <c r="G1198" t="s">
         <v>7</v>
@@ -27928,22 +27928,22 @@
     </row>
     <row r="1199">
       <c r="A1199" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1199" t="n">
-        <v>6750</v>
+        <v>2250</v>
       </c>
       <c r="C1199" t="n">
-        <v>8.46000003814697</v>
+        <v>8.34000015258789</v>
       </c>
       <c r="D1199" t="n">
-        <v>8.30000019073486</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="E1199" t="n">
         <v>8.30000019073486</v>
       </c>
       <c r="F1199" t="n">
-        <v>8.46000003814697</v>
+        <v>8.34000015258789</v>
       </c>
       <c r="G1199" t="s">
         <v>7</v>
@@ -27951,22 +27951,22 @@
     </row>
     <row r="1200">
       <c r="A1200" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1200" t="n">
-        <v>5750</v>
+        <v>6750</v>
       </c>
       <c r="C1200" t="n">
-        <v>8.39999961853027</v>
+        <v>8.46000003814697</v>
       </c>
       <c r="D1200" t="n">
-        <v>8.27999973297119</v>
+        <v>8.30000019073486</v>
       </c>
       <c r="E1200" t="n">
-        <v>8.31999969482422</v>
+        <v>8.30000019073486</v>
       </c>
       <c r="F1200" t="n">
-        <v>8.39999961853027</v>
+        <v>8.46000003814697</v>
       </c>
       <c r="G1200" t="s">
         <v>7</v>
@@ -27974,22 +27974,22 @@
     </row>
     <row r="1201">
       <c r="A1201" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1201" t="n">
-        <v>8500</v>
+        <v>5750</v>
       </c>
       <c r="C1201" t="n">
         <v>8.39999961853027</v>
       </c>
       <c r="D1201" t="n">
-        <v>8.11999988555908</v>
+        <v>8.27999973297119</v>
       </c>
       <c r="E1201" t="n">
+        <v>8.31999969482422</v>
+      </c>
+      <c r="F1201" t="n">
         <v>8.39999961853027</v>
-      </c>
-      <c r="F1201" t="n">
-        <v>8.23999977111816</v>
       </c>
       <c r="G1201" t="s">
         <v>7</v>
@@ -27997,22 +27997,22 @@
     </row>
     <row r="1202">
       <c r="A1202" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1202" t="n">
-        <v>7000</v>
+        <v>8500</v>
       </c>
       <c r="C1202" t="n">
-        <v>8.27999973297119</v>
+        <v>8.39999961853027</v>
       </c>
       <c r="D1202" t="n">
-        <v>8.15999984741211</v>
+        <v>8.11999988555908</v>
       </c>
       <c r="E1202" t="n">
-        <v>8.19999980926514</v>
+        <v>8.39999961853027</v>
       </c>
       <c r="F1202" t="n">
-        <v>8.27999973297119</v>
+        <v>8.23999977111816</v>
       </c>
       <c r="G1202" t="s">
         <v>7</v>
@@ -28020,24 +28020,47 @@
     </row>
     <row r="1203">
       <c r="A1203" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1203" t="n">
-        <v>1250</v>
+        <v>7000</v>
       </c>
       <c r="C1203" t="n">
-        <v>8.31999969482422</v>
+        <v>8.27999973297119</v>
       </c>
       <c r="D1203" t="n">
-        <v>8.22000026702881</v>
+        <v>8.15999984741211</v>
       </c>
       <c r="E1203" t="n">
-        <v>8.31999969482422</v>
+        <v>8.19999980926514</v>
       </c>
       <c r="F1203" t="n">
-        <v>8.22000026702881</v>
+        <v>8.27999973297119</v>
       </c>
       <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>8.19999980926514</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>8.14000034332275</v>
+      </c>
+      <c r="G1204" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516045570374</v>
+        <v>2.62516021728516</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805168151855</v>
+        <v>4.20805215835571</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>5.30099201202393</v>
+        <v>5.30099153518677</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.459068775177</v>
+        <v>4.45906925201416</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558362007141</v>
+        <v>3.90558385848999</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.08488178253174</v>
+        <v>4.0848822593689</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794843673706</v>
+        <v>3.96794891357422</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136517524719</v>
+        <v>3.76136541366577</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574400901794</v>
+        <v>3.97574377059937</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>4.35772752761841</v>
+        <v>4.35772800445557</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2641806602478</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977132797241</v>
+        <v>4.27977180480957</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2641806602478</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.2641806602478</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.17063331604004</v>
+        <v>4.17063283920288</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>4.15504169464111</v>
+        <v>4.15504217147827</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961093902588</v>
+        <v>4.20961141586304</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283798217773</v>
+        <v>4.16283845901489</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>4.0536994934082</v>
+        <v>4.05369997024536</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999199867249</v>
+        <v>3.8899929523468</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8705039024353</v>
+        <v>3.87050414085388</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101509094238</v>
+        <v>3.85101437568665</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711718559265</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034375190735</v>
+        <v>3.80034351348877</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015286445618</v>
+        <v>3.96015238761902</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8705039024353</v>
+        <v>3.87050414085388</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.7262852191925</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187684059143</v>
+        <v>3.74187707901001</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088496208191</v>
+        <v>3.55088448524475</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922174453735</v>
+        <v>3.30922198295593</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704805374146</v>
+        <v>3.08704829216003</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.35209822654724</v>
+        <v>3.35209774971008</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685764312744</v>
+        <v>3.24685740470886</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.34430241584778</v>
+        <v>3.3443021774292</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.41056442260742</v>
+        <v>3.410564661026</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.41056442260742</v>
+        <v>3.410564661026</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123623847961</v>
+        <v>3.46123576164246</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529381752014</v>
+        <v>3.53529357910156</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698705673218</v>
+        <v>3.54698753356934</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133515357971</v>
+        <v>3.99133467674255</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.99913024902344</v>
+        <v>3.99913120269775</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456124305725</v>
+        <v>3.94456148147583</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337966918945</v>
+        <v>3.91337919235229</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762765884399</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321856498718</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711718559265</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999199867249</v>
+        <v>3.8899929523468</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711718559265</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321856498718</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.788649559021</v>
+        <v>3.78865027427673</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762765884399</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644536972046</v>
+        <v>3.79644513130188</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459735870361</v>
+        <v>3.82459712028503</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448937416077</v>
+        <v>3.80448889732361</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111730575562</v>
+        <v>3.92111706733704</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.90503025054932</v>
+        <v>3.9050304889679</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535468101501</v>
+        <v>3.96535539627075</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469783782959</v>
+        <v>4.21469831466675</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209178924561</v>
+        <v>4.10209131240845</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383205413818</v>
+        <v>4.05383157730103</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.8004674911499</v>
+        <v>3.80046701431274</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949229240417</v>
+        <v>3.61949276924133</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123303413391</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970921516418</v>
+        <v>3.65970945358276</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775250434875</v>
+        <v>3.66775274276733</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688624382019</v>
+        <v>3.50688600540161</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895141601562</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123303413391</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297306060791</v>
+        <v>3.52297282218933</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123303413391</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.52699446678162</v>
+        <v>3.52699494361877</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>3.5792760848999</v>
+        <v>3.57927584648132</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895141601562</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>3.48275637626648</v>
+        <v>3.4827561378479</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069096565247</v>
+        <v>3.47069144248962</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40232348442078</v>
+        <v>3.40232300758362</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036629676819</v>
+        <v>3.41036653518677</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069096565247</v>
+        <v>3.47069144248962</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884271621704</v>
+        <v>3.49884295463562</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862674713135</v>
+        <v>3.45862627029419</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797645568848</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.31384634971619</v>
+        <v>3.31384682655334</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>3.1047203540802</v>
+        <v>3.10472059249878</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080717086792</v>
+        <v>3.12080693244934</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222229003906</v>
+        <v>3.01222205162048</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>3.04841685295105</v>
+        <v>3.04841709136963</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624369621277</v>
+        <v>3.01624393463135</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>2.87146425247192</v>
+        <v>2.87146401405334</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G208" t="n">
-        <v>2.7266845703125</v>
+        <v>2.72668433189392</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G209" t="n">
-        <v>2.7266845703125</v>
+        <v>2.72668433189392</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059799194336</v>
+        <v>2.71059775352478</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G211" t="n">
-        <v>2.7266845703125</v>
+        <v>2.72668433189392</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896595001221</v>
+        <v>2.77896571159363</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>2.84733414649963</v>
+        <v>2.84733438491821</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929109573364</v>
+        <v>2.83929085731506</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.84733414649963</v>
+        <v>2.84733438491821</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581056594849</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.89961576461792</v>
+        <v>2.89961552619934</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G238" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157247543335</v>
+        <v>2.89157271385193</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.89961576461792</v>
+        <v>2.89961552619934</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581056594849</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417900085449</v>
+        <v>3.00417876243591</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581056594849</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797645568848</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047475814819</v>
+        <v>3.43047451972961</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52699446678162</v>
+        <v>3.52699494361877</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612820625305</v>
+        <v>3.36612796783447</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.32591199874878</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.32591199874878</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797645568848</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547112464905</v>
+        <v>3.61547088623047</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.4505832195282</v>
+        <v>3.45058298110962</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862674713135</v>
+        <v>3.45862627029419</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G319" t="n">
-        <v>3.22537016868591</v>
+        <v>3.22537040710449</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797645568848</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373836517334</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373836517334</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189035415649</v>
+        <v>3.32189011573792</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>3.31384634971619</v>
+        <v>3.31384682655334</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.24950003623962</v>
+        <v>3.2495002746582</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.24950003623962</v>
+        <v>3.2495002746582</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>3.22537016868591</v>
+        <v>3.22537040710449</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.39327478408813</v>
+        <v>3.39327454566956</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192384719849</v>
+        <v>3.45192360877991</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246496200562</v>
+        <v>3.55246520042419</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679113388062</v>
+        <v>3.73679137229919</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G386" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G387" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597898483276</v>
+        <v>3.58597874641418</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.62787127494812</v>
+        <v>3.62787103652954</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.62787127494812</v>
+        <v>3.62787103652954</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>3.59435725212097</v>
+        <v>3.59435749053955</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408669471741</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.51057267189026</v>
+        <v>3.51057291030884</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354557991028</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354557991028</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>3.36813902854919</v>
+        <v>3.36813926696777</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G438" t="n">
-        <v>3.04975771903992</v>
+        <v>3.0497579574585</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G456" t="n">
-        <v>3.00786519050598</v>
+        <v>3.00786542892456</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G553" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.16705632209778</v>
+        <v>3.1670560836792</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -31728,6 +31728,32 @@
         <v>8.23999977111816</v>
       </c>
       <c r="H1206" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>7250</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>8.38000011444092</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>8.27999973297119</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>8.35999965667725</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>8.30000019073486</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>8.30000019073486</v>
+      </c>
+      <c r="H1207" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516021728516</v>
+        <v>2.62516045570374</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621223449707</v>
+        <v>3.25621247291565</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>5.30099153518677</v>
+        <v>5.30099201202393</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906925201416</v>
+        <v>4.459068775177</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558385848999</v>
+        <v>3.90558362007141</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794891357422</v>
+        <v>3.96794843673706</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136541366577</v>
+        <v>3.76136517524719</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574377059937</v>
+        <v>3.97574353218079</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>4.35772800445557</v>
+        <v>4.35772752761841</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977180480957</v>
+        <v>4.27977132797241</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.17063283920288</v>
+        <v>4.17063331604004</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267711639404</v>
+        <v>4.0926775932312</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858903884888</v>
+        <v>4.24858856201172</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283845901489</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047340393066</v>
+        <v>4.10047292709351</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>4.05369997024536</v>
+        <v>4.0536994934082</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.8899929523468</v>
+        <v>3.88999199867249</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050414085388</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778852462769</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101437568665</v>
+        <v>3.85101509094238</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034351348877</v>
+        <v>3.80034327507019</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050414085388</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628569602966</v>
+        <v>3.72628593444824</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.35209774971008</v>
+        <v>3.35209798812866</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685740470886</v>
+        <v>3.24685764312744</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733785629272</v>
+        <v>3.4573380947113</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021362304688</v>
+        <v>3.5002133846283</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123576164246</v>
+        <v>3.46123600006104</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529357910156</v>
+        <v>3.53529381752014</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698753356934</v>
+        <v>3.54698729515076</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456148147583</v>
+        <v>3.94456124305725</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337919235229</v>
+        <v>3.91337966918945</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778852462769</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762765884399</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.8899929523468</v>
+        <v>3.88999199867249</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778852462769</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593489646912</v>
+        <v>3.81593441963196</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762765884399</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593489646912</v>
+        <v>3.81593441963196</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644513130188</v>
+        <v>3.79644560813904</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709542274475</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459712028503</v>
+        <v>3.82459735870361</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111706733704</v>
+        <v>3.92111682891846</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720388412476</v>
+        <v>3.9372034072876</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720388412476</v>
+        <v>3.9372034072876</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709542274475</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.9050304889679</v>
+        <v>3.90503025054932</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666205406189</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666205406189</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709542274475</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535539627075</v>
+        <v>3.96535491943359</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>4.08600521087646</v>
+        <v>4.08600473403931</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274112701416</v>
+        <v>4.22274160385132</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G115" t="n">
-        <v>4.23078489303589</v>
+        <v>4.23078441619873</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.8768789768219</v>
+        <v>3.87687873840332</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.80046701431274</v>
+        <v>3.8004674911499</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992589950562</v>
+        <v>3.69992566108704</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775274276733</v>
+        <v>3.66775226593018</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297282218933</v>
+        <v>3.52297306060791</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025831222534</v>
+        <v>3.39025807380676</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.52699494361877</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112433433533</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112433433533</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677802085876</v>
+        <v>3.48677778244019</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>3.4827561378479</v>
+        <v>3.48275637626648</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40232300758362</v>
+        <v>3.4023232460022</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036653518677</v>
+        <v>3.41036605834961</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884295463562</v>
+        <v>3.49884247779846</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862627029419</v>
+        <v>3.45862650871277</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>3.34601974487305</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>3.33797645568848</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.31384682655334</v>
+        <v>3.31384658813477</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.23341345787048</v>
+        <v>3.2334132194519</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>3.10472059249878</v>
+        <v>3.1047203540802</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080693244934</v>
+        <v>3.12080717086792</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222205162048</v>
+        <v>3.01222229003906</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>2.96396231651306</v>
+        <v>2.96396207809448</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>2.87146401405334</v>
+        <v>2.87146425247192</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G208" t="n">
-        <v>2.72668433189392</v>
+        <v>2.7266845703125</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G209" t="n">
-        <v>2.72668433189392</v>
+        <v>2.7266845703125</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059775352478</v>
+        <v>2.71059799194336</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G211" t="n">
-        <v>2.72668433189392</v>
+        <v>2.7266845703125</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896571159363</v>
+        <v>2.77896595001221</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331250190735</v>
+        <v>2.84331274032593</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994067192078</v>
+        <v>2.95994091033936</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581056594849</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.89961552619934</v>
+        <v>2.89961576461792</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G238" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157271385193</v>
+        <v>2.89157247543335</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950730323792</v>
+        <v>2.87950754165649</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.89961552619934</v>
+        <v>2.89961576461792</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581056594849</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417876243591</v>
+        <v>3.00417900085449</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581056594849</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>3.33797645568848</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52699494361877</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656109809875</v>
+        <v>3.44656133651733</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>3.38623642921448</v>
+        <v>3.38623666763306</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G299" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.32591152191162</v>
+        <v>3.3259117603302</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.32591152191162</v>
+        <v>3.3259117603302</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>3.33797645568848</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>3.34601974487305</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862627029419</v>
+        <v>3.45862650871277</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G319" t="n">
-        <v>3.22537040710449</v>
+        <v>3.22537016868591</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.33797645568848</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189011573792</v>
+        <v>3.32188987731934</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>3.31384682655334</v>
+        <v>3.31384658813477</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145698547363</v>
+        <v>3.24145674705505</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.2495002746582</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.2495002746582</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>3.22537040710449</v>
+        <v>3.22537016868591</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G356" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246520042419</v>
+        <v>3.55246472358704</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G389" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597874641418</v>
+        <v>3.58597922325134</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>3.46030235290527</v>
+        <v>3.46030211448669</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>3.49381589889526</v>
+        <v>3.49381613731384</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.62787103652954</v>
+        <v>3.62787127494812</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G402" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.62787103652954</v>
+        <v>3.62787127494812</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>3.59435749053955</v>
+        <v>3.59435725212097</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G415" t="n">
-        <v>3.37651777267456</v>
+        <v>3.37651753425598</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>3.36813926696777</v>
+        <v>3.36813902854919</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G420" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G424" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.75</v>
       </c>
       <c r="G430" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.75</v>
       </c>
       <c r="G432" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>3.10002851486206</v>
+        <v>3.10002875328064</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0497579574585</v>
+        <v>3.04975771903992</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>3.10002851486206</v>
+        <v>3.10002875328064</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G452" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G500" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G583" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.75</v>
       </c>
       <c r="G584" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G587" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543482780457</v>
+        <v>3.17543458938599</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705888748169</v>
+        <v>3.47705912590027</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G625" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G652" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>3.24117803573608</v>
+        <v>3.24117827415466</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>3.34601402282715</v>
+        <v>3.34601378440857</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G711" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G714" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G717" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G722" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G728" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G789" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G794" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85272097587585</v>
+        <v>3.85272121429443</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G804" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.7915666103363</v>
+        <v>3.79156684875488</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G812" t="n">
-        <v>3.8352484703064</v>
+        <v>3.83524823188782</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.66052174568176</v>
+        <v>3.66052198410034</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>3.69546699523926</v>
+        <v>3.69546723365784</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.25</v>
       </c>
       <c r="G828" t="n">
-        <v>3.71293973922729</v>
+        <v>3.71293997764587</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>3.70420336723328</v>
+        <v>3.7042031288147</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>4.32448291778564</v>
+        <v>4.32448244094849</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G849" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G853" t="n">
-        <v>4.52541828155518</v>
+        <v>4.52541780471802</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>4.6302547454834</v>
+        <v>4.63025426864624</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -31754,6 +31754,32 @@
         <v>8.30000019073486</v>
       </c>
       <c r="H1207" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>8.35999965667725</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>8.30000019073486</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="H1208" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516045570374</v>
+        <v>2.62516021728516</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805215835571</v>
+        <v>4.20805263519287</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.459068775177</v>
+        <v>4.45906925201416</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558362007141</v>
+        <v>3.90558409690857</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0848822593689</v>
+        <v>4.08488178253174</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794843673706</v>
+        <v>3.96794867515564</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136517524719</v>
+        <v>3.76136541366577</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574353218079</v>
+        <v>3.97574400901794</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977132797241</v>
+        <v>4.27977085113525</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0926775932312</v>
+        <v>4.09267807006836</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756666183472</v>
+        <v>4.28756713867188</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858856201172</v>
+        <v>4.24858903884888</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>4.15504217147827</v>
+        <v>4.15504169464111</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283750534058</v>
+        <v>4.16283798217773</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047292709351</v>
+        <v>4.10047340393066</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>4.03031301498413</v>
+        <v>4.03031253814697</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999199867249</v>
+        <v>3.88999247550964</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219738006592</v>
+        <v>3.88219690322876</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778852462769</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101509094238</v>
+        <v>3.8510148525238</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711647033691</v>
+        <v>3.84711694717407</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034327507019</v>
+        <v>3.80034351348877</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015238761902</v>
+        <v>3.9601526260376</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628593444824</v>
+        <v>3.72628545761108</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088448524475</v>
+        <v>3.55088472366333</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922198295593</v>
+        <v>3.30922150611877</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704829216003</v>
+        <v>3.08704853057861</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516416549683</v>
+        <v>3.23516440391541</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685764312744</v>
+        <v>3.24685740470886</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.5002133846283</v>
+        <v>3.50021362304688</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3443021774292</v>
+        <v>3.34430241584778</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.410564661026</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.410564661026</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.3832802772522</v>
+        <v>3.38328003883362</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529381752014</v>
+        <v>3.53529334068298</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698729515076</v>
+        <v>3.54698705673218</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542394638062</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117524147034</v>
+        <v>3.92117500305176</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133467674255</v>
+        <v>3.99133491516113</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.99913120269775</v>
+        <v>3.9991307258606</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337966918945</v>
+        <v>3.91337919235229</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778852462769</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491275787354</v>
+        <v>3.85491251945496</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762765884399</v>
+        <v>3.82762742042542</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219738006592</v>
+        <v>3.88219690322876</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542394638062</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219738006592</v>
+        <v>3.88219690322876</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711647033691</v>
+        <v>3.84711694717407</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999199867249</v>
+        <v>3.88999247550964</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778852462769</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711647033691</v>
+        <v>3.84711694717407</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.7379789352417</v>
+        <v>3.73797869682312</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78865027427673</v>
+        <v>3.78865003585815</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762765884399</v>
+        <v>3.82762742042542</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542394638062</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644560813904</v>
+        <v>3.79644536972046</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -31780,6 +31780,32 @@
         <v>8.18000030517578</v>
       </c>
       <c r="H1208" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>8.07999992370605</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="H1209" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -473,7 +473,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621247291565</v>
+        <v>3.25621199607849</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805263519287</v>
+        <v>4.20805215835571</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>5.30099201202393</v>
+        <v>5.30099153518677</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558409690857</v>
+        <v>3.90558362007141</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794867515564</v>
+        <v>3.9679479598999</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574400901794</v>
+        <v>3.97574424743652</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977085113525</v>
+        <v>4.27977132797241</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G22" t="n">
-        <v>4.17063331604004</v>
+        <v>4.17063283920288</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267807006836</v>
+        <v>4.0926775932312</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756713867188</v>
+        <v>4.28756666183472</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>4.15504169464111</v>
+        <v>4.15504217147827</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961141586304</v>
+        <v>4.20961093902588</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283798217773</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>4.03031253814697</v>
+        <v>4.03031301498413</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999247550964</v>
+        <v>3.88999223709106</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778828620911</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.8510148525238</v>
+        <v>3.85101461410522</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034351348877</v>
+        <v>3.80034327507019</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.9601526260376</v>
+        <v>3.96015238761902</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628545761108</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187707901001</v>
+        <v>3.74187660217285</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922150611877</v>
+        <v>3.30922198295593</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704853057861</v>
+        <v>3.08704829216003</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685740470886</v>
+        <v>3.24685764312744</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021362304688</v>
+        <v>3.50021314620972</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.34430241584778</v>
+        <v>3.3443021774292</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.38328003883362</v>
+        <v>3.3832802772522</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123600006104</v>
+        <v>3.46123576164246</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529334068298</v>
+        <v>3.53529381752014</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698705673218</v>
+        <v>3.54698753356934</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542323112488</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117500305176</v>
+        <v>3.9211757183075</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133491516113</v>
+        <v>3.99133467674255</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.9991307258606</v>
+        <v>3.99913048744202</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456124305725</v>
+        <v>3.94456171989441</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337919235229</v>
+        <v>3.91337943077087</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778828620911</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491251945496</v>
+        <v>3.8549120426178</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762742042542</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542323112488</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999247550964</v>
+        <v>3.88999223709106</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778828620911</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78865003585815</v>
+        <v>3.78865027427673</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762742042542</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542323112488</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644536972046</v>
+        <v>3.79644560813904</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709542274475</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88894414901733</v>
+        <v>3.88894391059875</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448889732361</v>
+        <v>3.80448913574219</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111682891846</v>
+        <v>3.92111706733704</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709542274475</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666205406189</v>
+        <v>3.83666229248047</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666205406189</v>
+        <v>3.83666229248047</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709542274475</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535491943359</v>
+        <v>3.96535563468933</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>4.09404850006104</v>
+        <v>4.09404802322388</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274160385132</v>
+        <v>4.22274112701416</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G115" t="n">
-        <v>4.23078441619873</v>
+        <v>4.23078489303589</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209131240845</v>
+        <v>4.10209178924561</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383157730103</v>
+        <v>4.05383205413818</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133399009705</v>
+        <v>3.96133375167847</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.8004674911499</v>
+        <v>3.80046701431274</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601223945618</v>
+        <v>3.7160120010376</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949300765991</v>
+        <v>3.61949253082275</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340595245361</v>
+        <v>3.60340619087219</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73209881782532</v>
+        <v>3.7320990562439</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992566108704</v>
+        <v>3.69992589950562</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970945358276</v>
+        <v>3.65970969200134</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.55916786193848</v>
+        <v>3.5591676235199</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482131004333</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025807380676</v>
+        <v>3.39025831222534</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G145" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G146" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482131004333</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.55916786193848</v>
+        <v>3.5591676235199</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112433433533</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112433433533</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069144248962</v>
+        <v>3.47069120407104</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069144248962</v>
+        <v>3.47069120407104</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884247779846</v>
+        <v>3.49884295463562</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>3.49079966545105</v>
+        <v>3.49079990386963</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.2334132194519</v>
+        <v>3.23341345787048</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080717086792</v>
+        <v>3.12080693244934</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G201" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>2.96396207809448</v>
+        <v>2.96396231651306</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059799194336</v>
+        <v>2.71059775352478</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331274032593</v>
+        <v>2.84331250190735</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G237" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G238" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950754165649</v>
+        <v>2.87950730323792</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417900085449</v>
+        <v>3.00417876243591</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047451972961</v>
+        <v>3.43047475814819</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656133651733</v>
+        <v>3.44656109809875</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612796783447</v>
+        <v>3.36612820625305</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>3.37015008926392</v>
+        <v>3.37014985084534</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G299" t="n">
-        <v>3.37015008926392</v>
+        <v>3.37014985084534</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>3.37015008926392</v>
+        <v>3.37014985084534</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.35004162788391</v>
+        <v>3.35004138946533</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G317" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.30580353736877</v>
+        <v>3.3058032989502</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -31806,6 +31806,32 @@
         <v>8.02000045776367</v>
       </c>
       <c r="H1209" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="H1210" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516045570374</v>
+        <v>2.62516069412231</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621247291565</v>
+        <v>3.25621223449707</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805168151855</v>
+        <v>4.20805215835571</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906972885132</v>
+        <v>4.45906925201416</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929111480713</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794843673706</v>
+        <v>3.9679479598999</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136541366577</v>
+        <v>3.76136517524719</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574353218079</v>
+        <v>3.97574377059937</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>4.35772752761841</v>
+        <v>4.35772800445557</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977132797241</v>
+        <v>4.27977180480957</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0926775932312</v>
+        <v>4.09267711639404</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756713867188</v>
+        <v>4.28756666183472</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>4.15504264831543</v>
+        <v>4.15504217147827</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961141586304</v>
+        <v>4.20961093902588</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929111480713</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047340393066</v>
+        <v>4.10047292709351</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929111480713</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050366401672</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101437568665</v>
+        <v>3.85101509094238</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034303665161</v>
+        <v>3.80034351348877</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015286445618</v>
+        <v>3.96015334129333</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050366401672</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628593444824</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187684059143</v>
+        <v>3.74187707901001</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088448524475</v>
+        <v>3.55088520050049</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704805374146</v>
+        <v>3.08704829216003</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516416549683</v>
+        <v>3.23516440391541</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.35209822654724</v>
+        <v>3.35209774971008</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733833312988</v>
+        <v>3.4573380947113</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.38328003883362</v>
+        <v>3.38328051567078</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529381752014</v>
+        <v>3.53529357910156</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117500305176</v>
+        <v>3.92117476463318</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133491516113</v>
+        <v>3.99133467674255</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337919235229</v>
+        <v>3.91337943077087</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491299629211</v>
+        <v>3.85491251945496</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983208656311</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593465805054</v>
+        <v>3.81593441963196</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.7379789352417</v>
+        <v>3.73797869682312</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78865051269531</v>
+        <v>3.78865027427673</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593465805054</v>
+        <v>3.81593441963196</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983208656311</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983208656311</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644560813904</v>
+        <v>3.79644536972046</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88894414901733</v>
+        <v>3.88894391059875</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448889732361</v>
+        <v>3.80448913574219</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111730575562</v>
+        <v>3.92111706733704</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720388412476</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720388412476</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666205406189</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666205406189</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535515785217</v>
+        <v>3.96535539627075</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383157730103</v>
+        <v>4.05383205413818</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133351325989</v>
+        <v>3.96133327484131</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687945365906</v>
+        <v>3.87687921524048</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.80046701431274</v>
+        <v>3.80046725273132</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601247787476</v>
+        <v>3.71601223945618</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>3.63960099220276</v>
+        <v>3.63960075378418</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949253082275</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73209881782532</v>
+        <v>3.7320990562439</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970969200134</v>
+        <v>3.65970897674561</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775250434875</v>
+        <v>3.66775226593018</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.55916786193848</v>
+        <v>3.55916810035706</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688624382019</v>
+        <v>3.50688648223877</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297282218933</v>
+        <v>3.52297306060791</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025831222534</v>
+        <v>3.39025807380676</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.55916786193848</v>
+        <v>3.55916810035706</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677802085876</v>
+        <v>3.48677825927734</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>3.48275637626648</v>
+        <v>3.4827561378479</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253945350647</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253945350647</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.2334132194519</v>
+        <v>3.23341369628906</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080693244934</v>
+        <v>3.12080717086792</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222205162048</v>
+        <v>3.01222229003906</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059775352478</v>
+        <v>2.7105975151062</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.73472809791565</v>
+        <v>2.73472762107849</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896571159363</v>
+        <v>2.77896595001221</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>2.84733438491821</v>
+        <v>2.84733414649963</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.84733438491821</v>
+        <v>2.84733414649963</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994067192078</v>
+        <v>2.95994091033936</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G231" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157247543335</v>
+        <v>2.89157271385193</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G249" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G250" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374587059021</v>
+        <v>2.92374563217163</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G275" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.93178915977478</v>
+        <v>2.93178868293762</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917536735535</v>
+        <v>3.18917512893677</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047451972961</v>
+        <v>3.43047475814819</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656085968018</v>
+        <v>3.44656109809875</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612796783447</v>
+        <v>3.36612820625305</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.3259117603302</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.3259117603302</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253945350647</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G316" t="n">
-        <v>3.20526170730591</v>
+        <v>3.20526194572449</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373836517334</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373836517334</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189035415649</v>
+        <v>3.32189011573792</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.2977602481842</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.2977602481842</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.30580353736877</v>
+        <v>3.3058032989502</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.24950003623962</v>
+        <v>3.24949979782104</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.24950003623962</v>
+        <v>3.24949979782104</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.25084066390991</v>
+        <v>3.25084090232849</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.39327478408813</v>
+        <v>3.39327454566956</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>3.38489603996277</v>
+        <v>3.38489580154419</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192384719849</v>
+        <v>3.45192360877991</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>3.4854371547699</v>
+        <v>3.48543739318848</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246496200562</v>
+        <v>3.55246520042419</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679113388062</v>
+        <v>3.73679137229919</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G386" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G387" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597898483276</v>
+        <v>3.58597874641418</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>3.49381589889526</v>
+        <v>3.49381566047668</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.62787127494812</v>
+        <v>3.62787103652954</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.62787127494812</v>
+        <v>3.62787103652954</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>3.4854371547699</v>
+        <v>3.48543739318848</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408669471741</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.51057267189026</v>
+        <v>3.51057291030884</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354557991028</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354557991028</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>3.36813902854919</v>
+        <v>3.36813926696777</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G438" t="n">
-        <v>3.04975771903992</v>
+        <v>3.0497579574585</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G456" t="n">
-        <v>3.00786519050598</v>
+        <v>3.00786542892456</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G457" t="n">
-        <v>3.01624369621277</v>
+        <v>3.01624393463135</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>2.88218879699707</v>
+        <v>2.88218855857849</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>2.88218879699707</v>
+        <v>2.88218855857849</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G487" t="n">
-        <v>2.80678248405457</v>
+        <v>2.80678272247314</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G493" t="n">
-        <v>2.80678248405457</v>
+        <v>2.80678272247314</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G498" t="n">
-        <v>2.7816469669342</v>
+        <v>2.78164720535278</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G506" t="n">
-        <v>2.88218879699707</v>
+        <v>2.88218855857849</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>2.8654317855835</v>
+        <v>2.86543202400208</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>2.8654317855835</v>
+        <v>2.86543202400208</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.88218879699707</v>
+        <v>2.88218855857849</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G548" t="n">
-        <v>2.88218879699707</v>
+        <v>2.88218855857849</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G553" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.8654317855835</v>
+        <v>2.86543202400208</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G565" t="n">
-        <v>2.88218879699707</v>
+        <v>2.88218855857849</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.16705632209778</v>
+        <v>3.1670560836792</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543482780457</v>
+        <v>3.17543458938599</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705888748169</v>
+        <v>3.47705912590027</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -31884,6 +31884,32 @@
         <v>8</v>
       </c>
       <c r="H1212" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>8.02000045776367</v>
+      </c>
+      <c r="H1213" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -28333,8 +28333,31 @@
       <c r="E1216" t="n">
         <v>8.19999980926514</v>
       </c>
-      <c r="F1216"/>
+      <c r="F1216" t="n">
+        <v>8.18000030517578</v>
+      </c>
       <c r="G1216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>12250</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>8.11999988555908</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>8.0600004196167</v>
+      </c>
+      <c r="F1217"/>
+      <c r="G1217" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -28356,8 +28356,31 @@
       <c r="E1217" t="n">
         <v>8.0600004196167</v>
       </c>
-      <c r="F1217"/>
+      <c r="F1217" t="n">
+        <v>8</v>
+      </c>
       <c r="G1217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="F1218"/>
+      <c r="G1218" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -28371,7 +28371,7 @@
         <v>750</v>
       </c>
       <c r="C1218" t="n">
-        <v>7.90000009536743</v>
+        <v>7.98000001907349</v>
       </c>
       <c r="D1218" t="n">
         <v>7.88000011444092</v>
@@ -28379,8 +28379,31 @@
       <c r="E1218" t="n">
         <v>7.90000009536743</v>
       </c>
-      <c r="F1218"/>
+      <c r="F1218" t="n">
+        <v>7.98000001907349</v>
+      </c>
       <c r="G1218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>7.98000001907349</v>
+      </c>
+      <c r="F1219"/>
+      <c r="G1219" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -28402,8 +28402,31 @@
       <c r="E1219" t="n">
         <v>7.98000001907349</v>
       </c>
-      <c r="F1219"/>
+      <c r="F1219" t="n">
+        <v>7.96000003814697</v>
+      </c>
       <c r="G1219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>7.94000005722046</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="F1220"/>
+      <c r="G1220" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -28432,6 +28432,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>23750</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516021728516</v>
+        <v>2.62516045570374</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66764616966248</v>
+        <v>2.6676459312439</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805215835571</v>
+        <v>4.20805168151855</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574329376221</v>
+        <v>3.97574377059937</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977180480957</v>
+        <v>4.27977132797241</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0926775932312</v>
+        <v>4.09267807006836</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756666183472</v>
+        <v>4.28756713867188</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858951568604</v>
+        <v>4.24858903884888</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961093902588</v>
+        <v>4.20961141586304</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283845901489</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>4.03031349182129</v>
+        <v>4.03031301498413</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676662445068</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676662445068</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628617286682</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088496208191</v>
+        <v>3.55088448524475</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922198295593</v>
+        <v>3.30922174453735</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704829216003</v>
+        <v>3.08704805374146</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685740470886</v>
+        <v>3.24685764312744</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4573380947113</v>
+        <v>3.45733785629272</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021386146545</v>
+        <v>3.50021362304688</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.34430193901062</v>
+        <v>3.3443021774292</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.410564661026</v>
+        <v>3.41056489944458</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.410564661026</v>
+        <v>3.41056489944458</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698753356934</v>
+        <v>3.54698777198792</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133443832397</v>
+        <v>3.99133515357971</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676662445068</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762742042542</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78865027427673</v>
+        <v>3.78864979743958</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762742042542</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644513130188</v>
+        <v>3.79644560813904</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535539627075</v>
+        <v>3.96535515785217</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.14230871200562</v>
+        <v>4.14230823516846</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469831466675</v>
+        <v>4.21469783782959</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274112701416</v>
+        <v>4.22274160385132</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.14230871200562</v>
+        <v>4.14230823516846</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G121" t="n">
-        <v>3.85677027702332</v>
+        <v>3.85677051544189</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.85677027702332</v>
+        <v>3.85677051544189</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.8768789768219</v>
+        <v>3.87687945365906</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82057547569275</v>
+        <v>3.82057571411133</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601223945618</v>
+        <v>3.71601271629333</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340595245361</v>
+        <v>3.60340619087219</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970897674561</v>
+        <v>3.65970969200134</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775226593018</v>
+        <v>3.66775250434875</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.55916833877563</v>
+        <v>3.55916786193848</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688624382019</v>
+        <v>3.50688600540161</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895141601562</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731961250305</v>
+        <v>3.58731913566589</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731961250305</v>
+        <v>3.58731913566589</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297306060791</v>
+        <v>3.52297282218933</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025807380676</v>
+        <v>3.39025855064392</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.55916833877563</v>
+        <v>3.55916786193848</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>3.57927584648132</v>
+        <v>3.5792760848999</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895141601562</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112481117249</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112481117249</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677825927734</v>
+        <v>3.48677802085876</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.4023232460022</v>
+        <v>3.40232300758362</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884295463562</v>
+        <v>3.4988431930542</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>3.49079990386963</v>
+        <v>3.49079966545105</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>3.34601998329163</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08863353729248</v>
+        <v>3.08863377571106</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080717086792</v>
+        <v>3.12080693244934</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222229003906</v>
+        <v>3.0122218132019</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211382865906</v>
+        <v>2.99211406707764</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.74679279327393</v>
+        <v>2.7467930316925</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>2.84733414649963</v>
+        <v>2.84733438491821</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.84733414649963</v>
+        <v>2.84733438491821</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581056594849</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G231" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.91168069839478</v>
+        <v>2.9116804599762</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G238" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157271385193</v>
+        <v>2.89157247543335</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G249" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G250" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559435844421</v>
+        <v>2.89559412002563</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581056594849</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374587059021</v>
+        <v>2.92374563217163</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559435844421</v>
+        <v>2.89559412002563</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.91168069839478</v>
+        <v>2.9116804599762</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G275" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581056594849</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047475814819</v>
+        <v>3.43047451972961</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612820625305</v>
+        <v>3.36612796783447</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.37417197227478</v>
+        <v>3.3741717338562</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.35004186630249</v>
+        <v>3.35004162788391</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.37417197227478</v>
+        <v>3.3741717338562</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>3.34601998329163</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547088623047</v>
+        <v>3.61547064781189</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.45058274269104</v>
+        <v>3.45058298110962</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G319" t="n">
-        <v>3.22537040710449</v>
+        <v>3.22537016868591</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.3058032989502</v>
+        <v>3.30580353736877</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.24950003623962</v>
+        <v>3.2495002746582</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.24950003623962</v>
+        <v>3.2495002746582</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>3.22537040710449</v>
+        <v>3.22537016868591</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.25084090232849</v>
+        <v>3.25084066390991</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>3.38489580154419</v>
+        <v>3.38489603996277</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>3.48543739318848</v>
+        <v>3.4854371547699</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273599624634</v>
+        <v>3.60273575782776</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>3.49381566047668</v>
+        <v>3.49381589889526</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>3.59435725212097</v>
+        <v>3.59435749053955</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273599624634</v>
+        <v>3.60273575782776</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>3.48543739318848</v>
+        <v>3.4854371547699</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354510307312</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354510307312</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435468673706</v>
+        <v>3.28435444831848</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435468673706</v>
+        <v>3.28435444831848</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G457" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G472" t="n">
-        <v>2.88218855857849</v>
+        <v>2.88218879699707</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G474" t="n">
-        <v>2.88218855857849</v>
+        <v>2.88218879699707</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G487" t="n">
-        <v>2.80678272247314</v>
+        <v>2.80678248405457</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G493" t="n">
-        <v>2.80678272247314</v>
+        <v>2.80678248405457</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G498" t="n">
-        <v>2.78164720535278</v>
+        <v>2.7816469669342</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G506" t="n">
-        <v>2.88218855857849</v>
+        <v>2.88218879699707</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>2.86543202400208</v>
+        <v>2.8654317855835</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>2.86543202400208</v>
+        <v>2.8654317855835</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>2.88218855857849</v>
+        <v>2.88218879699707</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G548" t="n">
-        <v>2.88218855857849</v>
+        <v>2.88218879699707</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.86543202400208</v>
+        <v>2.8654317855835</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G565" t="n">
-        <v>2.88218855857849</v>
+        <v>2.88218879699707</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543458938599</v>
+        <v>3.17543482780457</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705912590027</v>
+        <v>3.47705888748169</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -32155,7 +32155,7 @@
         <v>6250</v>
       </c>
       <c r="C1223" t="n">
-        <v>7.8600001335144</v>
+        <v>7.88000011444092</v>
       </c>
       <c r="D1223" t="n">
         <v>7.6399998664856</v>
@@ -32170,6 +32170,32 @@
         <v>7.88000011444092</v>
       </c>
       <c r="H1223" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>7.96000003814697</v>
+      </c>
+      <c r="H1224" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6676459312439</v>
+        <v>2.66764616966248</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558385848999</v>
+        <v>3.90558409690857</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0848822593689</v>
+        <v>4.08488178253174</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794843673706</v>
+        <v>3.9679479598999</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136541366577</v>
+        <v>3.76136565208435</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574377059937</v>
+        <v>3.97574353218079</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>4.35772752761841</v>
+        <v>4.35772705078125</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267807006836</v>
+        <v>4.0926775932312</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283750534058</v>
+        <v>4.16283798217773</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047340393066</v>
+        <v>4.10047292709351</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G33" t="n">
-        <v>4.0069260597229</v>
+        <v>4.00692653656006</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676662445068</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676662445068</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050414085388</v>
+        <v>3.87050342559814</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015238761902</v>
+        <v>3.9601526260376</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050414085388</v>
+        <v>3.87050342559814</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628569602966</v>
+        <v>3.72628545761108</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088448524475</v>
+        <v>3.55088496208191</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922174453735</v>
+        <v>3.30922198295593</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704805374146</v>
+        <v>3.08704829216003</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516416549683</v>
+        <v>3.23516440391541</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733785629272</v>
+        <v>3.45733833312988</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021362304688</v>
+        <v>3.5002133846283</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3443021774292</v>
+        <v>3.34430193901062</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.41056489944458</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.41056489944458</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123576164246</v>
+        <v>3.46123600006104</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698777198792</v>
+        <v>3.54698753356934</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117524147034</v>
+        <v>3.92117500305176</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133515357971</v>
+        <v>3.99133491516113</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456148147583</v>
+        <v>3.94456171989441</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676662445068</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337919235229</v>
+        <v>3.91337966918945</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491275787354</v>
+        <v>3.85491251945496</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983208656311</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711647033691</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.73797869682312</v>
+        <v>3.7379789352417</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78864979743958</v>
+        <v>3.78865003585815</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983208656311</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983208656311</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644560813904</v>
+        <v>3.79644536972046</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709494590759</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459712028503</v>
+        <v>3.82459735870361</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111706733704</v>
+        <v>3.92111682891846</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709494590759</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.9050304889679</v>
+        <v>3.90503025054932</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666253089905</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666253089905</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709494590759</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535515785217</v>
+        <v>3.96535539627075</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>4.08600521087646</v>
+        <v>4.08600473403931</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>4.09404850006104</v>
+        <v>4.09404802322388</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469783782959</v>
+        <v>4.21469831466675</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209131240845</v>
+        <v>4.10209178924561</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133375167847</v>
+        <v>3.96133399009705</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687945365906</v>
+        <v>3.87687921524048</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82057571411133</v>
+        <v>3.82057547569275</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601271629333</v>
+        <v>3.7160120010376</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340619087219</v>
+        <v>3.60340595245361</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73209881782532</v>
+        <v>3.7320990562439</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992589950562</v>
+        <v>3.69992566108704</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731913566589</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731913566589</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297282218933</v>
+        <v>3.52297306060791</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025855064392</v>
+        <v>3.39025831222534</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G145" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G146" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>3.5792760848999</v>
+        <v>3.57927584648132</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112481117249</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112481117249</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677802085876</v>
+        <v>3.48677778244019</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40232300758362</v>
+        <v>3.4023232460022</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036653518677</v>
+        <v>3.41036629676819</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.4988431930542</v>
+        <v>3.49884271621704</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862650871277</v>
+        <v>3.45862627029419</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.23341345787048</v>
+        <v>3.2334132194519</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.0122218132019</v>
+        <v>3.01222229003906</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>3.03233051300049</v>
+        <v>3.03233027458191</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211406707764</v>
+        <v>2.99211382865906</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.03233051300049</v>
+        <v>3.03233027458191</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>2.87146401405334</v>
+        <v>2.87146425247192</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059775352478</v>
+        <v>2.71059799194336</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.7467930316925</v>
+        <v>2.74679279327393</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929085731506</v>
+        <v>2.83929061889648</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331250190735</v>
+        <v>2.84331274032593</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994067192078</v>
+        <v>2.95994091033936</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G231" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.625</v>
       </c>
       <c r="G234" t="n">
-        <v>2.91570258140564</v>
+        <v>2.91570234298706</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.625</v>
       </c>
       <c r="G235" t="n">
-        <v>2.91570258140564</v>
+        <v>2.91570234298706</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157247543335</v>
+        <v>2.89157223701477</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.625</v>
       </c>
       <c r="G248" t="n">
-        <v>2.91570258140564</v>
+        <v>2.91570234298706</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G249" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G250" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G275" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>3.03233051300049</v>
+        <v>3.03233027458191</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>3.38623642921448</v>
+        <v>3.38623666763306</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612796783447</v>
+        <v>3.36612820625305</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.32591152191162</v>
+        <v>3.3259117603302</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.32591152191162</v>
+        <v>3.3259117603302</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547064781189</v>
+        <v>3.61547088623047</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862650871277</v>
+        <v>3.45862627029419</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G316" t="n">
-        <v>3.20526170730591</v>
+        <v>3.20526146888733</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G317" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>3.28167343139648</v>
+        <v>3.28167319297791</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.30580353736877</v>
+        <v>3.3058032989502</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145698547363</v>
+        <v>3.24145674705505</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>3.28167343139648</v>
+        <v>3.28167319297791</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.2495002746582</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.2495002746582</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G356" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246520042419</v>
+        <v>3.55246472358704</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G389" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597874641418</v>
+        <v>3.58597922325134</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>3.46030235290527</v>
+        <v>3.46030211448669</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>3.49381589889526</v>
+        <v>3.49381613731384</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.62787103652954</v>
+        <v>3.62787127494812</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G402" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.62787103652954</v>
+        <v>3.62787127494812</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>3.59435749053955</v>
+        <v>3.59435725212097</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G415" t="n">
-        <v>3.37651777267456</v>
+        <v>3.37651753425598</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>3.36813926696777</v>
+        <v>3.36813902854919</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G420" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G424" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.75</v>
       </c>
       <c r="G430" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.75</v>
       </c>
       <c r="G432" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>3.10002851486206</v>
+        <v>3.10002875328064</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0497579574585</v>
+        <v>3.04975771903992</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>3.10002851486206</v>
+        <v>3.10002875328064</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G452" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G500" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G583" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.75</v>
       </c>
       <c r="G584" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G587" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543482780457</v>
+        <v>3.17543458938599</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705888748169</v>
+        <v>3.47705912590027</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G625" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G652" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>3.24117803573608</v>
+        <v>3.24117827415466</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>3.34601402282715</v>
+        <v>3.34601378440857</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G711" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G714" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G717" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G722" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G728" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G789" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G794" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85272097587585</v>
+        <v>3.85272121429443</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G804" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.7915666103363</v>
+        <v>3.79156684875488</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G812" t="n">
-        <v>3.8352484703064</v>
+        <v>3.83524823188782</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.66052174568176</v>
+        <v>3.66052198410034</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>3.69546699523926</v>
+        <v>3.69546723365784</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.25</v>
       </c>
       <c r="G828" t="n">
-        <v>3.71293973922729</v>
+        <v>3.71293997764587</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>3.70420336723328</v>
+        <v>3.7042031288147</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>4.32448291778564</v>
+        <v>4.32448244094849</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G849" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G853" t="n">
-        <v>4.52541828155518</v>
+        <v>4.52541780471802</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>4.6302547454834</v>
+        <v>4.63025426864624</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -32196,6 +32196,32 @@
         <v>7.96000003814697</v>
       </c>
       <c r="H1224" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1225" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>8.03999996185303</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>8</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>8</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1225" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -485,7 +485,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621223449707</v>
+        <v>3.25621247291565</v>
       </c>
       <c r="H4" t="n">
         <v>912000</v>
@@ -543,7 +543,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>5.30099248886108</v>
+        <v>5.30099201202393</v>
       </c>
       <c r="H6" t="n">
         <v>635500</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906972885132</v>
+        <v>4.45906925201416</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -601,7 +601,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H8" t="n">
         <v>594000</v>
@@ -630,7 +630,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558409690857</v>
+        <v>3.90558362007141</v>
       </c>
       <c r="H9" t="n">
         <v>388500</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.08488130569458</v>
+        <v>4.0848822593689</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -717,7 +717,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794843673706</v>
+        <v>3.9679479598999</v>
       </c>
       <c r="H12" t="n">
         <v>65500</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136517524719</v>
+        <v>3.76136565208435</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -804,7 +804,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>4.35772705078125</v>
+        <v>4.35772752761841</v>
       </c>
       <c r="H15" t="n">
         <v>539000</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0926775932312</v>
+        <v>4.09267711639404</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756713867188</v>
+        <v>4.28756666183472</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1181,7 +1181,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961141586304</v>
+        <v>4.20961093902588</v>
       </c>
       <c r="H28" t="n">
         <v>43500</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283798217773</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1239,7 +1239,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H30" t="n">
         <v>54500</v>
@@ -1297,7 +1297,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H32" t="n">
         <v>11500</v>
@@ -1355,7 +1355,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>4.03031301498413</v>
+        <v>4.03031349182129</v>
       </c>
       <c r="H34" t="n">
         <v>24000</v>
@@ -1471,7 +1471,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999223709106</v>
+        <v>3.88999247550964</v>
       </c>
       <c r="H38" t="n">
         <v>32000</v>
@@ -1558,7 +1558,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219714164734</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H41" t="n">
         <v>10500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1703,7 +1703,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034375190735</v>
+        <v>3.80034351348877</v>
       </c>
       <c r="H46" t="n">
         <v>82500</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015286445618</v>
+        <v>3.96015238761902</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628593444824</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088448524475</v>
+        <v>3.55088472366333</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1877,7 +1877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922174453735</v>
+        <v>3.30922198295593</v>
       </c>
       <c r="H52" t="n">
         <v>36500</v>
@@ -1906,7 +1906,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704805374146</v>
+        <v>3.08704829216003</v>
       </c>
       <c r="H53" t="n">
         <v>44000</v>
@@ -1993,7 +1993,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685764312744</v>
+        <v>3.24685740470886</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2051,7 +2051,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021362304688</v>
+        <v>3.5002133846283</v>
       </c>
       <c r="H58" t="n">
         <v>8000</v>
@@ -2109,7 +2109,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.41056489944458</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H60" t="n">
         <v>8000</v>
@@ -2138,7 +2138,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.41056489944458</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H61" t="n">
         <v>500</v>
@@ -2167,7 +2167,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.38328003883362</v>
+        <v>3.38328051567078</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2196,7 +2196,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123552322388</v>
+        <v>3.46123600006104</v>
       </c>
       <c r="H63" t="n">
         <v>5500</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698777198792</v>
+        <v>3.54698753356934</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2312,7 +2312,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117524147034</v>
+        <v>3.92117476463318</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133491516113</v>
+        <v>3.99133467674255</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2370,7 +2370,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.99913048744202</v>
+        <v>3.9991307258606</v>
       </c>
       <c r="H69" t="n">
         <v>13000</v>
@@ -2428,7 +2428,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456148147583</v>
+        <v>3.94456171989441</v>
       </c>
       <c r="H71" t="n">
         <v>13500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2544,7 +2544,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491299629211</v>
+        <v>3.85491228103638</v>
       </c>
       <c r="H75" t="n">
         <v>11000</v>
@@ -2602,7 +2602,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219714164734</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.8432195186615</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219714164734</v>
+        <v>3.88219738006592</v>
       </c>
       <c r="H81" t="n">
         <v>1500</v>
@@ -2776,7 +2776,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999223709106</v>
+        <v>3.88999247550964</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2834,7 +2834,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593489646912</v>
+        <v>3.81593465805054</v>
       </c>
       <c r="H85" t="n">
         <v>2500</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.8432195186615</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2950,7 +2950,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78864979743958</v>
+        <v>3.78865003585815</v>
       </c>
       <c r="H89" t="n">
         <v>6500</v>
@@ -3037,7 +3037,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593489646912</v>
+        <v>3.81593465805054</v>
       </c>
       <c r="H92" t="n">
         <v>6500</v>
@@ -3211,7 +3211,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88894414901733</v>
+        <v>3.88894391059875</v>
       </c>
       <c r="H98" t="n">
         <v>5000</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448889732361</v>
+        <v>3.80448913574219</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111730575562</v>
+        <v>3.92111706733704</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720388412476</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720388412476</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3501,7 +3501,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535515785217</v>
+        <v>3.96535563468933</v>
       </c>
       <c r="H108" t="n">
         <v>10500</v>
@@ -3530,7 +3530,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>4.08600521087646</v>
+        <v>4.08600473403931</v>
       </c>
       <c r="H109" t="n">
         <v>17000</v>
@@ -3588,7 +3588,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>4.09404850006104</v>
+        <v>4.09404802322388</v>
       </c>
       <c r="H111" t="n">
         <v>4000</v>
@@ -3617,7 +3617,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469783782959</v>
+        <v>4.21469831466675</v>
       </c>
       <c r="H112" t="n">
         <v>17000</v>
@@ -3820,7 +3820,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383157730103</v>
+        <v>4.05383205413818</v>
       </c>
       <c r="H119" t="n">
         <v>3500</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133351325989</v>
+        <v>3.96133375167847</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687945365906</v>
+        <v>3.87687873840332</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -4023,7 +4023,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601247787476</v>
+        <v>3.7160120010376</v>
       </c>
       <c r="H126" t="n">
         <v>9000</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949253082275</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4139,7 +4139,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340595245361</v>
+        <v>3.60340619087219</v>
       </c>
       <c r="H130" t="n">
         <v>1500</v>
@@ -4168,7 +4168,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H131" t="n">
         <v>3000</v>
@@ -4197,7 +4197,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73209881782532</v>
+        <v>3.7320990562439</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4284,7 +4284,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775250434875</v>
+        <v>3.66775226593018</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4313,7 +4313,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.55916786193848</v>
+        <v>3.5591676235199</v>
       </c>
       <c r="H136" t="n">
         <v>10500</v>
@@ -4342,7 +4342,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688624382019</v>
+        <v>3.50688600540161</v>
       </c>
       <c r="H137" t="n">
         <v>500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482083320618</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H139" t="n">
         <v>500</v>
@@ -4429,7 +4429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297282218933</v>
+        <v>3.52297306060791</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482083320618</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4661,7 +4661,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.55916786193848</v>
+        <v>3.5591676235199</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H150" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H154" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>3.5792760848999</v>
+        <v>3.57927584648132</v>
       </c>
       <c r="H155" t="n">
         <v>2500</v>
@@ -4893,7 +4893,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H156" t="n">
         <v>9500</v>
@@ -4980,7 +4980,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677802085876</v>
+        <v>3.48677778244019</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5067,7 +5067,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069144248962</v>
+        <v>3.47069120407104</v>
       </c>
       <c r="H162" t="n">
         <v>5000</v>
@@ -5125,7 +5125,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036653518677</v>
+        <v>3.41036605834961</v>
       </c>
       <c r="H164" t="n">
         <v>500</v>
@@ -5154,7 +5154,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069144248962</v>
+        <v>3.47069120407104</v>
       </c>
       <c r="H165" t="n">
         <v>1500</v>
@@ -5183,7 +5183,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H166" t="n">
         <v>500</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>3.49079966545105</v>
+        <v>3.49079990386963</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5357,7 +5357,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>3.34601974487305</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.2334132194519</v>
+        <v>3.23341345787048</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5589,7 +5589,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H180" t="n">
         <v>2000</v>
@@ -5618,7 +5618,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H181" t="n">
         <v>2500</v>
@@ -5647,7 +5647,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5879,7 +5879,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222205162048</v>
+        <v>3.01222229003906</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5966,7 +5966,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H193" t="n">
         <v>92500</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H196" t="n">
         <v>19000</v>
@@ -6169,7 +6169,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G201" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H201" t="n">
         <v>5000</v>
@@ -6227,7 +6227,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H203" t="n">
         <v>500</v>
@@ -6314,7 +6314,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.73472809791565</v>
+        <v>2.73472785949707</v>
       </c>
       <c r="H213" t="n">
         <v>10000</v>
@@ -6575,7 +6575,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896571159363</v>
+        <v>2.77896595001221</v>
       </c>
       <c r="H214" t="n">
         <v>9000</v>
@@ -6604,7 +6604,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H215" t="n">
         <v>5500</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="n">
         <v>7500</v>
@@ -6662,7 +6662,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929109573364</v>
+        <v>2.83929085731506</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -6981,7 +6981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994067192078</v>
+        <v>2.95994091033936</v>
       </c>
       <c r="H228" t="n">
         <v>5000</v>
@@ -7010,7 +7010,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H229" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G231" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H231" t="n">
         <v>1500</v>
@@ -7097,7 +7097,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H232" t="n">
         <v>4000</v>
@@ -7126,7 +7126,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H233" t="n">
         <v>500</v>
@@ -7213,7 +7213,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H236" t="n">
         <v>2500</v>
@@ -7242,7 +7242,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G237" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H237" t="n">
         <v>1000</v>
@@ -7329,7 +7329,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H240" t="n">
         <v>2000</v>
@@ -7358,7 +7358,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G249" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7619,7 +7619,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G250" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7706,7 +7706,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.89961576461792</v>
+        <v>2.8996160030365</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7764,7 +7764,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H257" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H260" t="n">
         <v>2000</v>
@@ -7938,7 +7938,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H261" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H262" t="n">
         <v>2000</v>
@@ -7996,7 +7996,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8170,7 +8170,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H269" t="n">
         <v>11500</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8228,7 +8228,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8315,7 +8315,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H274" t="n">
         <v>7000</v>
@@ -8344,7 +8344,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G275" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8373,7 +8373,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H276" t="n">
         <v>7000</v>
@@ -8431,7 +8431,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H278" t="n">
         <v>1500</v>
@@ -8518,7 +8518,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="n">
         <v>13500</v>
@@ -8576,7 +8576,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H283" t="n">
         <v>17500</v>
@@ -8605,7 +8605,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917536735535</v>
+        <v>3.18917512893677</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8808,7 +8808,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047451972961</v>
+        <v>3.43047475814819</v>
       </c>
       <c r="H291" t="n">
         <v>70000</v>
@@ -8837,7 +8837,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H292" t="n">
         <v>17000</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656085968018</v>
+        <v>3.44656109809875</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8924,7 +8924,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>3.38623642921448</v>
+        <v>3.38623666763306</v>
       </c>
       <c r="H295" t="n">
         <v>47000</v>
@@ -8953,7 +8953,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612796783447</v>
+        <v>3.36612820625305</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9127,7 +9127,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H302" t="n">
         <v>7000</v>
@@ -9156,7 +9156,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.35004162788391</v>
+        <v>3.35004138946533</v>
       </c>
       <c r="H303" t="n">
         <v>1500</v>
@@ -9214,7 +9214,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H305" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>3.34601974487305</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9417,7 +9417,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9562,7 +9562,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G317" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H317" t="n">
         <v>17500</v>
@@ -9736,7 +9736,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H323" t="n">
         <v>7500</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H326" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H328" t="n">
         <v>4000</v>
@@ -9910,7 +9910,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10055,7 +10055,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H334" t="n">
         <v>4500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189035415649</v>
+        <v>3.32188987731934</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.2977602481842</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.2977602481842</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10229,7 +10229,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.30580353736877</v>
+        <v>3.3058032989502</v>
       </c>
       <c r="H340" t="n">
         <v>1000</v>
@@ -10258,7 +10258,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>3.26558661460876</v>
+        <v>3.26558685302734</v>
       </c>
       <c r="H341" t="n">
         <v>2000</v>
@@ -10287,7 +10287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H342" t="n">
         <v>8000</v>
@@ -10316,7 +10316,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145698547363</v>
+        <v>3.24145674705505</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H347" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H350" t="n">
         <v>3500</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H352" t="n">
         <v>500</v>
@@ -10664,7 +10664,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G356" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H359" t="n">
         <v>34500</v>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H361" t="n">
         <v>3500</v>
@@ -10867,7 +10867,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H362" t="n">
         <v>16500</v>
@@ -10896,7 +10896,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.39327478408813</v>
+        <v>3.39327454566956</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H369" t="n">
         <v>9000</v>
@@ -11099,7 +11099,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192384719849</v>
+        <v>3.45192360877991</v>
       </c>
       <c r="H370" t="n">
         <v>10500</v>
@@ -11128,7 +11128,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H372" t="n">
         <v>13500</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H373" t="n">
         <v>10500</v>
@@ -11273,7 +11273,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H376" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H377" t="n">
         <v>4000</v>
@@ -11331,7 +11331,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246496200562</v>
+        <v>3.55246472358704</v>
       </c>
       <c r="H378" t="n">
         <v>27000</v>
@@ -11389,7 +11389,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H380" t="n">
         <v>61500</v>
@@ -11418,7 +11418,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H381" t="n">
         <v>17500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H382" t="n">
         <v>25500</v>
@@ -11476,7 +11476,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H383" t="n">
         <v>33500</v>
@@ -11505,7 +11505,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H384" t="n">
         <v>14000</v>
@@ -11534,7 +11534,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679113388062</v>
+        <v>3.73679137229919</v>
       </c>
       <c r="H385" t="n">
         <v>34000</v>
@@ -11563,7 +11563,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G386" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H386" t="n">
         <v>127500</v>
@@ -11592,7 +11592,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G387" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H387" t="n">
         <v>8000</v>
@@ -11650,7 +11650,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G389" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H389" t="n">
         <v>59500</v>
@@ -11679,7 +11679,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597898483276</v>
+        <v>3.58597922325134</v>
       </c>
       <c r="H390" t="n">
         <v>24500</v>
@@ -11708,7 +11708,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H391" t="n">
         <v>7000</v>
@@ -11737,7 +11737,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H392" t="n">
         <v>15500</v>
@@ -11766,7 +11766,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>3.46030235290527</v>
+        <v>3.46030211448669</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11795,7 +11795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H394" t="n">
         <v>16500</v>
@@ -11824,7 +11824,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H395" t="n">
         <v>10500</v>
@@ -11853,7 +11853,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>3.49381589889526</v>
+        <v>3.49381613731384</v>
       </c>
       <c r="H396" t="n">
         <v>5000</v>
@@ -12027,7 +12027,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G402" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H402" t="n">
         <v>7000</v>
@@ -12114,7 +12114,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H405" t="n">
         <v>15000</v>
@@ -12201,7 +12201,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H408" t="n">
         <v>5000</v>
@@ -12230,7 +12230,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408669471741</v>
       </c>
       <c r="H409" t="n">
         <v>10500</v>
@@ -12259,7 +12259,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.51057267189026</v>
+        <v>3.51057291030884</v>
       </c>
       <c r="H410" t="n">
         <v>8000</v>
@@ -12288,7 +12288,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354557991028</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H411" t="n">
         <v>14500</v>
@@ -12317,7 +12317,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H412" t="n">
         <v>27500</v>
@@ -12346,7 +12346,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354557991028</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H413" t="n">
         <v>8500</v>
@@ -12404,7 +12404,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G415" t="n">
-        <v>3.37651777267456</v>
+        <v>3.37651753425598</v>
       </c>
       <c r="H415" t="n">
         <v>8500</v>
@@ -12462,7 +12462,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H417" t="n">
         <v>10500</v>
@@ -12520,7 +12520,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H419" t="n">
         <v>9000</v>
@@ -12549,7 +12549,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G420" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H420" t="n">
         <v>45000</v>
@@ -12578,7 +12578,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H421" t="n">
         <v>28500</v>
@@ -12607,7 +12607,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H422" t="n">
         <v>11500</v>
@@ -12636,7 +12636,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H423" t="n">
         <v>57000</v>
@@ -12665,7 +12665,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G424" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H424" t="n">
         <v>9500</v>
@@ -12723,7 +12723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H426" t="n">
         <v>16000</v>
@@ -12781,7 +12781,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H428" t="n">
         <v>19000</v>
@@ -12810,7 +12810,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H429" t="n">
         <v>10500</v>
@@ -12839,7 +12839,7 @@
         <v>3.75</v>
       </c>
       <c r="G430" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H430" t="n">
         <v>12500</v>
@@ -12897,7 +12897,7 @@
         <v>3.75</v>
       </c>
       <c r="G432" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H432" t="n">
         <v>13500</v>
@@ -12955,7 +12955,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H434" t="n">
         <v>19000</v>
@@ -12984,7 +12984,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>3.10002851486206</v>
+        <v>3.10002875328064</v>
       </c>
       <c r="H435" t="n">
         <v>2000</v>
@@ -13100,7 +13100,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H439" t="n">
         <v>18000</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>3.10002851486206</v>
+        <v>3.10002875328064</v>
       </c>
       <c r="H446" t="n">
         <v>5000</v>
@@ -13419,7 +13419,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H451" t="n">
         <v>2000</v>
@@ -13477,7 +13477,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G452" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H452" t="n">
         <v>55500</v>
@@ -13535,7 +13535,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H454" t="n">
         <v>22000</v>
@@ -13564,7 +13564,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H455" t="n">
         <v>3500</v>
@@ -13593,7 +13593,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G456" t="n">
-        <v>3.00786519050598</v>
+        <v>3.00786542892456</v>
       </c>
       <c r="H456" t="n">
         <v>17000</v>
@@ -13738,7 +13738,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H461" t="n">
         <v>20500</v>
@@ -13767,7 +13767,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H462" t="n">
         <v>12000</v>
@@ -13970,7 +13970,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H469" t="n">
         <v>19500</v>
@@ -13999,7 +13999,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H470" t="n">
         <v>500</v>
@@ -14289,7 +14289,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H480" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H481" t="n">
         <v>1000</v>
@@ -14579,7 +14579,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H490" t="n">
         <v>13500</v>
@@ -14637,7 +14637,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H492" t="n">
         <v>13500</v>
@@ -14869,7 +14869,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G500" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H500" t="n">
         <v>23500</v>
@@ -14956,7 +14956,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H503" t="n">
         <v>72000</v>
@@ -15014,7 +15014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H505" t="n">
         <v>18000</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H516" t="n">
         <v>7500</v>
@@ -15362,7 +15362,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H517" t="n">
         <v>39500</v>
@@ -15391,7 +15391,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H518" t="n">
         <v>16500</v>
@@ -15420,7 +15420,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H519" t="n">
         <v>19000</v>
@@ -15449,7 +15449,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H520" t="n">
         <v>12000</v>
@@ -15594,7 +15594,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H525" t="n">
         <v>20500</v>
@@ -15855,7 +15855,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H534" t="n">
         <v>10000</v>
@@ -16029,7 +16029,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H540" t="n">
         <v>16500</v>
@@ -16203,7 +16203,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H546" t="n">
         <v>20500</v>
@@ -16290,7 +16290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H549" t="n">
         <v>1500</v>
@@ -16377,7 +16377,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H552" t="n">
         <v>11000</v>
@@ -16406,7 +16406,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G553" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H553" t="n">
         <v>25500</v>
@@ -16464,7 +16464,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H555" t="n">
         <v>15500</v>
@@ -16493,7 +16493,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H556" t="n">
         <v>500</v>
@@ -16522,7 +16522,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H557" t="n">
         <v>12500</v>
@@ -16696,7 +16696,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H563" t="n">
         <v>37500</v>
@@ -16725,7 +16725,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H564" t="n">
         <v>10000</v>
@@ -16783,7 +16783,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H566" t="n">
         <v>7500</v>
@@ -16841,7 +16841,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H568" t="n">
         <v>1500</v>
@@ -16870,7 +16870,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H569" t="n">
         <v>4000</v>
@@ -16986,7 +16986,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732383728027</v>
       </c>
       <c r="H573" t="n">
         <v>8000</v>
@@ -17160,7 +17160,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H579" t="n">
         <v>18000</v>
@@ -17276,7 +17276,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G583" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H583" t="n">
         <v>7500</v>
@@ -17305,7 +17305,7 @@
         <v>3.75</v>
       </c>
       <c r="G584" t="n">
-        <v>3.14192080497742</v>
+        <v>3.14192056655884</v>
       </c>
       <c r="H584" t="n">
         <v>20500</v>
@@ -17334,7 +17334,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H585" t="n">
         <v>3000</v>
@@ -17392,7 +17392,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G587" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H587" t="n">
         <v>13500</v>
@@ -17421,7 +17421,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H588" t="n">
         <v>4500</v>
@@ -17450,7 +17450,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H589" t="n">
         <v>20000</v>
@@ -17508,7 +17508,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H591" t="n">
         <v>7000</v>
@@ -17566,7 +17566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.16705632209778</v>
+        <v>3.1670560836792</v>
       </c>
       <c r="H593" t="n">
         <v>20500</v>
@@ -17595,7 +17595,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543482780457</v>
+        <v>3.17543458938599</v>
       </c>
       <c r="H594" t="n">
         <v>10000</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H598" t="n">
         <v>15000</v>
@@ -17740,7 +17740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H599" t="n">
         <v>10000</v>
@@ -17769,7 +17769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H600" t="n">
         <v>29000</v>
@@ -17798,7 +17798,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H601" t="n">
         <v>13000</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H602" t="n">
         <v>20500</v>
@@ -18001,7 +18001,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705888748169</v>
+        <v>3.47705912590027</v>
       </c>
       <c r="H608" t="n">
         <v>67000</v>
@@ -18494,7 +18494,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G625" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H625" t="n">
         <v>7000</v>
@@ -18639,7 +18639,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H630" t="n">
         <v>8500</v>
@@ -18755,7 +18755,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H634" t="n">
         <v>3000</v>
@@ -18784,7 +18784,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H635" t="n">
         <v>11000</v>
@@ -18929,7 +18929,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H640" t="n">
         <v>10000</v>
@@ -18958,7 +18958,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H641" t="n">
         <v>8000</v>
@@ -18987,7 +18987,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H642" t="n">
         <v>67500</v>
@@ -19045,7 +19045,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H644" t="n">
         <v>10000</v>
@@ -19103,7 +19103,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H646" t="n">
         <v>7500</v>
@@ -19248,7 +19248,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H651" t="n">
         <v>17500</v>
@@ -19277,7 +19277,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G652" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H652" t="n">
         <v>22500</v>
@@ -19306,7 +19306,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H653" t="n">
         <v>23500</v>
@@ -19393,7 +19393,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>3.24117803573608</v>
+        <v>3.24117827415466</v>
       </c>
       <c r="H656" t="n">
         <v>35500</v>
@@ -19625,7 +19625,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H664" t="n">
         <v>13500</v>
@@ -19654,7 +19654,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>3.34601402282715</v>
+        <v>3.34601378440857</v>
       </c>
       <c r="H665" t="n">
         <v>6000</v>
@@ -19683,7 +19683,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H666" t="n">
         <v>31500</v>
@@ -19741,7 +19741,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H668" t="n">
         <v>21500</v>
@@ -19915,7 +19915,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H674" t="n">
         <v>52000</v>
@@ -19944,7 +19944,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H675" t="n">
         <v>9500</v>
@@ -19973,7 +19973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H676" t="n">
         <v>26000</v>
@@ -20089,7 +20089,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H680" t="n">
         <v>6500</v>
@@ -20408,7 +20408,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H691" t="n">
         <v>6500</v>
@@ -20437,7 +20437,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H692" t="n">
         <v>12500</v>
@@ -20988,7 +20988,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G711" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H711" t="n">
         <v>25000</v>
@@ -21075,7 +21075,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G714" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H714" t="n">
         <v>12500</v>
@@ -21162,7 +21162,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G717" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H717" t="n">
         <v>38000</v>
@@ -21307,7 +21307,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G722" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H722" t="n">
         <v>33500</v>
@@ -21423,7 +21423,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H726" t="n">
         <v>12500</v>
@@ -21481,7 +21481,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G728" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H728" t="n">
         <v>15000</v>
@@ -22873,7 +22873,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H776" t="n">
         <v>49000</v>
@@ -23221,7 +23221,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H788" t="n">
         <v>12500</v>
@@ -23250,7 +23250,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G789" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H789" t="n">
         <v>9500</v>
@@ -23395,7 +23395,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G794" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H794" t="n">
         <v>14500</v>
@@ -23511,7 +23511,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H798" t="n">
         <v>8000</v>
@@ -23569,7 +23569,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85272097587585</v>
+        <v>3.85272121429443</v>
       </c>
       <c r="H800" t="n">
         <v>42000</v>
@@ -23685,7 +23685,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G804" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H804" t="n">
         <v>13500</v>
@@ -23743,7 +23743,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.7915666103363</v>
+        <v>3.79156684875488</v>
       </c>
       <c r="H808" t="n">
         <v>3500</v>
@@ -23917,7 +23917,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G812" t="n">
-        <v>3.8352484703064</v>
+        <v>3.83524823188782</v>
       </c>
       <c r="H812" t="n">
         <v>18000</v>
@@ -24062,7 +24062,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.66052174568176</v>
+        <v>3.66052198410034</v>
       </c>
       <c r="H817" t="n">
         <v>36000</v>
@@ -24294,7 +24294,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>3.69546699523926</v>
+        <v>3.69546723365784</v>
       </c>
       <c r="H825" t="n">
         <v>17500</v>
@@ -24381,7 +24381,7 @@
         <v>4.25</v>
       </c>
       <c r="G828" t="n">
-        <v>3.71293973922729</v>
+        <v>3.71293997764587</v>
       </c>
       <c r="H828" t="n">
         <v>10000</v>
@@ -24410,7 +24410,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>3.70420336723328</v>
+        <v>3.7042031288147</v>
       </c>
       <c r="H829" t="n">
         <v>6500</v>
@@ -24700,7 +24700,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>4.32448291778564</v>
+        <v>4.32448244094849</v>
       </c>
       <c r="H839" t="n">
         <v>26000</v>
@@ -24990,7 +24990,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G849" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H849" t="n">
         <v>14000</v>
@@ -25048,7 +25048,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H851" t="n">
         <v>14000</v>
@@ -25106,7 +25106,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G853" t="n">
-        <v>4.52541828155518</v>
+        <v>4.52541780471802</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25222,7 +25222,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>4.6302547454834</v>
+        <v>4.63025426864624</v>
       </c>
       <c r="H857" t="n">
         <v>8500</v>
@@ -25309,7 +25309,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H860" t="n">
         <v>4000</v>
@@ -25396,7 +25396,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H863" t="n">
         <v>3500</v>
@@ -35929,6 +35929,35 @@
         <v>10750</v>
       </c>
       <c r="I1226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1227" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>7.8600001335144</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>7.90000009536743</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I1227" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516045570374</v>
+        <v>2.62516021728516</v>
       </c>
       <c r="H2" t="n">
         <v>1387000</v>
@@ -456,7 +456,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66764616966248</v>
+        <v>2.6676459312439</v>
       </c>
       <c r="H3" t="n">
         <v>383000</v>
@@ -485,7 +485,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621247291565</v>
+        <v>3.25621199607849</v>
       </c>
       <c r="H4" t="n">
         <v>912000</v>
@@ -514,7 +514,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805168151855</v>
+        <v>4.20805215835571</v>
       </c>
       <c r="H5" t="n">
         <v>1121500</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906925201416</v>
+        <v>4.45906972885132</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -601,7 +601,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H8" t="n">
         <v>594000</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0848822593689</v>
+        <v>4.08488178253174</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -833,7 +833,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536247253418</v>
+        <v>4.2953634262085</v>
       </c>
       <c r="H16" t="n">
         <v>208500</v>
@@ -862,7 +862,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H17" t="n">
         <v>60000</v>
@@ -920,7 +920,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H19" t="n">
         <v>93500</v>
@@ -949,7 +949,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536247253418</v>
+        <v>4.2953634262085</v>
       </c>
       <c r="H20" t="n">
         <v>61500</v>
@@ -978,7 +978,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H21" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267711639404</v>
+        <v>4.0926775932312</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756666183472</v>
+        <v>4.28756713867188</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1094,7 +1094,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536247253418</v>
+        <v>4.2953634262085</v>
       </c>
       <c r="H25" t="n">
         <v>60000</v>
@@ -1181,7 +1181,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961093902588</v>
+        <v>4.20961141586304</v>
       </c>
       <c r="H28" t="n">
         <v>43500</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283750534058</v>
+        <v>4.16283798217773</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1239,7 +1239,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H30" t="n">
         <v>54500</v>
@@ -1268,7 +1268,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047340393066</v>
+        <v>4.10047292709351</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1297,7 +1297,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929016113281</v>
       </c>
       <c r="H32" t="n">
         <v>11500</v>
@@ -1326,7 +1326,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G33" t="n">
-        <v>4.0069260597229</v>
+        <v>4.00692653656006</v>
       </c>
       <c r="H33" t="n">
         <v>16000</v>
@@ -1355,7 +1355,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>4.03031349182129</v>
+        <v>4.03031301498413</v>
       </c>
       <c r="H34" t="n">
         <v>24000</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050366401672</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1674,7 +1674,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711694717407</v>
       </c>
       <c r="H45" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015238761902</v>
+        <v>3.96015214920044</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050366401672</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628569602966</v>
+        <v>3.72628545761108</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088472366333</v>
+        <v>3.55088448524475</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1935,7 +1935,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516416549683</v>
+        <v>3.23516440391541</v>
       </c>
       <c r="H54" t="n">
         <v>7500</v>
@@ -1993,7 +1993,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685740470886</v>
+        <v>3.24685764312744</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4573380947113</v>
+        <v>3.45733833312988</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2051,7 +2051,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.5002133846283</v>
+        <v>3.50021314620972</v>
       </c>
       <c r="H58" t="n">
         <v>8000</v>
@@ -2080,7 +2080,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3443021774292</v>
+        <v>3.34430193901062</v>
       </c>
       <c r="H59" t="n">
         <v>18500</v>
@@ -2167,7 +2167,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.38328051567078</v>
+        <v>3.3832802772522</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2225,7 +2225,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529381752014</v>
+        <v>3.53529405593872</v>
       </c>
       <c r="H64" t="n">
         <v>3500</v>
@@ -2283,7 +2283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542346954346</v>
+        <v>3.8354229927063</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117476463318</v>
+        <v>3.92117547988892</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133467674255</v>
+        <v>3.99133491516113</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676590919495</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2486,7 +2486,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337966918945</v>
+        <v>3.91337919235229</v>
       </c>
       <c r="H73" t="n">
         <v>6500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2544,7 +2544,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491228103638</v>
+        <v>3.8549120426178</v>
       </c>
       <c r="H75" t="n">
         <v>11000</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542346954346</v>
+        <v>3.8354229927063</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.8432195186615</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2747,7 +2747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711694717407</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2834,7 +2834,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593465805054</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H85" t="n">
         <v>2500</v>
@@ -2863,7 +2863,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711694717407</v>
       </c>
       <c r="H86" t="n">
         <v>1000</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.8432195186615</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542346954346</v>
+        <v>3.8354229927063</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3037,7 +3037,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593465805054</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H92" t="n">
         <v>6500</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3153,7 +3153,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709494590759</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88894391059875</v>
+        <v>3.88894414901733</v>
       </c>
       <c r="H98" t="n">
         <v>5000</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448913574219</v>
+        <v>3.80448889732361</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111706733704</v>
+        <v>3.92111682891846</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720364570618</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720364570618</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3356,7 +3356,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709494590759</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3414,7 +3414,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666253089905</v>
       </c>
       <c r="H105" t="n">
         <v>10000</v>
@@ -3443,7 +3443,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666253089905</v>
       </c>
       <c r="H106" t="n">
         <v>3500</v>
@@ -3472,7 +3472,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709494590759</v>
       </c>
       <c r="H107" t="n">
         <v>21000</v>
@@ -3501,7 +3501,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535563468933</v>
+        <v>3.96535539627075</v>
       </c>
       <c r="H108" t="n">
         <v>10500</v>
@@ -3675,7 +3675,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274112701416</v>
+        <v>4.22274160385132</v>
       </c>
       <c r="H114" t="n">
         <v>6000</v>
@@ -3820,7 +3820,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383205413818</v>
+        <v>4.05383157730103</v>
       </c>
       <c r="H119" t="n">
         <v>3500</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133375167847</v>
+        <v>3.96133399009705</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687873840332</v>
+        <v>3.87687921524048</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949253082275</v>
+        <v>3.61949276924133</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4139,7 +4139,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340619087219</v>
+        <v>3.60340595245361</v>
       </c>
       <c r="H130" t="n">
         <v>1500</v>
@@ -4168,7 +4168,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H131" t="n">
         <v>3000</v>
@@ -4226,7 +4226,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992589950562</v>
+        <v>3.69992566108704</v>
       </c>
       <c r="H133" t="n">
         <v>5000</v>
@@ -4284,7 +4284,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775226593018</v>
+        <v>3.66775250434875</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4313,7 +4313,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.5591676235199</v>
+        <v>3.55916786193848</v>
       </c>
       <c r="H136" t="n">
         <v>10500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H139" t="n">
         <v>500</v>
@@ -4429,7 +4429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4661,7 +4661,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.5591676235199</v>
+        <v>3.55916786193848</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.5752546787262</v>
+        <v>3.57525444030762</v>
       </c>
       <c r="H150" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>3.5752546787262</v>
+        <v>3.57525444030762</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H156" t="n">
         <v>9500</v>
@@ -5009,7 +5009,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>3.48275637626648</v>
+        <v>3.4827561378479</v>
       </c>
       <c r="H160" t="n">
         <v>1000</v>
@@ -5067,7 +5067,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069120407104</v>
+        <v>3.47069144248962</v>
       </c>
       <c r="H162" t="n">
         <v>5000</v>
@@ -5125,7 +5125,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036605834961</v>
+        <v>3.41036629676819</v>
       </c>
       <c r="H164" t="n">
         <v>500</v>
@@ -5154,7 +5154,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069120407104</v>
+        <v>3.47069144248962</v>
       </c>
       <c r="H165" t="n">
         <v>1500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884295463562</v>
+        <v>3.49884271621704</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>3.49079990386963</v>
+        <v>3.49079966545105</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5270,7 +5270,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862650871277</v>
+        <v>3.45862627029419</v>
       </c>
       <c r="H169" t="n">
         <v>10500</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.23341345787048</v>
+        <v>3.2334132194519</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5560,7 +5560,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H179" t="n">
         <v>3500</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H183" t="n">
         <v>21500</v>
@@ -5850,7 +5850,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H189" t="n">
         <v>4000</v>
@@ -5995,7 +5995,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>3.03233051300049</v>
+        <v>3.03233027458191</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6082,7 +6082,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.03233051300049</v>
+        <v>3.03233027458191</v>
       </c>
       <c r="H197" t="n">
         <v>107500</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H199" t="n">
         <v>5500</v>
@@ -6198,7 +6198,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G201" t="n">
-        <v>2.92776727676392</v>
+        <v>2.9277675151825</v>
       </c>
       <c r="H201" t="n">
         <v>5000</v>
@@ -6227,7 +6227,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.92776727676392</v>
+        <v>2.9277675151825</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059775352478</v>
+        <v>2.71059799194336</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6662,7 +6662,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6691,7 +6691,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929085731506</v>
+        <v>2.83929061889648</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -6836,7 +6836,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331250190735</v>
+        <v>2.84331274032593</v>
       </c>
       <c r="H223" t="n">
         <v>1000</v>
@@ -7155,7 +7155,7 @@
         <v>3.625</v>
       </c>
       <c r="G234" t="n">
-        <v>2.91570258140564</v>
+        <v>2.91570234298706</v>
       </c>
       <c r="H234" t="n">
         <v>1500</v>
@@ -7184,7 +7184,7 @@
         <v>3.625</v>
       </c>
       <c r="G235" t="n">
-        <v>2.91570258140564</v>
+        <v>2.91570234298706</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G237" t="n">
-        <v>2.92776727676392</v>
+        <v>2.9277675151825</v>
       </c>
       <c r="H237" t="n">
         <v>1000</v>
@@ -7416,7 +7416,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H243" t="n">
         <v>500</v>
@@ -7445,7 +7445,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157247543335</v>
+        <v>2.89157223701477</v>
       </c>
       <c r="H245" t="n">
         <v>1000</v>
@@ -7503,7 +7503,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.625</v>
       </c>
       <c r="G248" t="n">
-        <v>2.91570258140564</v>
+        <v>2.91570234298706</v>
       </c>
       <c r="H248" t="n">
         <v>1500</v>
@@ -7793,7 +7793,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374587059021</v>
+        <v>2.92374563217163</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -7851,7 +7851,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H258" t="n">
         <v>1000</v>
@@ -8170,7 +8170,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H269" t="n">
         <v>11500</v>
@@ -8460,7 +8460,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H279" t="n">
         <v>5500</v>
@@ -8489,7 +8489,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H280" t="n">
         <v>15500</v>
@@ -8576,7 +8576,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H283" t="n">
         <v>17500</v>
@@ -8605,7 +8605,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8692,7 +8692,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H287" t="n">
         <v>5500</v>
@@ -8721,7 +8721,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>3.03233051300049</v>
+        <v>3.03233027458191</v>
       </c>
       <c r="H288" t="n">
         <v>13500</v>
@@ -8808,7 +8808,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047475814819</v>
+        <v>3.43047451972961</v>
       </c>
       <c r="H291" t="n">
         <v>70000</v>
@@ -9156,7 +9156,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.35004138946533</v>
+        <v>3.35004162788391</v>
       </c>
       <c r="H303" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862650871277</v>
+        <v>3.45862627029419</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G316" t="n">
-        <v>3.20526170730591</v>
+        <v>3.20526146888733</v>
       </c>
       <c r="H316" t="n">
         <v>18000</v>
@@ -9591,7 +9591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9736,7 +9736,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H323" t="n">
         <v>7500</v>
@@ -9765,7 +9765,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H324" t="n">
         <v>6500</v>
@@ -9794,7 +9794,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H327" t="n">
         <v>2500</v>
@@ -9881,7 +9881,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H328" t="n">
         <v>4000</v>
@@ -9910,7 +9910,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>3.28167343139648</v>
+        <v>3.28167319297791</v>
       </c>
       <c r="H332" t="n">
         <v>4500</v>
@@ -10026,7 +10026,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10055,7 +10055,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H334" t="n">
         <v>4500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32188987731934</v>
+        <v>3.32189011573792</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10287,7 +10287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H342" t="n">
         <v>8000</v>
@@ -10316,7 +10316,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>3.28167343139648</v>
+        <v>3.28167319297791</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -35958,6 +35958,35 @@
         <v>5500</v>
       </c>
       <c r="I1227" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1228" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>7.88000011444092</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>7.82000017166138</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>4750</v>
+      </c>
+      <c r="I1228" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516021728516</v>
+        <v>2.62516045570374</v>
       </c>
       <c r="H2" t="n">
         <v>1387000</v>
@@ -456,7 +456,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6676459312439</v>
+        <v>2.66764616966248</v>
       </c>
       <c r="H3" t="n">
         <v>383000</v>
@@ -485,7 +485,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621199607849</v>
+        <v>3.25621247291565</v>
       </c>
       <c r="H4" t="n">
         <v>912000</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906972885132</v>
+        <v>4.45906925201416</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -601,7 +601,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H8" t="n">
         <v>594000</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.08488178253174</v>
+        <v>4.0848822593689</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -717,7 +717,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9679479598999</v>
+        <v>3.96794843673706</v>
       </c>
       <c r="H12" t="n">
         <v>65500</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136565208435</v>
+        <v>3.76136517524719</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -833,7 +833,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2953634262085</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H16" t="n">
         <v>208500</v>
@@ -862,7 +862,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H17" t="n">
         <v>60000</v>
@@ -920,7 +920,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H19" t="n">
         <v>93500</v>
@@ -949,7 +949,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2953634262085</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H20" t="n">
         <v>61500</v>
@@ -978,7 +978,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H21" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0926775932312</v>
+        <v>4.09267711639404</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756713867188</v>
+        <v>4.28756666183472</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1094,7 +1094,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.2953634262085</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H25" t="n">
         <v>60000</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283798217773</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1239,7 +1239,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H30" t="n">
         <v>54500</v>
@@ -1268,7 +1268,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047292709351</v>
+        <v>4.10047388076782</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1297,7 +1297,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929016113281</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H32" t="n">
         <v>11500</v>
@@ -1326,7 +1326,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G33" t="n">
-        <v>4.00692653656006</v>
+        <v>4.0069260597229</v>
       </c>
       <c r="H33" t="n">
         <v>16000</v>
@@ -1471,7 +1471,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999247550964</v>
+        <v>3.88999199867249</v>
       </c>
       <c r="H38" t="n">
         <v>32000</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8705039024353</v>
+        <v>3.87050342559814</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1645,7 +1645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.8510148525238</v>
+        <v>3.85101509094238</v>
       </c>
       <c r="H44" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034351348877</v>
+        <v>3.80034375190735</v>
       </c>
       <c r="H46" t="n">
         <v>82500</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015214920044</v>
+        <v>3.96015238761902</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8705039024353</v>
+        <v>3.87050342559814</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628545761108</v>
+        <v>3.7262852191925</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088448524475</v>
+        <v>3.55088520050049</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1877,7 +1877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922198295593</v>
+        <v>3.30922174453735</v>
       </c>
       <c r="H52" t="n">
         <v>36500</v>
@@ -1906,7 +1906,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704829216003</v>
+        <v>3.08704805374146</v>
       </c>
       <c r="H53" t="n">
         <v>44000</v>
@@ -1935,7 +1935,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516440391541</v>
+        <v>3.23516416549683</v>
       </c>
       <c r="H54" t="n">
         <v>7500</v>
@@ -1964,7 +1964,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.35209798812866</v>
+        <v>3.35209822654724</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733833312988</v>
+        <v>3.45733785629272</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2051,7 +2051,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021314620972</v>
+        <v>3.5002133846283</v>
       </c>
       <c r="H58" t="n">
         <v>8000</v>
@@ -2080,7 +2080,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.34430193901062</v>
+        <v>3.34430241584778</v>
       </c>
       <c r="H59" t="n">
         <v>18500</v>
@@ -2196,7 +2196,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123600006104</v>
+        <v>3.46123623847961</v>
       </c>
       <c r="H63" t="n">
         <v>5500</v>
@@ -2225,7 +2225,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529405593872</v>
+        <v>3.53529357910156</v>
       </c>
       <c r="H64" t="n">
         <v>3500</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698753356934</v>
+        <v>3.54698729515076</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2283,7 +2283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.8354229927063</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117547988892</v>
+        <v>3.92117524147034</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133491516113</v>
+        <v>3.99133515357971</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2428,7 +2428,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456171989441</v>
+        <v>3.94456124305725</v>
       </c>
       <c r="H71" t="n">
         <v>13500</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676590919495</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2486,7 +2486,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337919235229</v>
+        <v>3.91337966918945</v>
       </c>
       <c r="H73" t="n">
         <v>6500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2544,7 +2544,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8549120426178</v>
+        <v>3.85491275787354</v>
       </c>
       <c r="H75" t="n">
         <v>11000</v>
@@ -2573,7 +2573,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762765884399</v>
       </c>
       <c r="H76" t="n">
         <v>3500</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.8354229927063</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321856498718</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2776,7 +2776,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999247550964</v>
+        <v>3.88999199867249</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2834,7 +2834,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593489646912</v>
+        <v>3.81593441963196</v>
       </c>
       <c r="H85" t="n">
         <v>2500</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321856498718</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2950,7 +2950,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78865003585815</v>
+        <v>3.788649559021</v>
       </c>
       <c r="H89" t="n">
         <v>6500</v>
@@ -2979,7 +2979,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762765884399</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.8354229927063</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3037,7 +3037,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593489646912</v>
+        <v>3.81593441963196</v>
       </c>
       <c r="H92" t="n">
         <v>6500</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3124,7 +3124,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644536972046</v>
+        <v>3.79644584655762</v>
       </c>
       <c r="H95" t="n">
         <v>7500</v>
@@ -3153,7 +3153,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709494590759</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459735870361</v>
+        <v>3.82459712028503</v>
       </c>
       <c r="H97" t="n">
         <v>2000</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448889732361</v>
+        <v>3.80448913574219</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111682891846</v>
+        <v>3.92111730575562</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720388412476</v>
+        <v>3.9372034072876</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720388412476</v>
+        <v>3.9372034072876</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3356,7 +3356,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709494590759</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.90503025054932</v>
+        <v>3.90503072738647</v>
       </c>
       <c r="H104" t="n">
         <v>17500</v>
@@ -3414,7 +3414,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666253089905</v>
+        <v>3.83666229248047</v>
       </c>
       <c r="H105" t="n">
         <v>10000</v>
@@ -3443,7 +3443,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666253089905</v>
+        <v>3.83666229248047</v>
       </c>
       <c r="H106" t="n">
         <v>3500</v>
@@ -3472,7 +3472,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709494590759</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H107" t="n">
         <v>21000</v>
@@ -3501,7 +3501,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535539627075</v>
+        <v>3.96535468101501</v>
       </c>
       <c r="H108" t="n">
         <v>10500</v>
@@ -3588,7 +3588,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>4.09404802322388</v>
+        <v>4.09404850006104</v>
       </c>
       <c r="H111" t="n">
         <v>4000</v>
@@ -3675,7 +3675,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274160385132</v>
+        <v>4.22274112701416</v>
       </c>
       <c r="H114" t="n">
         <v>6000</v>
@@ -3704,7 +3704,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G115" t="n">
-        <v>4.23078489303589</v>
+        <v>4.23078536987305</v>
       </c>
       <c r="H115" t="n">
         <v>28000</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687921524048</v>
+        <v>3.8768789768219</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -3994,7 +3994,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.80046701431274</v>
+        <v>3.80046725273132</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.7160120010376</v>
+        <v>3.71601223945618</v>
       </c>
       <c r="H126" t="n">
         <v>9000</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949253082275</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4110,7 +4110,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>3.60742783546448</v>
+        <v>3.6074275970459</v>
       </c>
       <c r="H129" t="n">
         <v>4500</v>
@@ -4168,7 +4168,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123303413391</v>
       </c>
       <c r="H131" t="n">
         <v>3000</v>
@@ -4197,7 +4197,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>3.7320990562439</v>
+        <v>3.73209881782532</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4255,7 +4255,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970969200134</v>
+        <v>3.65970945358276</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775250434875</v>
+        <v>3.66775226593018</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4342,7 +4342,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688600540161</v>
+        <v>3.50688624382019</v>
       </c>
       <c r="H137" t="n">
         <v>500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482131004333</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H139" t="n">
         <v>500</v>
@@ -4429,7 +4429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123303413391</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731961250305</v>
+        <v>3.58731937408447</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731961250305</v>
+        <v>3.58731937408447</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025831222534</v>
+        <v>3.39025807380676</v>
       </c>
       <c r="H144" t="n">
         <v>4500</v>
@@ -4574,7 +4574,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G145" t="n">
-        <v>3.39427947998047</v>
+        <v>3.39427995681763</v>
       </c>
       <c r="H145" t="n">
         <v>500</v>
@@ -4603,7 +4603,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G146" t="n">
-        <v>3.39427947998047</v>
+        <v>3.39427995681763</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482131004333</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4690,7 +4690,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123303413391</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905940055847</v>
+        <v>3.53905963897705</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905940055847</v>
+        <v>3.53905963897705</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.5269947052002</v>
+        <v>3.52699446678162</v>
       </c>
       <c r="H154" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>3.57927584648132</v>
+        <v>3.5792760848999</v>
       </c>
       <c r="H155" t="n">
         <v>2500</v>
@@ -4893,7 +4893,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H156" t="n">
         <v>9500</v>
@@ -4922,7 +4922,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112433433533</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112433433533</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677778244019</v>
+        <v>3.48677825927734</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5067,7 +5067,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069144248962</v>
+        <v>3.47069120407104</v>
       </c>
       <c r="H162" t="n">
         <v>5000</v>
@@ -5096,7 +5096,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.4023232460022</v>
+        <v>3.40232348442078</v>
       </c>
       <c r="H163" t="n">
         <v>5500</v>
@@ -5154,7 +5154,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069144248962</v>
+        <v>3.47069120407104</v>
       </c>
       <c r="H165" t="n">
         <v>1500</v>
@@ -5270,7 +5270,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862627029419</v>
+        <v>3.45862674713135</v>
       </c>
       <c r="H169" t="n">
         <v>10500</v>
@@ -5299,7 +5299,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G170" t="n">
-        <v>3.40634489059448</v>
+        <v>3.4063446521759</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G171" t="n">
-        <v>3.40634489059448</v>
+        <v>3.4063446521759</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>3.34601950645447</v>
+        <v>3.34601974487305</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5386,7 +5386,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H173" t="n">
         <v>1500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732664108276</v>
+        <v>3.21732687950134</v>
       </c>
       <c r="H180" t="n">
         <v>2000</v>
@@ -5618,7 +5618,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711043357849</v>
+        <v>3.17711019515991</v>
       </c>
       <c r="H181" t="n">
         <v>2500</v>
@@ -5647,7 +5647,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711043357849</v>
+        <v>3.17711019515991</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.13689374923706</v>
+        <v>3.13689351081848</v>
       </c>
       <c r="H184" t="n">
         <v>13000</v>
@@ -5995,7 +5995,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>3.03233027458191</v>
+        <v>3.03233051300049</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211382865906</v>
+        <v>2.99211406707764</v>
       </c>
       <c r="H195" t="n">
         <v>8500</v>
@@ -6082,7 +6082,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>3.03233027458191</v>
+        <v>3.03233051300049</v>
       </c>
       <c r="H197" t="n">
         <v>107500</v>
@@ -6169,7 +6169,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059799194336</v>
+        <v>2.71059775352478</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6517,7 +6517,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.74679279327393</v>
+        <v>2.74679255485535</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6604,7 +6604,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H215" t="n">
         <v>5500</v>
@@ -6691,7 +6691,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>2.84733438491821</v>
+        <v>2.84733414649963</v>
       </c>
       <c r="H221" t="n">
         <v>41000</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929061889648</v>
+        <v>2.83929085731506</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -6836,7 +6836,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331274032593</v>
+        <v>2.84331250190735</v>
       </c>
       <c r="H223" t="n">
         <v>1000</v>
@@ -6865,7 +6865,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.84733438491821</v>
+        <v>2.84733414649963</v>
       </c>
       <c r="H224" t="n">
         <v>7500</v>
@@ -6981,7 +6981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994091033936</v>
+        <v>2.95994067192078</v>
       </c>
       <c r="H228" t="n">
         <v>5000</v>
@@ -7010,7 +7010,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581104278564</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H229" t="n">
         <v>1500</v>
@@ -7097,7 +7097,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G232" t="n">
-        <v>2.8996160030365</v>
+        <v>2.89961576461792</v>
       </c>
       <c r="H232" t="n">
         <v>4000</v>
@@ -7155,7 +7155,7 @@
         <v>3.625</v>
       </c>
       <c r="G234" t="n">
-        <v>2.91570234298706</v>
+        <v>2.91570258140564</v>
       </c>
       <c r="H234" t="n">
         <v>1500</v>
@@ -7184,7 +7184,7 @@
         <v>3.625</v>
       </c>
       <c r="G235" t="n">
-        <v>2.91570234298706</v>
+        <v>2.91570258140564</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.91168069839478</v>
+        <v>2.9116804599762</v>
       </c>
       <c r="H236" t="n">
         <v>2500</v>
@@ -7329,7 +7329,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H240" t="n">
         <v>2000</v>
@@ -7358,7 +7358,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G245" t="n">
-        <v>2.89157223701477</v>
+        <v>2.89157247543335</v>
       </c>
       <c r="H245" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950730323792</v>
+        <v>2.87950754165649</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7561,7 +7561,7 @@
         <v>3.625</v>
       </c>
       <c r="G248" t="n">
-        <v>2.91570234298706</v>
+        <v>2.91570258140564</v>
       </c>
       <c r="H248" t="n">
         <v>1500</v>
@@ -7677,7 +7677,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559388160706</v>
+        <v>2.89559412002563</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7706,7 +7706,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.8996160030365</v>
+        <v>2.89961576461792</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.94787549972534</v>
+        <v>2.9478759765625</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7764,7 +7764,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581104278564</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374563217163</v>
+        <v>2.92374587059021</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559388160706</v>
+        <v>2.89559412002563</v>
       </c>
       <c r="H257" t="n">
         <v>5000</v>
@@ -7909,7 +7909,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H260" t="n">
         <v>2000</v>
@@ -7938,7 +7938,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.91168069839478</v>
+        <v>2.9116804599762</v>
       </c>
       <c r="H261" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H262" t="n">
         <v>2000</v>
@@ -7996,7 +7996,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8112,7 +8112,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417876243591</v>
+        <v>3.00417900085449</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8141,7 +8141,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H268" t="n">
         <v>2000</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.94787549972534</v>
+        <v>2.9478759765625</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8228,7 +8228,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.94787549972534</v>
+        <v>2.9478759765625</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8315,7 +8315,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H274" t="n">
         <v>7000</v>
@@ -8373,7 +8373,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581104278564</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H276" t="n">
         <v>7000</v>
@@ -8431,7 +8431,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.9317889213562</v>
+        <v>2.93178915977478</v>
       </c>
       <c r="H278" t="n">
         <v>1500</v>
@@ -8460,7 +8460,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H279" t="n">
         <v>5500</v>
@@ -8489,7 +8489,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H280" t="n">
         <v>15500</v>
@@ -8634,7 +8634,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H285" t="n">
         <v>37500</v>
@@ -8663,7 +8663,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H286" t="n">
         <v>33000</v>
@@ -8692,7 +8692,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H287" t="n">
         <v>5500</v>
@@ -8721,7 +8721,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>3.03233027458191</v>
+        <v>3.03233051300049</v>
       </c>
       <c r="H288" t="n">
         <v>13500</v>
@@ -8808,7 +8808,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047451972961</v>
+        <v>3.43047475814819</v>
       </c>
       <c r="H291" t="n">
         <v>70000</v>
@@ -8837,7 +8837,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5269947052002</v>
+        <v>3.52699446678162</v>
       </c>
       <c r="H292" t="n">
         <v>17000</v>
@@ -8895,7 +8895,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G294" t="n">
-        <v>3.40634489059448</v>
+        <v>3.4063446521759</v>
       </c>
       <c r="H294" t="n">
         <v>6000</v>
@@ -8924,7 +8924,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>3.38623666763306</v>
+        <v>3.38623642921448</v>
       </c>
       <c r="H295" t="n">
         <v>47000</v>
@@ -8953,7 +8953,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612820625305</v>
+        <v>3.36612844467163</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9127,7 +9127,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.37417149543762</v>
+        <v>3.3741717338562</v>
       </c>
       <c r="H302" t="n">
         <v>7000</v>
@@ -9214,7 +9214,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.37417149543762</v>
+        <v>3.3741717338562</v>
       </c>
       <c r="H305" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>3.34601950645447</v>
+        <v>3.34601974487305</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9359,7 +9359,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H310" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.45058298110962</v>
+        <v>3.4505832195282</v>
       </c>
       <c r="H314" t="n">
         <v>14000</v>
@@ -9504,7 +9504,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862627029419</v>
+        <v>3.45862674713135</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G316" t="n">
-        <v>3.20526146888733</v>
+        <v>3.20526170730591</v>
       </c>
       <c r="H316" t="n">
         <v>18000</v>
@@ -9562,7 +9562,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G317" t="n">
-        <v>3.26558685302734</v>
+        <v>3.26558661460876</v>
       </c>
       <c r="H317" t="n">
         <v>17500</v>
@@ -9649,7 +9649,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>3.39427947998047</v>
+        <v>3.39427995681763</v>
       </c>
       <c r="H320" t="n">
         <v>14500</v>
@@ -9678,7 +9678,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H321" t="n">
         <v>8000</v>
@@ -9823,7 +9823,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G326" t="n">
-        <v>3.26558685302734</v>
+        <v>3.26558661460876</v>
       </c>
       <c r="H326" t="n">
         <v>500</v>
@@ -9997,7 +9997,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>3.28167319297791</v>
+        <v>3.28167343139648</v>
       </c>
       <c r="H332" t="n">
         <v>4500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189011573792</v>
+        <v>3.32189035415649</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10229,7 +10229,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.3058032989502</v>
+        <v>3.30580353736877</v>
       </c>
       <c r="H340" t="n">
         <v>1000</v>
@@ -10258,7 +10258,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>3.26558685302734</v>
+        <v>3.26558661460876</v>
       </c>
       <c r="H341" t="n">
         <v>2000</v>
@@ -10374,7 +10374,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>3.28167319297791</v>
+        <v>3.28167343139648</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732664108276</v>
+        <v>3.21732687950134</v>
       </c>
       <c r="H347" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732664108276</v>
+        <v>3.21732687950134</v>
       </c>
       <c r="H350" t="n">
         <v>3500</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H352" t="n">
         <v>500</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.35138201713562</v>
+        <v>3.3513822555542</v>
       </c>
       <c r="H359" t="n">
         <v>34500</v>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.35138201713562</v>
+        <v>3.3513822555542</v>
       </c>
       <c r="H361" t="n">
         <v>3500</v>
@@ -10867,7 +10867,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H362" t="n">
         <v>16500</v>
@@ -10896,7 +10896,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H369" t="n">
         <v>9000</v>
@@ -11099,7 +11099,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192360877991</v>
+        <v>3.45192384719849</v>
       </c>
       <c r="H370" t="n">
         <v>10500</v>
@@ -11128,7 +11128,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H372" t="n">
         <v>13500</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H373" t="n">
         <v>10500</v>
@@ -11273,7 +11273,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.52732992172241</v>
+        <v>3.52732968330383</v>
       </c>
       <c r="H376" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H377" t="n">
         <v>4000</v>
@@ -11476,7 +11476,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003412246704</v>
+        <v>3.72003436088562</v>
       </c>
       <c r="H383" t="n">
         <v>33500</v>
@@ -11505,7 +11505,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003412246704</v>
+        <v>3.72003436088562</v>
       </c>
       <c r="H384" t="n">
         <v>14000</v>
@@ -11679,7 +11679,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597922325134</v>
+        <v>3.58597898483276</v>
       </c>
       <c r="H390" t="n">
         <v>24500</v>
@@ -11737,7 +11737,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H392" t="n">
         <v>15500</v>
@@ -11766,7 +11766,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>3.46030211448669</v>
+        <v>3.46030235290527</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11795,7 +11795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H394" t="n">
         <v>16500</v>
@@ -11824,7 +11824,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>3.52732992172241</v>
+        <v>3.52732968330383</v>
       </c>
       <c r="H395" t="n">
         <v>10500</v>
@@ -11853,7 +11853,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>3.49381613731384</v>
+        <v>3.49381589889526</v>
       </c>
       <c r="H396" t="n">
         <v>5000</v>
@@ -12201,7 +12201,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>3.52732992172241</v>
+        <v>3.52732968330383</v>
       </c>
       <c r="H408" t="n">
         <v>5000</v>
@@ -12288,7 +12288,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354510307312</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H411" t="n">
         <v>14500</v>
@@ -12317,7 +12317,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H412" t="n">
         <v>27500</v>
@@ -12346,7 +12346,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354510307312</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H413" t="n">
         <v>8500</v>
@@ -12404,7 +12404,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G415" t="n">
-        <v>3.37651753425598</v>
+        <v>3.37651777267456</v>
       </c>
       <c r="H415" t="n">
         <v>8500</v>
@@ -12462,7 +12462,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H417" t="n">
         <v>10500</v>
@@ -12520,7 +12520,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H419" t="n">
         <v>9000</v>
@@ -12578,7 +12578,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435468673706</v>
+        <v>3.28435444831848</v>
       </c>
       <c r="H421" t="n">
         <v>28500</v>
@@ -12607,7 +12607,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435468673706</v>
+        <v>3.28435444831848</v>
       </c>
       <c r="H422" t="n">
         <v>11500</v>
@@ -12636,7 +12636,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H423" t="n">
         <v>57000</v>
@@ -12665,7 +12665,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G424" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H424" t="n">
         <v>9500</v>
@@ -12694,7 +12694,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H425" t="n">
         <v>9000</v>
@@ -12839,7 +12839,7 @@
         <v>3.75</v>
       </c>
       <c r="G430" t="n">
-        <v>3.14192056655884</v>
+        <v>3.14192080497742</v>
       </c>
       <c r="H430" t="n">
         <v>12500</v>
@@ -12897,7 +12897,7 @@
         <v>3.75</v>
       </c>
       <c r="G432" t="n">
-        <v>3.14192056655884</v>
+        <v>3.14192080497742</v>
       </c>
       <c r="H432" t="n">
         <v>13500</v>
@@ -12955,7 +12955,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H434" t="n">
         <v>19000</v>
@@ -12984,7 +12984,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>3.10002875328064</v>
+        <v>3.10002851486206</v>
       </c>
       <c r="H435" t="n">
         <v>2000</v>
@@ -13042,7 +13042,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13129,7 +13129,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>3.10002875328064</v>
+        <v>3.10002851486206</v>
       </c>
       <c r="H446" t="n">
         <v>5000</v>
@@ -13361,7 +13361,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H448" t="n">
         <v>43500</v>
@@ -13477,7 +13477,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G452" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H452" t="n">
         <v>55500</v>
@@ -13738,7 +13738,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H461" t="n">
         <v>20500</v>
@@ -13767,7 +13767,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H462" t="n">
         <v>12000</v>
@@ -13970,7 +13970,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H469" t="n">
         <v>19500</v>
@@ -13999,7 +13999,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H470" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H486" t="n">
         <v>26000</v>
@@ -14521,7 +14521,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H488" t="n">
         <v>9500</v>
@@ -14579,7 +14579,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.81516075134277</v>
+        <v>2.81516098976135</v>
       </c>
       <c r="H490" t="n">
         <v>13500</v>
@@ -14695,7 +14695,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H494" t="n">
         <v>5500</v>
@@ -14840,7 +14840,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H499" t="n">
         <v>14000</v>
@@ -14869,7 +14869,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G500" t="n">
-        <v>2.81516075134277</v>
+        <v>2.81516098976135</v>
       </c>
       <c r="H500" t="n">
         <v>23500</v>
@@ -14898,7 +14898,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H501" t="n">
         <v>21500</v>
@@ -14956,7 +14956,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H503" t="n">
         <v>72000</v>
@@ -15014,7 +15014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H505" t="n">
         <v>18000</v>
@@ -15304,7 +15304,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G515" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H515" t="n">
         <v>32500</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H516" t="n">
         <v>7500</v>
@@ -15362,7 +15362,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H517" t="n">
         <v>39500</v>
@@ -15391,7 +15391,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H518" t="n">
         <v>16500</v>
@@ -15420,7 +15420,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H519" t="n">
         <v>19000</v>
@@ -15710,7 +15710,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G529" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H529" t="n">
         <v>28000</v>
@@ -15768,7 +15768,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H531" t="n">
         <v>58000</v>
@@ -15855,7 +15855,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H534" t="n">
         <v>10000</v>
@@ -15884,7 +15884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H535" t="n">
         <v>24500</v>
@@ -15913,7 +15913,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H536" t="n">
         <v>1500</v>
@@ -15942,7 +15942,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H537" t="n">
         <v>21500</v>
@@ -16029,7 +16029,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H540" t="n">
         <v>16500</v>
@@ -16290,7 +16290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H549" t="n">
         <v>1500</v>
@@ -16377,7 +16377,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H552" t="n">
         <v>11000</v>
@@ -16464,7 +16464,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H555" t="n">
         <v>15500</v>
@@ -16493,7 +16493,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H556" t="n">
         <v>500</v>
@@ -16522,7 +16522,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H557" t="n">
         <v>12500</v>
@@ -16725,7 +16725,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H564" t="n">
         <v>10000</v>
@@ -16783,7 +16783,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H566" t="n">
         <v>7500</v>
@@ -16841,7 +16841,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H568" t="n">
         <v>1500</v>
@@ -16986,7 +16986,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732383728027</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H573" t="n">
         <v>8000</v>
@@ -17102,7 +17102,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H577" t="n">
         <v>25000</v>
@@ -17160,7 +17160,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H579" t="n">
         <v>18000</v>
@@ -17247,7 +17247,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H582" t="n">
         <v>42500</v>
@@ -17276,7 +17276,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G583" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H583" t="n">
         <v>7500</v>
@@ -17305,7 +17305,7 @@
         <v>3.75</v>
       </c>
       <c r="G584" t="n">
-        <v>3.14192056655884</v>
+        <v>3.14192080497742</v>
       </c>
       <c r="H584" t="n">
         <v>20500</v>
@@ -17363,7 +17363,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H586" t="n">
         <v>9000</v>
@@ -17392,7 +17392,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G587" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H587" t="n">
         <v>13500</v>
@@ -17450,7 +17450,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H589" t="n">
         <v>20000</v>
@@ -17508,7 +17508,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H591" t="n">
         <v>7000</v>
@@ -17566,7 +17566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.1670560836792</v>
+        <v>3.16705632209778</v>
       </c>
       <c r="H593" t="n">
         <v>20500</v>
@@ -17740,7 +17740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H599" t="n">
         <v>10000</v>
@@ -17769,7 +17769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H600" t="n">
         <v>29000</v>
@@ -17798,7 +17798,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H601" t="n">
         <v>13000</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H602" t="n">
         <v>20500</v>
@@ -17856,7 +17856,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>3.32624673843384</v>
+        <v>3.32624697685242</v>
       </c>
       <c r="H603" t="n">
         <v>21500</v>
@@ -18001,7 +18001,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705912590027</v>
+        <v>3.47705888748169</v>
       </c>
       <c r="H608" t="n">
         <v>67000</v>
@@ -35987,6 +35987,35 @@
         <v>4750</v>
       </c>
       <c r="I1228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1229" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1229" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516045570374</v>
+        <v>2.62516021728516</v>
       </c>
       <c r="H2" t="n">
         <v>1387000</v>
@@ -485,7 +485,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621247291565</v>
+        <v>3.25621223449707</v>
       </c>
       <c r="H4" t="n">
         <v>912000</v>
@@ -514,7 +514,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805215835571</v>
+        <v>4.20805168151855</v>
       </c>
       <c r="H5" t="n">
         <v>1121500</v>
@@ -543,7 +543,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>5.30099201202393</v>
+        <v>5.30099153518677</v>
       </c>
       <c r="H6" t="n">
         <v>635500</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906925201416</v>
+        <v>4.459068775177</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0848822593689</v>
+        <v>4.08488178253174</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136517524719</v>
+        <v>3.76136493682861</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -775,7 +775,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574400901794</v>
+        <v>3.97574353218079</v>
       </c>
       <c r="H14" t="n">
         <v>84000</v>
@@ -833,7 +833,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H16" t="n">
         <v>208500</v>
@@ -949,7 +949,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H20" t="n">
         <v>61500</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267711639404</v>
+        <v>4.0926775932312</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1094,7 +1094,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H25" t="n">
         <v>60000</v>
@@ -1123,7 +1123,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858903884888</v>
+        <v>4.24858856201172</v>
       </c>
       <c r="H26" t="n">
         <v>26000</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283750534058</v>
+        <v>4.16283798217773</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1268,7 +1268,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G31" t="n">
-        <v>4.10047388076782</v>
+        <v>4.10047340393066</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1471,7 +1471,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999199867249</v>
+        <v>3.88999247550964</v>
       </c>
       <c r="H38" t="n">
         <v>32000</v>
@@ -1558,7 +1558,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219738006592</v>
+        <v>3.88219690322876</v>
       </c>
       <c r="H41" t="n">
         <v>10500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050342559814</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1645,7 +1645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101509094238</v>
+        <v>3.8510148525238</v>
       </c>
       <c r="H44" t="n">
         <v>25000</v>
@@ -1674,7 +1674,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H45" t="n">
         <v>3000</v>
@@ -1703,7 +1703,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034375190735</v>
+        <v>3.80034351348877</v>
       </c>
       <c r="H46" t="n">
         <v>82500</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015238761902</v>
+        <v>3.96015286445618</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050342559814</v>
+        <v>3.8705039024353</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.7262852191925</v>
+        <v>3.72628545761108</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088520050049</v>
+        <v>3.55088496208191</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733785629272</v>
+        <v>3.4573380947113</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2196,7 +2196,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123623847961</v>
+        <v>3.46123600006104</v>
       </c>
       <c r="H63" t="n">
         <v>5500</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698729515076</v>
+        <v>3.54698705673218</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2283,7 +2283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542394638062</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2486,7 +2486,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337966918945</v>
+        <v>3.91337919235229</v>
       </c>
       <c r="H73" t="n">
         <v>6500</v>
@@ -2573,7 +2573,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762765884399</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H76" t="n">
         <v>3500</v>
@@ -2602,7 +2602,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219738006592</v>
+        <v>3.88219690322876</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542394638062</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2718,7 +2718,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219738006592</v>
+        <v>3.88219690322876</v>
       </c>
       <c r="H81" t="n">
         <v>1500</v>
@@ -2747,7 +2747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999199867249</v>
+        <v>3.88999247550964</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2863,7 +2863,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711694717407</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H86" t="n">
         <v>1000</v>
@@ -2950,7 +2950,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.788649559021</v>
+        <v>3.78864979743958</v>
       </c>
       <c r="H89" t="n">
         <v>6500</v>
@@ -2979,7 +2979,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762765884399</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542394638062</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448913574219</v>
+        <v>3.80448937416077</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111730575562</v>
+        <v>3.92111706733704</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3385,7 +3385,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.90503072738647</v>
+        <v>3.9050304889679</v>
       </c>
       <c r="H104" t="n">
         <v>17500</v>
@@ -3530,7 +3530,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>4.08600473403931</v>
+        <v>4.08600521087646</v>
       </c>
       <c r="H109" t="n">
         <v>17000</v>
@@ -3617,7 +3617,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469831466675</v>
+        <v>4.21469783782959</v>
       </c>
       <c r="H112" t="n">
         <v>17000</v>
@@ -3675,7 +3675,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274112701416</v>
+        <v>4.22274160385132</v>
       </c>
       <c r="H114" t="n">
         <v>6000</v>
@@ -3704,7 +3704,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G115" t="n">
-        <v>4.23078536987305</v>
+        <v>4.23078489303589</v>
       </c>
       <c r="H115" t="n">
         <v>28000</v>
@@ -3762,7 +3762,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209178924561</v>
+        <v>4.10209131240845</v>
       </c>
       <c r="H117" t="n">
         <v>11000</v>
@@ -3820,7 +3820,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383157730103</v>
+        <v>4.05383205413818</v>
       </c>
       <c r="H119" t="n">
         <v>3500</v>
@@ -3965,7 +3965,7 @@
         <v>4.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82057547569275</v>
+        <v>3.82057571411133</v>
       </c>
       <c r="H124" t="n">
         <v>4500</v>
@@ -3994,7 +3994,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.80046725273132</v>
+        <v>3.8004674911499</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949253082275</v>
+        <v>3.61949229240417</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4110,7 +4110,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>3.6074275970459</v>
+        <v>3.60742783546448</v>
       </c>
       <c r="H129" t="n">
         <v>4500</v>
@@ -4139,7 +4139,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340595245361</v>
+        <v>3.60340619087219</v>
       </c>
       <c r="H130" t="n">
         <v>1500</v>
@@ -4168,7 +4168,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123303413391</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H131" t="n">
         <v>3000</v>
@@ -4226,7 +4226,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992566108704</v>
+        <v>3.69992589950562</v>
       </c>
       <c r="H133" t="n">
         <v>5000</v>
@@ -4255,7 +4255,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970945358276</v>
+        <v>3.65970921516418</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775226593018</v>
+        <v>3.66775250434875</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4342,7 +4342,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688624382019</v>
+        <v>3.50688600540161</v>
       </c>
       <c r="H137" t="n">
         <v>500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4429,7 +4429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123303413391</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731913566589</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731913566589</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025807380676</v>
+        <v>3.39025855064392</v>
       </c>
       <c r="H144" t="n">
         <v>4500</v>
@@ -4574,7 +4574,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G145" t="n">
-        <v>3.39427995681763</v>
+        <v>3.39427971839905</v>
       </c>
       <c r="H145" t="n">
         <v>500</v>
@@ -4603,7 +4603,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G146" t="n">
-        <v>3.39427995681763</v>
+        <v>3.39427971839905</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482131004333</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4690,7 +4690,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123303413391</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H154" t="n">
         <v>4000</v>
@@ -4922,7 +4922,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112433433533</v>
+        <v>3.55112481117249</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112433433533</v>
+        <v>3.55112481117249</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677825927734</v>
+        <v>3.48677802085876</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253993034363</v>
+        <v>3.44253969192505</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5067,7 +5067,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069120407104</v>
+        <v>3.47069096565247</v>
       </c>
       <c r="H162" t="n">
         <v>5000</v>
@@ -5096,7 +5096,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40232348442078</v>
+        <v>3.4023232460022</v>
       </c>
       <c r="H163" t="n">
         <v>5500</v>
@@ -5154,7 +5154,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069120407104</v>
+        <v>3.47069096565247</v>
       </c>
       <c r="H165" t="n">
         <v>1500</v>
@@ -5183,7 +5183,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253993034363</v>
+        <v>3.44253969192505</v>
       </c>
       <c r="H166" t="n">
         <v>500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884271621704</v>
+        <v>3.49884295463562</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5299,7 +5299,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G170" t="n">
-        <v>3.4063446521759</v>
+        <v>3.40634489059448</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G171" t="n">
-        <v>3.4063446521759</v>
+        <v>3.40634489059448</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>3.34601974487305</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993292808533</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993292808533</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.31384658813477</v>
+        <v>3.31384634971619</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.2334132194519</v>
+        <v>3.23341369628906</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5618,7 +5618,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H181" t="n">
         <v>2500</v>
@@ -5647,7 +5647,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.13689351081848</v>
+        <v>3.13689374923706</v>
       </c>
       <c r="H184" t="n">
         <v>13000</v>
@@ -5763,7 +5763,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>3.11276364326477</v>
+        <v>3.11276340484619</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080693244934</v>
+        <v>3.12080717086792</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5879,7 +5879,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222229003906</v>
+        <v>3.01222205162048</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>3.04841709136963</v>
+        <v>3.04841685295105</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.11276364326477</v>
+        <v>3.11276340484619</v>
       </c>
       <c r="H196" t="n">
         <v>19000</v>
@@ -6111,7 +6111,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6343,7 +6343,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>2.87146425247192</v>
+        <v>2.87146401405334</v>
       </c>
       <c r="H206" t="n">
         <v>5500</v>
@@ -6459,7 +6459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059775352478</v>
+        <v>2.71059799194336</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6517,7 +6517,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.74679255485535</v>
+        <v>2.7467930316925</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.73472785949707</v>
+        <v>2.73472762107849</v>
       </c>
       <c r="H213" t="n">
         <v>10000</v>
@@ -6575,7 +6575,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896595001221</v>
+        <v>2.77896618843079</v>
       </c>
       <c r="H214" t="n">
         <v>9000</v>
@@ -6604,7 +6604,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H215" t="n">
         <v>5500</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H216" t="n">
         <v>7500</v>
@@ -6691,7 +6691,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6894,7 +6894,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H225" t="n">
         <v>4500</v>
@@ -6923,7 +6923,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G226" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H226" t="n">
         <v>2500</v>
@@ -6952,7 +6952,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G227" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H227" t="n">
         <v>3000</v>
@@ -7039,7 +7039,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G230" t="n">
-        <v>2.90765905380249</v>
+        <v>2.90765881538391</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7271,7 +7271,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G238" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H238" t="n">
         <v>1500</v>
@@ -7300,7 +7300,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H242" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950754165649</v>
+        <v>2.87950730323792</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7793,7 +7793,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374587059021</v>
+        <v>2.92374563217163</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H259" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H265" t="n">
         <v>500</v>
@@ -8083,7 +8083,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8112,7 +8112,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417900085449</v>
+        <v>3.00417876243591</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8228,7 +8228,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8402,7 +8402,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>2.91972422599792</v>
+        <v>2.9197244644165</v>
       </c>
       <c r="H277" t="n">
         <v>4000</v>
@@ -8460,7 +8460,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H279" t="n">
         <v>5500</v>
@@ -8489,7 +8489,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H280" t="n">
         <v>15500</v>
@@ -8518,7 +8518,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H281" t="n">
         <v>13500</v>
@@ -8547,7 +8547,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>2.95189738273621</v>
+        <v>2.95189762115479</v>
       </c>
       <c r="H282" t="n">
         <v>15000</v>
@@ -8692,7 +8692,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H287" t="n">
         <v>5500</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917512893677</v>
+        <v>3.18917489051819</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8837,7 +8837,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H292" t="n">
         <v>17000</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656109809875</v>
+        <v>3.44656133651733</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8895,7 +8895,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G294" t="n">
-        <v>3.4063446521759</v>
+        <v>3.40634489059448</v>
       </c>
       <c r="H294" t="n">
         <v>6000</v>
@@ -8953,7 +8953,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612844467163</v>
+        <v>3.36612820625305</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993292808533</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993292808533</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>3.34601974487305</v>
+        <v>3.34601950645447</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9417,7 +9417,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253993034363</v>
+        <v>3.44253969192505</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547088623047</v>
+        <v>3.61547112464905</v>
       </c>
       <c r="H313" t="n">
         <v>9000</v>
@@ -9649,7 +9649,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>3.39427995681763</v>
+        <v>3.39427971839905</v>
       </c>
       <c r="H320" t="n">
         <v>14500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189035415649</v>
+        <v>3.32189011573792</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993292808533</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10200,7 +10200,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>3.31384658813477</v>
+        <v>3.31384634971619</v>
       </c>
       <c r="H339" t="n">
         <v>8000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145674705505</v>
+        <v>3.24145698547363</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.24950003623962</v>
+        <v>3.2495002746582</v>
       </c>
       <c r="H346" t="n">
         <v>67500</v>
@@ -10461,7 +10461,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.24950003623962</v>
+        <v>3.2495002746582</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H352" t="n">
         <v>500</v>
@@ -10664,7 +10664,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>3.29273319244385</v>
+        <v>3.29273295402527</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G356" t="n">
-        <v>3.29273319244385</v>
+        <v>3.29273295402527</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H359" t="n">
         <v>34500</v>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H361" t="n">
         <v>3500</v>
@@ -10867,7 +10867,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H362" t="n">
         <v>16500</v>
@@ -10896,7 +10896,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H369" t="n">
         <v>9000</v>
@@ -11099,7 +11099,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192384719849</v>
+        <v>3.45192360877991</v>
       </c>
       <c r="H370" t="n">
         <v>10500</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H373" t="n">
         <v>10500</v>
@@ -11331,7 +11331,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246472358704</v>
+        <v>3.55246520042419</v>
       </c>
       <c r="H378" t="n">
         <v>27000</v>
@@ -11476,7 +11476,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H383" t="n">
         <v>33500</v>
@@ -11505,7 +11505,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H384" t="n">
         <v>14000</v>
@@ -11650,7 +11650,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G389" t="n">
-        <v>3.61949300765991</v>
+        <v>3.61949276924133</v>
       </c>
       <c r="H389" t="n">
         <v>59500</v>
@@ -11679,7 +11679,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597898483276</v>
+        <v>3.58597874641418</v>
       </c>
       <c r="H390" t="n">
         <v>24500</v>
@@ -11708,7 +11708,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273599624634</v>
+        <v>3.60273575782776</v>
       </c>
       <c r="H391" t="n">
         <v>7000</v>
@@ -11737,7 +11737,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H392" t="n">
         <v>15500</v>
@@ -11795,7 +11795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H394" t="n">
         <v>16500</v>
@@ -11998,7 +11998,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.62787127494812</v>
+        <v>3.62787103652954</v>
       </c>
       <c r="H401" t="n">
         <v>8000</v>
@@ -12027,7 +12027,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G402" t="n">
-        <v>3.61949300765991</v>
+        <v>3.61949276924133</v>
       </c>
       <c r="H402" t="n">
         <v>7000</v>
@@ -12056,7 +12056,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.62787127494812</v>
+        <v>3.62787103652954</v>
       </c>
       <c r="H403" t="n">
         <v>8000</v>
@@ -12085,7 +12085,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>3.59435725212097</v>
+        <v>3.59435749053955</v>
       </c>
       <c r="H404" t="n">
         <v>34000</v>
@@ -12114,7 +12114,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273599624634</v>
+        <v>3.60273575782776</v>
       </c>
       <c r="H405" t="n">
         <v>15000</v>
@@ -12433,7 +12433,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>3.36813902854919</v>
+        <v>3.36813926696777</v>
       </c>
       <c r="H416" t="n">
         <v>6000</v>
@@ -12462,7 +12462,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H417" t="n">
         <v>10500</v>
@@ -12520,7 +12520,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H419" t="n">
         <v>9000</v>
@@ -12549,7 +12549,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G420" t="n">
-        <v>3.29273319244385</v>
+        <v>3.29273295402527</v>
       </c>
       <c r="H420" t="n">
         <v>45000</v>
@@ -12694,7 +12694,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840702056885</v>
       </c>
       <c r="H425" t="n">
         <v>9000</v>
@@ -13042,7 +13042,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840702056885</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13071,7 +13071,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G438" t="n">
-        <v>3.04975771903992</v>
+        <v>3.0497579574585</v>
       </c>
       <c r="H438" t="n">
         <v>8500</v>
@@ -13129,7 +13129,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840702056885</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13158,7 +13158,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H441" t="n">
         <v>18000</v>
@@ -13332,7 +13332,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H447" t="n">
         <v>12000</v>
@@ -13361,7 +13361,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840702056885</v>
       </c>
       <c r="H448" t="n">
         <v>43500</v>
@@ -13535,7 +13535,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05813646316528</v>
+        <v>3.0581362247467</v>
       </c>
       <c r="H454" t="n">
         <v>22000</v>
@@ -13564,7 +13564,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.05813646316528</v>
+        <v>3.0581362247467</v>
       </c>
       <c r="H455" t="n">
         <v>3500</v>
@@ -13738,7 +13738,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H461" t="n">
         <v>20500</v>
@@ -13767,7 +13767,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H462" t="n">
         <v>12000</v>
@@ -13796,7 +13796,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H463" t="n">
         <v>26000</v>
@@ -13912,7 +13912,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H467" t="n">
         <v>28000</v>
@@ -14086,7 +14086,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H473" t="n">
         <v>20000</v>
@@ -14144,7 +14144,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H475" t="n">
         <v>7500</v>
@@ -14173,7 +14173,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H476" t="n">
         <v>18000</v>
@@ -14289,7 +14289,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353949546814</v>
+        <v>2.82353925704956</v>
       </c>
       <c r="H480" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353949546814</v>
+        <v>2.82353925704956</v>
       </c>
       <c r="H481" t="n">
         <v>1000</v>
@@ -14347,7 +14347,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029674530029</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029674530029</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H486" t="n">
         <v>26000</v>
@@ -14521,7 +14521,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H488" t="n">
         <v>9500</v>
@@ -14637,7 +14637,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353949546814</v>
+        <v>2.82353925704956</v>
       </c>
       <c r="H492" t="n">
         <v>13500</v>
@@ -14695,7 +14695,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H494" t="n">
         <v>5500</v>
@@ -14840,7 +14840,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H499" t="n">
         <v>14000</v>
@@ -14898,7 +14898,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029674530029</v>
+        <v>2.84029626846313</v>
       </c>
       <c r="H501" t="n">
         <v>21500</v>
@@ -14927,7 +14927,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>3.07489323616028</v>
+        <v>3.0748929977417</v>
       </c>
       <c r="H502" t="n">
         <v>158000</v>
@@ -15217,7 +15217,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H512" t="n">
         <v>13500</v>
@@ -15304,7 +15304,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G515" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H515" t="n">
         <v>32500</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H516" t="n">
         <v>7500</v>
@@ -15478,7 +15478,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H521" t="n">
         <v>26500</v>
@@ -15507,7 +15507,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H522" t="n">
         <v>99000</v>
@@ -15536,7 +15536,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H523" t="n">
         <v>47500</v>
@@ -15681,7 +15681,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H528" t="n">
         <v>18500</v>
@@ -15710,7 +15710,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G529" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H529" t="n">
         <v>28000</v>
@@ -15768,7 +15768,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H531" t="n">
         <v>58000</v>
@@ -15826,7 +15826,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H533" t="n">
         <v>500</v>
@@ -15855,7 +15855,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H534" t="n">
         <v>10000</v>
@@ -15884,7 +15884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H535" t="n">
         <v>24500</v>
@@ -15913,7 +15913,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H536" t="n">
         <v>1500</v>
@@ -15942,7 +15942,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H537" t="n">
         <v>21500</v>
@@ -16087,7 +16087,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H542" t="n">
         <v>8000</v>
@@ -16116,7 +16116,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H543" t="n">
         <v>7500</v>
@@ -16232,7 +16232,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H547" t="n">
         <v>5000</v>
@@ -16609,7 +16609,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.8486750125885</v>
+        <v>2.84867477416992</v>
       </c>
       <c r="H560" t="n">
         <v>11000</v>
@@ -16899,7 +16899,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H570" t="n">
         <v>15500</v>
@@ -16928,7 +16928,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H572" t="n">
         <v>11500</v>
@@ -17102,7 +17102,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H577" t="n">
         <v>25000</v>
@@ -17160,7 +17160,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H579" t="n">
         <v>18000</v>
@@ -17247,7 +17247,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840702056885</v>
       </c>
       <c r="H582" t="n">
         <v>42500</v>
@@ -17363,7 +17363,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840702056885</v>
       </c>
       <c r="H586" t="n">
         <v>9000</v>
@@ -17566,7 +17566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.16705632209778</v>
+        <v>3.1670560836792</v>
       </c>
       <c r="H593" t="n">
         <v>20500</v>
@@ -17595,7 +17595,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543458938599</v>
+        <v>3.17543482780457</v>
       </c>
       <c r="H594" t="n">
         <v>10000</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.29273319244385</v>
+        <v>3.29273295402527</v>
       </c>
       <c r="H598" t="n">
         <v>15000</v>
@@ -17740,7 +17740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30948972702026</v>
       </c>
       <c r="H599" t="n">
         <v>10000</v>
@@ -17769,7 +17769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H600" t="n">
         <v>29000</v>
@@ -17798,7 +17798,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H601" t="n">
         <v>13000</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H602" t="n">
         <v>20500</v>
@@ -17856,7 +17856,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>3.32624697685242</v>
+        <v>3.32624673843384</v>
       </c>
       <c r="H603" t="n">
         <v>21500</v>
@@ -18494,7 +18494,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G625" t="n">
-        <v>3.11886930465698</v>
+        <v>3.11886954307556</v>
       </c>
       <c r="H625" t="n">
         <v>7000</v>
@@ -18639,7 +18639,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>3.11886930465698</v>
+        <v>3.11886954307556</v>
       </c>
       <c r="H630" t="n">
         <v>8500</v>
@@ -18755,7 +18755,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.13634204864502</v>
+        <v>3.13634181022644</v>
       </c>
       <c r="H634" t="n">
         <v>3000</v>
@@ -18784,7 +18784,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>3.13634204864502</v>
+        <v>3.13634181022644</v>
       </c>
       <c r="H635" t="n">
         <v>11000</v>
@@ -18929,7 +18929,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>3.11886930465698</v>
+        <v>3.11886954307556</v>
       </c>
       <c r="H640" t="n">
         <v>10000</v>
@@ -18958,7 +18958,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.13634204864502</v>
+        <v>3.13634181022644</v>
       </c>
       <c r="H641" t="n">
         <v>8000</v>
@@ -18987,7 +18987,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>3.06645131111145</v>
+        <v>3.06645154953003</v>
       </c>
       <c r="H642" t="n">
         <v>67500</v>
@@ -19045,7 +19045,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>3.06645131111145</v>
+        <v>3.06645154953003</v>
       </c>
       <c r="H644" t="n">
         <v>10000</v>
@@ -19103,7 +19103,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>3.11886930465698</v>
+        <v>3.11886954307556</v>
       </c>
       <c r="H646" t="n">
         <v>7500</v>
@@ -19248,7 +19248,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>3.11886930465698</v>
+        <v>3.11886954307556</v>
       </c>
       <c r="H651" t="n">
         <v>17500</v>
@@ -19277,7 +19277,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G652" t="n">
-        <v>3.22370553016663</v>
+        <v>3.22370529174805</v>
       </c>
       <c r="H652" t="n">
         <v>22500</v>
@@ -19306,7 +19306,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>3.22370553016663</v>
+        <v>3.22370529174805</v>
       </c>
       <c r="H653" t="n">
         <v>23500</v>
@@ -19393,7 +19393,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>3.24117827415466</v>
+        <v>3.24117803573608</v>
       </c>
       <c r="H656" t="n">
         <v>35500</v>
@@ -19625,7 +19625,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.36348652839661</v>
+        <v>3.36348676681519</v>
       </c>
       <c r="H664" t="n">
         <v>13500</v>
@@ -19654,7 +19654,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>3.34601378440857</v>
+        <v>3.34601402282715</v>
       </c>
       <c r="H665" t="n">
         <v>6000</v>
@@ -19683,7 +19683,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.36348652839661</v>
+        <v>3.36348676681519</v>
       </c>
       <c r="H666" t="n">
         <v>31500</v>
@@ -19741,7 +19741,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H668" t="n">
         <v>21500</v>
@@ -19915,7 +19915,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H674" t="n">
         <v>52000</v>
@@ -19944,7 +19944,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H675" t="n">
         <v>9500</v>
@@ -19973,7 +19973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H676" t="n">
         <v>26000</v>
@@ -20089,7 +20089,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H680" t="n">
         <v>6500</v>
@@ -20408,7 +20408,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H691" t="n">
         <v>6500</v>
@@ -20437,7 +20437,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31106853485107</v>
+        <v>3.31106877326965</v>
       </c>
       <c r="H692" t="n">
         <v>12500</v>
@@ -20988,7 +20988,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G711" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H711" t="n">
         <v>25000</v>
@@ -21075,7 +21075,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G714" t="n">
-        <v>3.53821325302124</v>
+        <v>3.53821349143982</v>
       </c>
       <c r="H714" t="n">
         <v>12500</v>
@@ -21162,7 +21162,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G717" t="n">
-        <v>3.53821325302124</v>
+        <v>3.53821349143982</v>
       </c>
       <c r="H717" t="n">
         <v>38000</v>
@@ -21307,7 +21307,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G722" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H722" t="n">
         <v>33500</v>
@@ -21423,7 +21423,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H726" t="n">
         <v>12500</v>
@@ -21481,7 +21481,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G728" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H728" t="n">
         <v>15000</v>
@@ -22873,7 +22873,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>3.53821325302124</v>
+        <v>3.53821349143982</v>
       </c>
       <c r="H776" t="n">
         <v>49000</v>
@@ -23221,7 +23221,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H788" t="n">
         <v>12500</v>
@@ -23250,7 +23250,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G789" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H789" t="n">
         <v>9500</v>
@@ -23395,7 +23395,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G794" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H794" t="n">
         <v>14500</v>
@@ -23511,7 +23511,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.59063124656677</v>
+        <v>3.59063148498535</v>
       </c>
       <c r="H798" t="n">
         <v>8000</v>
@@ -23569,7 +23569,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85272121429443</v>
+        <v>3.85272097587585</v>
       </c>
       <c r="H800" t="n">
         <v>42000</v>
@@ -23685,7 +23685,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G804" t="n">
-        <v>3.75662159919739</v>
+        <v>3.75662136077881</v>
       </c>
       <c r="H804" t="n">
         <v>13500</v>
@@ -23743,7 +23743,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.75662159919739</v>
+        <v>3.75662136077881</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.79156684875488</v>
+        <v>3.7915666103363</v>
       </c>
       <c r="H808" t="n">
         <v>3500</v>
@@ -23917,7 +23917,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G812" t="n">
-        <v>3.83524823188782</v>
+        <v>3.8352484703064</v>
       </c>
       <c r="H812" t="n">
         <v>18000</v>
@@ -24062,7 +24062,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.66052198410034</v>
+        <v>3.66052174568176</v>
       </c>
       <c r="H817" t="n">
         <v>36000</v>
@@ -24294,7 +24294,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>3.69546723365784</v>
+        <v>3.69546699523926</v>
       </c>
       <c r="H825" t="n">
         <v>17500</v>
@@ -24381,7 +24381,7 @@
         <v>4.25</v>
       </c>
       <c r="G828" t="n">
-        <v>3.71293997764587</v>
+        <v>3.71293973922729</v>
       </c>
       <c r="H828" t="n">
         <v>10000</v>
@@ -24410,7 +24410,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>3.7042031288147</v>
+        <v>3.70420336723328</v>
       </c>
       <c r="H829" t="n">
         <v>6500</v>
@@ -24700,7 +24700,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>4.32448244094849</v>
+        <v>4.32448291778564</v>
       </c>
       <c r="H839" t="n">
         <v>26000</v>
@@ -24990,7 +24990,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G849" t="n">
-        <v>4.49047327041626</v>
+        <v>4.4904727935791</v>
       </c>
       <c r="H849" t="n">
         <v>14000</v>
@@ -25048,7 +25048,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.49047327041626</v>
+        <v>4.4904727935791</v>
       </c>
       <c r="H851" t="n">
         <v>14000</v>
@@ -25106,7 +25106,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G853" t="n">
-        <v>4.52541780471802</v>
+        <v>4.52541828155518</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25222,7 +25222,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>4.63025426864624</v>
+        <v>4.6302547454834</v>
       </c>
       <c r="H857" t="n">
         <v>8500</v>
@@ -25309,7 +25309,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>4.7350902557373</v>
+        <v>4.73509073257446</v>
       </c>
       <c r="H860" t="n">
         <v>4000</v>
@@ -25396,7 +25396,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>4.7350902557373</v>
+        <v>4.73509073257446</v>
       </c>
       <c r="H863" t="n">
         <v>3500</v>
@@ -36016,6 +36016,35 @@
         <v>9000</v>
       </c>
       <c r="I1229" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1230" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>7.42000007629395</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>24500</v>
+      </c>
+      <c r="I1230" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516021728516</v>
+        <v>2.62516045570374</v>
       </c>
       <c r="H2" t="n">
         <v>1387000</v>
@@ -456,7 +456,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66764616966248</v>
+        <v>2.6676459312439</v>
       </c>
       <c r="H3" t="n">
         <v>383000</v>
@@ -543,7 +543,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>5.30099153518677</v>
+        <v>5.30099201202393</v>
       </c>
       <c r="H6" t="n">
         <v>635500</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.459068775177</v>
+        <v>4.45906972885132</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -630,7 +630,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558362007141</v>
+        <v>3.90558385848999</v>
       </c>
       <c r="H9" t="n">
         <v>388500</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.08488178253174</v>
+        <v>4.0848822593689</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136493682861</v>
+        <v>3.76136541366577</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -775,7 +775,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574353218079</v>
+        <v>3.97574377059937</v>
       </c>
       <c r="H14" t="n">
         <v>84000</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0926775932312</v>
+        <v>4.09267807006836</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756666183472</v>
+        <v>4.28756713867188</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1123,7 +1123,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858856201172</v>
+        <v>4.24858903884888</v>
       </c>
       <c r="H26" t="n">
         <v>26000</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283798217773</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1384,7 +1384,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>4.0536994934082</v>
+        <v>4.05369997024536</v>
       </c>
       <c r="H35" t="n">
         <v>19000</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676662445068</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676662445068</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8705039024353</v>
+        <v>3.87050414085388</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1674,7 +1674,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711718559265</v>
       </c>
       <c r="H45" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015286445618</v>
+        <v>3.96015238761902</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8705039024353</v>
+        <v>3.87050414085388</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628545761108</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1819,7 +1819,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187684059143</v>
+        <v>3.74187707901001</v>
       </c>
       <c r="H50" t="n">
         <v>2500</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088496208191</v>
+        <v>3.55088448524475</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1964,7 +1964,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.35209822654724</v>
+        <v>3.35209798812866</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4573380947113</v>
+        <v>3.45733785629272</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2051,7 +2051,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.5002133846283</v>
+        <v>3.50021362304688</v>
       </c>
       <c r="H58" t="n">
         <v>8000</v>
@@ -2080,7 +2080,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.34430241584778</v>
+        <v>3.3443021774292</v>
       </c>
       <c r="H59" t="n">
         <v>18500</v>
@@ -2109,7 +2109,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.41056442260742</v>
+        <v>3.41056489944458</v>
       </c>
       <c r="H60" t="n">
         <v>8000</v>
@@ -2138,7 +2138,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.41056442260742</v>
+        <v>3.41056489944458</v>
       </c>
       <c r="H61" t="n">
         <v>500</v>
@@ -2196,7 +2196,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G63" t="n">
-        <v>3.46123600006104</v>
+        <v>3.46123576164246</v>
       </c>
       <c r="H63" t="n">
         <v>5500</v>
@@ -2225,7 +2225,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529357910156</v>
+        <v>3.53529381752014</v>
       </c>
       <c r="H64" t="n">
         <v>3500</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698705673218</v>
+        <v>3.54698777198792</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2283,7 +2283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2428,7 +2428,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456124305725</v>
+        <v>3.94456148147583</v>
       </c>
       <c r="H71" t="n">
         <v>13500</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676662445068</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2573,7 +2573,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762742042542</v>
       </c>
       <c r="H76" t="n">
         <v>3500</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321856498718</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2747,7 +2747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711718559265</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2863,7 +2863,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711718559265</v>
       </c>
       <c r="H86" t="n">
         <v>1000</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321856498718</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.7379789352417</v>
+        <v>3.73797869682312</v>
       </c>
       <c r="H88" t="n">
         <v>36500</v>
@@ -2979,7 +2979,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762789726257</v>
+        <v>3.82762742042542</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542394638062</v>
+        <v>3.83542346954346</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3124,7 +3124,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644584655762</v>
+        <v>3.79644560813904</v>
       </c>
       <c r="H95" t="n">
         <v>7500</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448937416077</v>
+        <v>3.80448889732361</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3501,7 +3501,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535468101501</v>
+        <v>3.96535515785217</v>
       </c>
       <c r="H108" t="n">
         <v>10500</v>
@@ -3820,7 +3820,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383205413818</v>
+        <v>4.05383157730103</v>
       </c>
       <c r="H119" t="n">
         <v>3500</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133399009705</v>
+        <v>3.96133375167847</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.8768789768219</v>
+        <v>3.87687945365906</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -3994,7 +3994,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.8004674911499</v>
+        <v>3.80046701431274</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601223945618</v>
+        <v>3.71601271629333</v>
       </c>
       <c r="H126" t="n">
         <v>9000</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949229240417</v>
+        <v>3.61949276924133</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4168,7 +4168,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H131" t="n">
         <v>3000</v>
@@ -4255,7 +4255,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970921516418</v>
+        <v>3.65970969200134</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482131004333</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895141601562</v>
       </c>
       <c r="H139" t="n">
         <v>500</v>
@@ -4429,7 +4429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4516,7 +4516,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297306060791</v>
+        <v>3.52297282218933</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482131004333</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4690,7 +4690,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123279571533</v>
+        <v>3.57123255729675</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4893,7 +4893,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895141601562</v>
       </c>
       <c r="H156" t="n">
         <v>9500</v>
@@ -5067,7 +5067,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G162" t="n">
-        <v>3.47069096565247</v>
+        <v>3.47069144248962</v>
       </c>
       <c r="H162" t="n">
         <v>5000</v>
@@ -5096,7 +5096,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.4023232460022</v>
+        <v>3.40232300758362</v>
       </c>
       <c r="H163" t="n">
         <v>5500</v>
@@ -5125,7 +5125,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036629676819</v>
+        <v>3.41036653518677</v>
       </c>
       <c r="H164" t="n">
         <v>500</v>
@@ -5154,7 +5154,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G165" t="n">
-        <v>3.47069096565247</v>
+        <v>3.47069144248962</v>
       </c>
       <c r="H165" t="n">
         <v>1500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884295463562</v>
+        <v>3.4988431930542</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5270,7 +5270,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862674713135</v>
+        <v>3.45862650871277</v>
       </c>
       <c r="H169" t="n">
         <v>10500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.31384634971619</v>
+        <v>3.31384658813477</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.23341369628906</v>
+        <v>3.23341345787048</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5560,7 +5560,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H179" t="n">
         <v>3500</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H183" t="n">
         <v>21500</v>
@@ -5821,7 +5821,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080717086792</v>
+        <v>3.12080693244934</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H189" t="n">
         <v>4000</v>
@@ -5879,7 +5879,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222205162048</v>
+        <v>3.0122218132019</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5908,7 +5908,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G191" t="n">
-        <v>3.04841685295105</v>
+        <v>3.04841709136963</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5966,7 +5966,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624369621277</v>
+        <v>3.01624393463135</v>
       </c>
       <c r="H193" t="n">
         <v>92500</v>
@@ -6111,7 +6111,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H199" t="n">
         <v>5500</v>
@@ -6459,7 +6459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059799194336</v>
+        <v>2.71059775352478</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6546,7 +6546,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.73472762107849</v>
+        <v>2.73472785949707</v>
       </c>
       <c r="H213" t="n">
         <v>10000</v>
@@ -6575,7 +6575,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896618843079</v>
+        <v>2.77896595001221</v>
       </c>
       <c r="H214" t="n">
         <v>9000</v>
@@ -6604,7 +6604,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H215" t="n">
         <v>5500</v>
@@ -6662,7 +6662,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6778,7 +6778,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>2.84733414649963</v>
+        <v>2.84733438491821</v>
       </c>
       <c r="H221" t="n">
         <v>41000</v>
@@ -6865,7 +6865,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.84733414649963</v>
+        <v>2.84733438491821</v>
       </c>
       <c r="H224" t="n">
         <v>7500</v>
@@ -6894,7 +6894,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G225" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H225" t="n">
         <v>4500</v>
@@ -6923,7 +6923,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G226" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H226" t="n">
         <v>2500</v>
@@ -6952,7 +6952,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G227" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H227" t="n">
         <v>3000</v>
@@ -7039,7 +7039,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G230" t="n">
-        <v>2.90765881538391</v>
+        <v>2.90765905380249</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7068,7 +7068,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G231" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H231" t="n">
         <v>1500</v>
@@ -7126,7 +7126,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H233" t="n">
         <v>500</v>
@@ -7271,7 +7271,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G238" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H238" t="n">
         <v>1500</v>
@@ -7300,7 +7300,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H242" t="n">
         <v>1000</v>
@@ -7416,7 +7416,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H243" t="n">
         <v>500</v>
@@ -7445,7 +7445,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7590,7 +7590,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G249" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7619,7 +7619,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G250" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -7851,7 +7851,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H258" t="n">
         <v>1000</v>
@@ -7880,7 +7880,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H259" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H265" t="n">
         <v>500</v>
@@ -8083,7 +8083,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8141,7 +8141,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H268" t="n">
         <v>2000</v>
@@ -8170,7 +8170,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H269" t="n">
         <v>11500</v>
@@ -8228,7 +8228,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8344,7 +8344,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G275" t="n">
-        <v>2.94385409355164</v>
+        <v>2.94385385513306</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8402,7 +8402,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>2.9197244644165</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H277" t="n">
         <v>4000</v>
@@ -8547,7 +8547,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>2.95189762115479</v>
+        <v>2.95189738273621</v>
       </c>
       <c r="H282" t="n">
         <v>15000</v>
@@ -8576,7 +8576,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H283" t="n">
         <v>17500</v>
@@ -8605,7 +8605,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591902732849</v>
+        <v>2.95591926574707</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H285" t="n">
         <v>37500</v>
@@ -8663,7 +8663,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98809218406677</v>
+        <v>2.98809242248535</v>
       </c>
       <c r="H286" t="n">
         <v>33000</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917489051819</v>
+        <v>3.18917512893677</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8808,7 +8808,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047475814819</v>
+        <v>3.43047451972961</v>
       </c>
       <c r="H291" t="n">
         <v>70000</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656133651733</v>
+        <v>3.44656109809875</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8953,7 +8953,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612820625305</v>
+        <v>3.36612796783447</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9098,7 +9098,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.3259117603302</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H301" t="n">
         <v>3500</v>
@@ -9185,7 +9185,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.3259117603302</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9446,7 +9446,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547112464905</v>
+        <v>3.61547064781189</v>
       </c>
       <c r="H313" t="n">
         <v>9000</v>
@@ -9475,7 +9475,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.4505832195282</v>
+        <v>3.45058298110962</v>
       </c>
       <c r="H314" t="n">
         <v>14000</v>
@@ -9504,7 +9504,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862674713135</v>
+        <v>3.45862650871277</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9591,7 +9591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9765,7 +9765,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H324" t="n">
         <v>6500</v>
@@ -9794,7 +9794,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H327" t="n">
         <v>2500</v>
@@ -9881,7 +9881,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H328" t="n">
         <v>4000</v>
@@ -9910,7 +9910,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993292808533</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10200,7 +10200,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>3.31384634971619</v>
+        <v>3.31384658813477</v>
       </c>
       <c r="H339" t="n">
         <v>8000</v>
@@ -36030,7 +36030,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="D1230" t="n">
-        <v>7.69999980926514</v>
+        <v>7.80000019073486</v>
       </c>
       <c r="E1230" t="n">
         <v>7.42000007629395</v>
@@ -36045,6 +36045,35 @@
         <v>24500</v>
       </c>
       <c r="I1230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1231" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>11250</v>
+      </c>
+      <c r="I1231" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -630,7 +630,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558385848999</v>
+        <v>3.90558457374573</v>
       </c>
       <c r="H9" t="n">
         <v>388500</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0848822593689</v>
+        <v>4.08488178253174</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136541366577</v>
+        <v>3.76136493682861</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -775,7 +775,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574377059937</v>
+        <v>3.97574353218079</v>
       </c>
       <c r="H14" t="n">
         <v>84000</v>
@@ -833,7 +833,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H16" t="n">
         <v>208500</v>
@@ -862,7 +862,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H17" t="n">
         <v>60000</v>
@@ -920,7 +920,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H19" t="n">
         <v>93500</v>
@@ -949,7 +949,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H20" t="n">
         <v>61500</v>
@@ -978,7 +978,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H21" t="n">
         <v>24000</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267807006836</v>
+        <v>4.09267711639404</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1094,7 +1094,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H25" t="n">
         <v>60000</v>
@@ -1181,7 +1181,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961141586304</v>
+        <v>4.2096118927002</v>
       </c>
       <c r="H28" t="n">
         <v>43500</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283750534058</v>
+        <v>4.16283798217773</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1384,7 +1384,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G35" t="n">
-        <v>4.05369997024536</v>
+        <v>4.0536994934082</v>
       </c>
       <c r="H35" t="n">
         <v>19000</v>
@@ -1471,7 +1471,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999247550964</v>
+        <v>3.88999223709106</v>
       </c>
       <c r="H38" t="n">
         <v>32000</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676662445068</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676662445068</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1558,7 +1558,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H41" t="n">
         <v>10500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050414085388</v>
+        <v>3.87050366401672</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1645,7 +1645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.8510148525238</v>
+        <v>3.85101437568665</v>
       </c>
       <c r="H44" t="n">
         <v>25000</v>
@@ -1674,7 +1674,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H45" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015238761902</v>
+        <v>3.96015286445618</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050414085388</v>
+        <v>3.87050366401672</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628569602966</v>
+        <v>3.72628593444824</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1819,7 +1819,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187707901001</v>
+        <v>3.74187684059143</v>
       </c>
       <c r="H50" t="n">
         <v>2500</v>
@@ -1877,7 +1877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922174453735</v>
+        <v>3.30922198295593</v>
       </c>
       <c r="H52" t="n">
         <v>36500</v>
@@ -2167,7 +2167,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.3832802772522</v>
+        <v>3.38328003883362</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698777198792</v>
+        <v>3.54698753356934</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133515357971</v>
+        <v>3.99133491516113</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2370,7 +2370,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.9991307258606</v>
+        <v>3.99913096427917</v>
       </c>
       <c r="H69" t="n">
         <v>13000</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676662445068</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2544,7 +2544,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491275787354</v>
+        <v>3.85491299629211</v>
       </c>
       <c r="H75" t="n">
         <v>11000</v>
@@ -2573,7 +2573,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762742042542</v>
+        <v>3.82762813568115</v>
       </c>
       <c r="H76" t="n">
         <v>3500</v>
@@ -2602,7 +2602,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983208656311</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219690322876</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H81" t="n">
         <v>1500</v>
@@ -2747,7 +2747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999247550964</v>
+        <v>3.88999223709106</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778780937195</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2834,7 +2834,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593465805054</v>
       </c>
       <c r="H85" t="n">
         <v>2500</v>
@@ -2863,7 +2863,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711718559265</v>
+        <v>3.84711670875549</v>
       </c>
       <c r="H86" t="n">
         <v>1000</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.73797869682312</v>
+        <v>3.7379789352417</v>
       </c>
       <c r="H88" t="n">
         <v>36500</v>
@@ -2950,7 +2950,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78864979743958</v>
+        <v>3.78865003585815</v>
       </c>
       <c r="H89" t="n">
         <v>6500</v>
@@ -2979,7 +2979,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762742042542</v>
+        <v>3.82762813568115</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3037,7 +3037,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593441963196</v>
+        <v>3.81593465805054</v>
       </c>
       <c r="H92" t="n">
         <v>6500</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983208656311</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983208656311</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3153,7 +3153,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459712028503</v>
+        <v>3.82459735870361</v>
       </c>
       <c r="H97" t="n">
         <v>2000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111706733704</v>
+        <v>3.92111730575562</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3356,7 +3356,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.9050304889679</v>
+        <v>3.90503025054932</v>
       </c>
       <c r="H104" t="n">
         <v>17500</v>
@@ -3472,7 +3472,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H107" t="n">
         <v>21000</v>
@@ -3675,7 +3675,7 @@
         <v>5.25</v>
       </c>
       <c r="G114" t="n">
-        <v>4.22274160385132</v>
+        <v>4.22274112701416</v>
       </c>
       <c r="H114" t="n">
         <v>6000</v>
@@ -3762,7 +3762,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209131240845</v>
+        <v>4.10209178924561</v>
       </c>
       <c r="H117" t="n">
         <v>11000</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133375167847</v>
+        <v>3.96133351325989</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3965,7 +3965,7 @@
         <v>4.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82057571411133</v>
+        <v>3.82057547569275</v>
       </c>
       <c r="H124" t="n">
         <v>4500</v>
@@ -4023,7 +4023,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601271629333</v>
+        <v>3.71601247787476</v>
       </c>
       <c r="H126" t="n">
         <v>9000</v>
@@ -4139,7 +4139,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340619087219</v>
+        <v>3.60340595245361</v>
       </c>
       <c r="H130" t="n">
         <v>1500</v>
@@ -4342,7 +4342,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G137" t="n">
-        <v>3.50688600540161</v>
+        <v>3.50688624382019</v>
       </c>
       <c r="H137" t="n">
         <v>500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482083320618</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731913566589</v>
+        <v>3.58731937408447</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731913566589</v>
+        <v>3.58731937408447</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025855064392</v>
+        <v>3.39025831222534</v>
       </c>
       <c r="H144" t="n">
         <v>4500</v>
@@ -4574,7 +4574,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G145" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H145" t="n">
         <v>500</v>
@@ -4603,7 +4603,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G146" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482083320618</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905940055847</v>
+        <v>3.53905963897705</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905940055847</v>
+        <v>3.53905963897705</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.5269947052002</v>
+        <v>3.52699446678162</v>
       </c>
       <c r="H154" t="n">
         <v>4000</v>
@@ -4922,7 +4922,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112481117249</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112481117249</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G160" t="n">
-        <v>3.4827561378479</v>
+        <v>3.48275637626648</v>
       </c>
       <c r="H160" t="n">
         <v>1000</v>
@@ -5096,7 +5096,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40232300758362</v>
+        <v>3.4023232460022</v>
       </c>
       <c r="H163" t="n">
         <v>5500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.4988431930542</v>
+        <v>3.49884295463562</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5357,7 +5357,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>3.34601950645447</v>
+        <v>3.34601974487305</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5386,7 +5386,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H173" t="n">
         <v>1500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.23341345787048</v>
+        <v>3.2334132194519</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5618,7 +5618,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711043357849</v>
+        <v>3.17711019515991</v>
       </c>
       <c r="H181" t="n">
         <v>2500</v>
@@ -5647,7 +5647,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711043357849</v>
+        <v>3.17711019515991</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.0122218132019</v>
+        <v>3.01222205162048</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -6024,7 +6024,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211406707764</v>
+        <v>2.99211382865906</v>
       </c>
       <c r="H195" t="n">
         <v>8500</v>
@@ -6256,7 +6256,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.97200560569763</v>
+        <v>2.97200584411621</v>
       </c>
       <c r="H203" t="n">
         <v>500</v>
@@ -6314,7 +6314,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97200560569763</v>
+        <v>2.97200584411621</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6343,7 +6343,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>2.87146401405334</v>
+        <v>2.87146425247192</v>
       </c>
       <c r="H206" t="n">
         <v>5500</v>
@@ -6517,7 +6517,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.7467930316925</v>
+        <v>2.74679279327393</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.73472785949707</v>
+        <v>2.73472809791565</v>
       </c>
       <c r="H213" t="n">
         <v>10000</v>
@@ -6575,7 +6575,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896595001221</v>
+        <v>2.77896571159363</v>
       </c>
       <c r="H214" t="n">
         <v>9000</v>
@@ -6691,7 +6691,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929085731506</v>
+        <v>2.83929109573364</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.94787573814392</v>
+        <v>2.9478759765625</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7793,7 +7793,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374563217163</v>
+        <v>2.92374587059021</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.94787573814392</v>
+        <v>2.9478759765625</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.94787573814392</v>
+        <v>2.9478759765625</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8460,7 +8460,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H279" t="n">
         <v>5500</v>
@@ -8489,7 +8489,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H280" t="n">
         <v>15500</v>
@@ -8692,7 +8692,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.97602725028992</v>
+        <v>2.9760274887085</v>
       </c>
       <c r="H287" t="n">
         <v>5500</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917512893677</v>
+        <v>3.18917536735535</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8837,7 +8837,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5269947052002</v>
+        <v>3.52699446678162</v>
       </c>
       <c r="H292" t="n">
         <v>17000</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656109809875</v>
+        <v>3.44656085968018</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9098,7 +9098,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.32591152191162</v>
+        <v>3.3259117603302</v>
       </c>
       <c r="H301" t="n">
         <v>3500</v>
@@ -9185,7 +9185,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.32591152191162</v>
+        <v>3.3259117603302</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9330,7 +9330,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>3.34601950645447</v>
+        <v>3.34601974487305</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9359,7 +9359,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H310" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9446,7 +9446,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547064781189</v>
+        <v>3.61547088623047</v>
       </c>
       <c r="H313" t="n">
         <v>9000</v>
@@ -9649,7 +9649,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>3.39427971839905</v>
+        <v>3.39427947998047</v>
       </c>
       <c r="H320" t="n">
         <v>14500</v>
@@ -9678,7 +9678,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H321" t="n">
         <v>8000</v>
@@ -9881,7 +9881,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H328" t="n">
         <v>4000</v>
@@ -9910,7 +9910,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373788833618</v>
+        <v>3.29373812675476</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189011573792</v>
+        <v>3.32189035415649</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29776000976562</v>
+        <v>3.2977602481842</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29776000976562</v>
+        <v>3.2977602481842</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10403,7 +10403,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.2495002746582</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H346" t="n">
         <v>67500</v>
@@ -10461,7 +10461,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.2495002746582</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H352" t="n">
         <v>500</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.35138201713562</v>
+        <v>3.3513822555542</v>
       </c>
       <c r="H359" t="n">
         <v>34500</v>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.35138201713562</v>
+        <v>3.3513822555542</v>
       </c>
       <c r="H361" t="n">
         <v>3500</v>
@@ -10867,7 +10867,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H362" t="n">
         <v>16500</v>
@@ -10896,7 +10896,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.39327454566956</v>
+        <v>3.39327478408813</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H369" t="n">
         <v>9000</v>
@@ -11099,7 +11099,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192360877991</v>
+        <v>3.45192384719849</v>
       </c>
       <c r="H370" t="n">
         <v>10500</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H373" t="n">
         <v>10500</v>
@@ -11331,7 +11331,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246520042419</v>
+        <v>3.55246496200562</v>
       </c>
       <c r="H378" t="n">
         <v>27000</v>
@@ -11389,7 +11389,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>3.67814183235168</v>
+        <v>3.67814207077026</v>
       </c>
       <c r="H380" t="n">
         <v>61500</v>
@@ -11418,7 +11418,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>3.67814183235168</v>
+        <v>3.67814207077026</v>
       </c>
       <c r="H381" t="n">
         <v>17500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>3.67814183235168</v>
+        <v>3.67814207077026</v>
       </c>
       <c r="H382" t="n">
         <v>25500</v>
@@ -11476,7 +11476,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003412246704</v>
+        <v>3.72003436088562</v>
       </c>
       <c r="H383" t="n">
         <v>33500</v>
@@ -11505,7 +11505,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003412246704</v>
+        <v>3.72003436088562</v>
       </c>
       <c r="H384" t="n">
         <v>14000</v>
@@ -11534,7 +11534,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679137229919</v>
+        <v>3.73679113388062</v>
       </c>
       <c r="H385" t="n">
         <v>34000</v>
@@ -11563,7 +11563,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G386" t="n">
-        <v>3.67814183235168</v>
+        <v>3.67814207077026</v>
       </c>
       <c r="H386" t="n">
         <v>127500</v>
@@ -11592,7 +11592,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G387" t="n">
-        <v>3.67814183235168</v>
+        <v>3.67814207077026</v>
       </c>
       <c r="H387" t="n">
         <v>8000</v>
@@ -11679,7 +11679,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>3.58597874641418</v>
+        <v>3.58597898483276</v>
       </c>
       <c r="H390" t="n">
         <v>24500</v>
@@ -11737,7 +11737,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H392" t="n">
         <v>15500</v>
@@ -11795,7 +11795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H394" t="n">
         <v>16500</v>
@@ -11998,7 +11998,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.62787103652954</v>
+        <v>3.62787127494812</v>
       </c>
       <c r="H401" t="n">
         <v>8000</v>
@@ -12056,7 +12056,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.62787103652954</v>
+        <v>3.62787127494812</v>
       </c>
       <c r="H403" t="n">
         <v>8000</v>
@@ -12085,7 +12085,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>3.59435749053955</v>
+        <v>3.59435725212097</v>
       </c>
       <c r="H404" t="n">
         <v>34000</v>
@@ -12230,7 +12230,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>3.54408669471741</v>
+        <v>3.54408645629883</v>
       </c>
       <c r="H409" t="n">
         <v>10500</v>
@@ -12259,7 +12259,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.51057291030884</v>
+        <v>3.51057267189026</v>
       </c>
       <c r="H410" t="n">
         <v>8000</v>
@@ -12288,7 +12288,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354557991028</v>
       </c>
       <c r="H411" t="n">
         <v>14500</v>
@@ -12346,7 +12346,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354557991028</v>
       </c>
       <c r="H413" t="n">
         <v>8500</v>
@@ -12433,7 +12433,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>3.36813926696777</v>
+        <v>3.36813902854919</v>
       </c>
       <c r="H416" t="n">
         <v>6000</v>
@@ -12462,7 +12462,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H417" t="n">
         <v>10500</v>
@@ -12520,7 +12520,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H419" t="n">
         <v>9000</v>
@@ -12723,7 +12723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>3.09165024757385</v>
+        <v>3.09165000915527</v>
       </c>
       <c r="H426" t="n">
         <v>16000</v>
@@ -12781,7 +12781,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>3.09165024757385</v>
+        <v>3.09165000915527</v>
       </c>
       <c r="H428" t="n">
         <v>19000</v>
@@ -12810,7 +12810,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>3.09165024757385</v>
+        <v>3.09165000915527</v>
       </c>
       <c r="H429" t="n">
         <v>10500</v>
@@ -13071,7 +13071,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0497579574585</v>
+        <v>3.04975771903992</v>
       </c>
       <c r="H438" t="n">
         <v>8500</v>
@@ -13100,7 +13100,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>3.09165024757385</v>
+        <v>3.09165000915527</v>
       </c>
       <c r="H439" t="n">
         <v>18000</v>
@@ -13158,7 +13158,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G441" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H441" t="n">
         <v>18000</v>
@@ -13332,7 +13332,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G447" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H447" t="n">
         <v>12000</v>
@@ -13419,7 +13419,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12516379356384</v>
+        <v>3.12516403198242</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12516379356384</v>
+        <v>3.12516403198242</v>
       </c>
       <c r="H451" t="n">
         <v>2000</v>
@@ -13593,7 +13593,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G456" t="n">
-        <v>3.00786542892456</v>
+        <v>3.00786519050598</v>
       </c>
       <c r="H456" t="n">
         <v>17000</v>
@@ -13738,7 +13738,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H461" t="n">
         <v>20500</v>
@@ -13767,7 +13767,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H462" t="n">
         <v>12000</v>
@@ -13796,7 +13796,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H463" t="n">
         <v>26000</v>
@@ -13912,7 +13912,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G467" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H467" t="n">
         <v>28000</v>
@@ -13970,7 +13970,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H469" t="n">
         <v>19500</v>
@@ -13999,7 +13999,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H470" t="n">
         <v>500</v>
@@ -14086,7 +14086,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H473" t="n">
         <v>20000</v>
@@ -14144,7 +14144,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H475" t="n">
         <v>7500</v>
@@ -14173,7 +14173,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H476" t="n">
         <v>18000</v>
@@ -14347,7 +14347,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029626846313</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H501" t="n">
         <v>21500</v>
@@ -14927,7 +14927,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>3.0748929977417</v>
+        <v>3.07489323616028</v>
       </c>
       <c r="H502" t="n">
         <v>158000</v>
@@ -14956,7 +14956,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H503" t="n">
         <v>72000</v>
@@ -15217,7 +15217,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H512" t="n">
         <v>13500</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H516" t="n">
         <v>7500</v>
@@ -15391,7 +15391,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H518" t="n">
         <v>16500</v>
@@ -15420,7 +15420,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H519" t="n">
         <v>19000</v>
@@ -15449,7 +15449,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>2.89056706428528</v>
+        <v>2.89056730270386</v>
       </c>
       <c r="H520" t="n">
         <v>12000</v>
@@ -15478,7 +15478,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H521" t="n">
         <v>26500</v>
@@ -15507,7 +15507,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H522" t="n">
         <v>99000</v>
@@ -15536,7 +15536,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H523" t="n">
         <v>47500</v>
@@ -15594,7 +15594,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.89056706428528</v>
+        <v>2.89056730270386</v>
       </c>
       <c r="H525" t="n">
         <v>20500</v>
@@ -15681,7 +15681,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H528" t="n">
         <v>18500</v>
@@ -15826,7 +15826,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H533" t="n">
         <v>500</v>
@@ -15855,7 +15855,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H534" t="n">
         <v>10000</v>
@@ -16029,7 +16029,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H540" t="n">
         <v>16500</v>
@@ -16087,7 +16087,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H542" t="n">
         <v>8000</v>
@@ -16116,7 +16116,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H543" t="n">
         <v>7500</v>
@@ -16203,7 +16203,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>2.89056706428528</v>
+        <v>2.89056730270386</v>
       </c>
       <c r="H546" t="n">
         <v>20500</v>
@@ -16232,7 +16232,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H547" t="n">
         <v>5000</v>
@@ -16290,7 +16290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H549" t="n">
         <v>1500</v>
@@ -16377,7 +16377,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H552" t="n">
         <v>11000</v>
@@ -16406,7 +16406,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G553" t="n">
-        <v>2.89056706428528</v>
+        <v>2.89056730270386</v>
       </c>
       <c r="H553" t="n">
         <v>25500</v>
@@ -16609,7 +16609,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.84867477416992</v>
+        <v>2.8486750125885</v>
       </c>
       <c r="H560" t="n">
         <v>11000</v>
@@ -16696,7 +16696,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89056706428528</v>
+        <v>2.89056730270386</v>
       </c>
       <c r="H563" t="n">
         <v>37500</v>
@@ -16725,7 +16725,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H564" t="n">
         <v>10000</v>
@@ -16870,7 +16870,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.89056706428528</v>
+        <v>2.89056730270386</v>
       </c>
       <c r="H569" t="n">
         <v>4000</v>
@@ -16899,7 +16899,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H570" t="n">
         <v>15500</v>
@@ -16928,7 +16928,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H572" t="n">
         <v>11500</v>
@@ -16986,7 +16986,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732407569885</v>
+        <v>2.90732431411743</v>
       </c>
       <c r="H573" t="n">
         <v>8000</v>
@@ -17160,7 +17160,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H579" t="n">
         <v>18000</v>
@@ -17334,7 +17334,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>3.12516379356384</v>
+        <v>3.12516403198242</v>
       </c>
       <c r="H585" t="n">
         <v>3000</v>
@@ -17421,7 +17421,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>3.12516379356384</v>
+        <v>3.12516403198242</v>
       </c>
       <c r="H588" t="n">
         <v>4500</v>
@@ -17566,7 +17566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.1670560836792</v>
+        <v>3.16705632209778</v>
       </c>
       <c r="H593" t="n">
         <v>20500</v>
@@ -17740,7 +17740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948972702026</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H599" t="n">
         <v>10000</v>
@@ -17769,7 +17769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H600" t="n">
         <v>29000</v>
@@ -17798,7 +17798,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H601" t="n">
         <v>13000</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H602" t="n">
         <v>20500</v>
@@ -36074,6 +36074,35 @@
         <v>11250</v>
       </c>
       <c r="I1231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1232" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>7.61999988555908</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1232" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516045570374</v>
+        <v>2.62516021728516</v>
       </c>
       <c r="H2" t="n">
         <v>1387000</v>
@@ -456,7 +456,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6676459312439</v>
+        <v>2.66764616966248</v>
       </c>
       <c r="H3" t="n">
         <v>383000</v>
@@ -485,7 +485,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621223449707</v>
+        <v>3.25621247291565</v>
       </c>
       <c r="H4" t="n">
         <v>912000</v>
@@ -514,7 +514,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805168151855</v>
+        <v>4.20805215835571</v>
       </c>
       <c r="H5" t="n">
         <v>1121500</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906972885132</v>
+        <v>4.45906925201416</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -630,7 +630,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558457374573</v>
+        <v>3.90558409690857</v>
       </c>
       <c r="H9" t="n">
         <v>388500</v>
@@ -659,7 +659,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G10" t="n">
-        <v>4.08488178253174</v>
+        <v>4.08488130569458</v>
       </c>
       <c r="H10" t="n">
         <v>357000</v>
@@ -688,7 +688,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H11" t="n">
         <v>83500</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136493682861</v>
+        <v>3.76136517524719</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -775,7 +775,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574353218079</v>
+        <v>3.97574400901794</v>
       </c>
       <c r="H14" t="n">
         <v>84000</v>
@@ -833,7 +833,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H16" t="n">
         <v>208500</v>
@@ -949,7 +949,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H20" t="n">
         <v>61500</v>
@@ -1036,7 +1036,7 @@
         <v>5.25</v>
       </c>
       <c r="G23" t="n">
-        <v>4.09267711639404</v>
+        <v>4.0926775932312</v>
       </c>
       <c r="H23" t="n">
         <v>109500</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756713867188</v>
+        <v>4.28756761550903</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1094,7 +1094,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536247253418</v>
+        <v>4.29536294937134</v>
       </c>
       <c r="H25" t="n">
         <v>60000</v>
@@ -1123,7 +1123,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858903884888</v>
+        <v>4.24858856201172</v>
       </c>
       <c r="H26" t="n">
         <v>26000</v>
@@ -1181,7 +1181,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.2096118927002</v>
+        <v>4.20961141586304</v>
       </c>
       <c r="H28" t="n">
         <v>43500</v>
@@ -1413,7 +1413,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1442,7 +1442,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H37" t="n">
         <v>39500</v>
@@ -1471,7 +1471,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999223709106</v>
+        <v>3.88999271392822</v>
       </c>
       <c r="H38" t="n">
         <v>32000</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676567077637</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676567077637</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1645,7 +1645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101437568665</v>
+        <v>3.8510148525238</v>
       </c>
       <c r="H44" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034351348877</v>
+        <v>3.80034375190735</v>
       </c>
       <c r="H46" t="n">
         <v>82500</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015286445618</v>
+        <v>3.96015238761902</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628593444824</v>
+        <v>3.72628569602966</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088448524475</v>
+        <v>3.55088472366333</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1877,7 +1877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922198295593</v>
+        <v>3.30922174453735</v>
       </c>
       <c r="H52" t="n">
         <v>36500</v>
@@ -1906,7 +1906,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704805374146</v>
+        <v>3.08704853057861</v>
       </c>
       <c r="H53" t="n">
         <v>44000</v>
@@ -1935,7 +1935,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516416549683</v>
+        <v>3.23516440391541</v>
       </c>
       <c r="H54" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733785629272</v>
+        <v>3.4573380947113</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2080,7 +2080,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3443021774292</v>
+        <v>3.34430241584778</v>
       </c>
       <c r="H59" t="n">
         <v>18500</v>
@@ -2109,7 +2109,7 @@
         <v>4.375</v>
       </c>
       <c r="G60" t="n">
-        <v>3.41056489944458</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H60" t="n">
         <v>8000</v>
@@ -2138,7 +2138,7 @@
         <v>4.375</v>
       </c>
       <c r="G61" t="n">
-        <v>3.41056489944458</v>
+        <v>3.41056442260742</v>
       </c>
       <c r="H61" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529381752014</v>
+        <v>3.53529357910156</v>
       </c>
       <c r="H64" t="n">
         <v>3500</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698753356934</v>
+        <v>3.54698729515076</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2283,7 +2283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542370796204</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117524147034</v>
+        <v>3.92117500305176</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133491516113</v>
+        <v>3.99133539199829</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2399,7 +2399,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456148147583</v>
+        <v>3.94456100463867</v>
       </c>
       <c r="H71" t="n">
         <v>13500</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676567077637</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2544,7 +2544,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.85491299629211</v>
+        <v>3.85491251945496</v>
       </c>
       <c r="H75" t="n">
         <v>11000</v>
@@ -2573,7 +2573,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762813568115</v>
+        <v>3.82762718200684</v>
       </c>
       <c r="H76" t="n">
         <v>3500</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542370796204</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983208656311</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2776,7 +2776,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999223709106</v>
+        <v>3.88999271392822</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778780937195</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.7379789352417</v>
+        <v>3.73797869682312</v>
       </c>
       <c r="H88" t="n">
         <v>36500</v>
@@ -2950,7 +2950,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G89" t="n">
-        <v>3.78865003585815</v>
+        <v>3.78865027427673</v>
       </c>
       <c r="H89" t="n">
         <v>6500</v>
@@ -2979,7 +2979,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762813568115</v>
+        <v>3.82762718200684</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542346954346</v>
+        <v>3.83542370796204</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983208656311</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983208656311</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3124,7 +3124,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644560813904</v>
+        <v>3.79644536972046</v>
       </c>
       <c r="H95" t="n">
         <v>7500</v>
@@ -3182,7 +3182,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459735870361</v>
+        <v>3.82459759712219</v>
       </c>
       <c r="H97" t="n">
         <v>2000</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448889732361</v>
+        <v>3.80448913574219</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720388412476</v>
+        <v>3.9372034072876</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720388412476</v>
+        <v>3.9372034072876</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3588,7 +3588,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>4.09404850006104</v>
+        <v>4.09404802322388</v>
       </c>
       <c r="H111" t="n">
         <v>4000</v>
@@ -3617,7 +3617,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469783782959</v>
+        <v>4.21469831466675</v>
       </c>
       <c r="H112" t="n">
         <v>17000</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133351325989</v>
+        <v>3.96133399009705</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687945365906</v>
+        <v>3.8768789768219</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -3994,7 +3994,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.80046701431274</v>
+        <v>3.80046725273132</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4023,7 +4023,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G126" t="n">
-        <v>3.71601247787476</v>
+        <v>3.71601223945618</v>
       </c>
       <c r="H126" t="n">
         <v>9000</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4110,7 +4110,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G129" t="n">
-        <v>3.60742783546448</v>
+        <v>3.6074275970459</v>
       </c>
       <c r="H129" t="n">
         <v>4500</v>
@@ -4168,7 +4168,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G131" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H131" t="n">
         <v>3000</v>
@@ -4226,7 +4226,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992589950562</v>
+        <v>3.69992566108704</v>
       </c>
       <c r="H133" t="n">
         <v>5000</v>
@@ -4255,7 +4255,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970969200134</v>
+        <v>3.65970945358276</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775250434875</v>
+        <v>3.66775226593018</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4313,7 +4313,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.55916786193848</v>
+        <v>3.5591676235199</v>
       </c>
       <c r="H136" t="n">
         <v>10500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482083320618</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>4.375</v>
       </c>
       <c r="G139" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H139" t="n">
         <v>500</v>
@@ -4429,7 +4429,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>3.52297282218933</v>
+        <v>3.52297306060791</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025831222534</v>
+        <v>3.39025807380676</v>
       </c>
       <c r="H144" t="n">
         <v>4500</v>
@@ -4574,7 +4574,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G145" t="n">
-        <v>3.39427947998047</v>
+        <v>3.39427971839905</v>
       </c>
       <c r="H145" t="n">
         <v>500</v>
@@ -4603,7 +4603,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G146" t="n">
-        <v>3.39427947998047</v>
+        <v>3.39427971839905</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482083320618</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4661,7 +4661,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.55916786193848</v>
+        <v>3.5591676235199</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G149" t="n">
-        <v>3.57123255729675</v>
+        <v>3.57123279571533</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G155" t="n">
-        <v>3.5792760848999</v>
+        <v>3.57927584648132</v>
       </c>
       <c r="H155" t="n">
         <v>2500</v>
@@ -4893,7 +4893,7 @@
         <v>4.375</v>
       </c>
       <c r="G156" t="n">
-        <v>3.51895141601562</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H156" t="n">
         <v>9500</v>
@@ -4922,7 +4922,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112433433533</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112433433533</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677802085876</v>
+        <v>3.48677778244019</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5096,7 +5096,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.4023232460022</v>
+        <v>3.40232348442078</v>
       </c>
       <c r="H163" t="n">
         <v>5500</v>
@@ -5125,7 +5125,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036653518677</v>
+        <v>3.41036605834961</v>
       </c>
       <c r="H164" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H166" t="n">
         <v>500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884295463562</v>
+        <v>3.49884271621704</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>3.49079966545105</v>
+        <v>3.49079990386963</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5270,7 +5270,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862650871277</v>
+        <v>3.45862674713135</v>
       </c>
       <c r="H169" t="n">
         <v>10500</v>
@@ -5386,7 +5386,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H173" t="n">
         <v>1500</v>
@@ -5473,7 +5473,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797693252563</v>
       </c>
       <c r="H176" t="n">
         <v>2500</v>
@@ -5560,7 +5560,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H179" t="n">
         <v>3500</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H183" t="n">
         <v>21500</v>
@@ -5705,7 +5705,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.13689374923706</v>
+        <v>3.13689351081848</v>
       </c>
       <c r="H184" t="n">
         <v>13000</v>
@@ -5763,7 +5763,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G186" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5850,7 +5850,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H189" t="n">
         <v>4000</v>
@@ -5879,7 +5879,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222205162048</v>
+        <v>3.01222229003906</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5966,7 +5966,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H193" t="n">
         <v>92500</v>
@@ -6024,7 +6024,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211382865906</v>
+        <v>2.99211406707764</v>
       </c>
       <c r="H195" t="n">
         <v>8500</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.11276340484619</v>
+        <v>3.11276364326477</v>
       </c>
       <c r="H196" t="n">
         <v>19000</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H199" t="n">
         <v>5500</v>
@@ -6169,7 +6169,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6256,7 +6256,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H203" t="n">
         <v>500</v>
@@ -6314,7 +6314,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97200584411621</v>
+        <v>2.97200560569763</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6517,7 +6517,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.74679279327393</v>
+        <v>2.74679255485535</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6546,7 +6546,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.73472809791565</v>
+        <v>2.73472785949707</v>
       </c>
       <c r="H213" t="n">
         <v>10000</v>
@@ -6575,7 +6575,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>2.77896571159363</v>
+        <v>2.77896595001221</v>
       </c>
       <c r="H214" t="n">
         <v>9000</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="n">
         <v>7500</v>
@@ -6691,7 +6691,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G218" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929109573364</v>
+        <v>2.83929085731506</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -7010,7 +7010,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H229" t="n">
         <v>1500</v>
@@ -7213,7 +7213,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G236" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H236" t="n">
         <v>2500</v>
@@ -7329,7 +7329,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G240" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H240" t="n">
         <v>2000</v>
@@ -7358,7 +7358,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H243" t="n">
         <v>500</v>
@@ -7445,7 +7445,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950730323792</v>
+        <v>2.87950754165649</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7677,7 +7677,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7764,7 +7764,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H257" t="n">
         <v>5000</v>
@@ -7851,7 +7851,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363717079163</v>
+        <v>2.90363740921021</v>
       </c>
       <c r="H258" t="n">
         <v>1000</v>
@@ -7909,7 +7909,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G260" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H260" t="n">
         <v>2000</v>
@@ -7938,7 +7938,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.9116804599762</v>
+        <v>2.91168069839478</v>
       </c>
       <c r="H261" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G262" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H262" t="n">
         <v>2000</v>
@@ -7996,7 +7996,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G263" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G264" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417876243591</v>
+        <v>3.00417900085449</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.9478759765625</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8315,7 +8315,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H274" t="n">
         <v>7000</v>
@@ -8373,7 +8373,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H276" t="n">
         <v>7000</v>
@@ -8431,7 +8431,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>2.93178915977478</v>
+        <v>2.9317889213562</v>
       </c>
       <c r="H278" t="n">
         <v>1500</v>
@@ -8460,7 +8460,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H279" t="n">
         <v>5500</v>
@@ -8489,7 +8489,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G280" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H280" t="n">
         <v>15500</v>
@@ -8518,7 +8518,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="n">
         <v>13500</v>
@@ -8692,7 +8692,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G287" t="n">
-        <v>2.9760274887085</v>
+        <v>2.97602725028992</v>
       </c>
       <c r="H287" t="n">
         <v>5500</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917536735535</v>
+        <v>3.18917512893677</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8779,7 +8779,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797693252563</v>
       </c>
       <c r="H290" t="n">
         <v>14500</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656085968018</v>
+        <v>3.44656109809875</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8924,7 +8924,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>3.38623642921448</v>
+        <v>3.38623666763306</v>
       </c>
       <c r="H295" t="n">
         <v>47000</v>
@@ -8953,7 +8953,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>3.36612796783447</v>
+        <v>3.36612820625305</v>
       </c>
       <c r="H296" t="n">
         <v>7500</v>
@@ -9011,7 +9011,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H298" t="n">
         <v>4500</v>
@@ -9040,7 +9040,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G299" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H299" t="n">
         <v>1000</v>
@@ -9069,7 +9069,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H302" t="n">
         <v>7000</v>
@@ -9214,7 +9214,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H305" t="n">
         <v>6000</v>
@@ -9301,7 +9301,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797693252563</v>
       </c>
       <c r="H308" t="n">
         <v>4000</v>
@@ -9359,7 +9359,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H310" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9504,7 +9504,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862650871277</v>
+        <v>3.45862674713135</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9591,7 +9591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9649,7 +9649,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>3.39427947998047</v>
+        <v>3.39427971839905</v>
       </c>
       <c r="H320" t="n">
         <v>14500</v>
@@ -9678,7 +9678,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H321" t="n">
         <v>8000</v>
@@ -9707,7 +9707,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.33797669410706</v>
+        <v>3.33797693252563</v>
       </c>
       <c r="H322" t="n">
         <v>8000</v>
@@ -9765,7 +9765,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H324" t="n">
         <v>6500</v>
@@ -9794,7 +9794,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H327" t="n">
         <v>2500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189035415649</v>
+        <v>3.32189011573792</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.2977602481842</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.2977602481842</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145698547363</v>
+        <v>3.24145674705505</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10664,7 +10664,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G355" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G356" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.39327478408813</v>
+        <v>3.39327454566956</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11331,7 +11331,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246496200562</v>
+        <v>3.55246472358704</v>
       </c>
       <c r="H378" t="n">
         <v>27000</v>
@@ -11389,7 +11389,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H380" t="n">
         <v>61500</v>
@@ -11418,7 +11418,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H381" t="n">
         <v>17500</v>
@@ -11447,7 +11447,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H382" t="n">
         <v>25500</v>
@@ -11534,7 +11534,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679113388062</v>
+        <v>3.73679137229919</v>
       </c>
       <c r="H385" t="n">
         <v>34000</v>
@@ -11563,7 +11563,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G386" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H386" t="n">
         <v>127500</v>
@@ -11592,7 +11592,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G387" t="n">
-        <v>3.67814207077026</v>
+        <v>3.67814183235168</v>
       </c>
       <c r="H387" t="n">
         <v>8000</v>
@@ -11650,7 +11650,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G389" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H389" t="n">
         <v>59500</v>
@@ -11708,7 +11708,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H391" t="n">
         <v>7000</v>
@@ -12027,7 +12027,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G402" t="n">
-        <v>3.61949276924133</v>
+        <v>3.61949300765991</v>
       </c>
       <c r="H402" t="n">
         <v>7000</v>
@@ -12114,7 +12114,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>3.60273575782776</v>
+        <v>3.60273599624634</v>
       </c>
       <c r="H405" t="n">
         <v>15000</v>
@@ -12230,7 +12230,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G409" t="n">
-        <v>3.54408645629883</v>
+        <v>3.54408669471741</v>
       </c>
       <c r="H409" t="n">
         <v>10500</v>
@@ -12259,7 +12259,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.51057267189026</v>
+        <v>3.51057291030884</v>
       </c>
       <c r="H410" t="n">
         <v>8000</v>
@@ -12288,7 +12288,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354557991028</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H411" t="n">
         <v>14500</v>
@@ -12346,7 +12346,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354557991028</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H413" t="n">
         <v>8500</v>
@@ -12549,7 +12549,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G420" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H420" t="n">
         <v>45000</v>
@@ -12694,7 +12694,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H425" t="n">
         <v>9000</v>
@@ -12723,7 +12723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G426" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H426" t="n">
         <v>16000</v>
@@ -12781,7 +12781,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H428" t="n">
         <v>19000</v>
@@ -12810,7 +12810,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G429" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H429" t="n">
         <v>10500</v>
@@ -13042,7 +13042,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13100,7 +13100,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G439" t="n">
-        <v>3.09165000915527</v>
+        <v>3.09165024757385</v>
       </c>
       <c r="H439" t="n">
         <v>18000</v>
@@ -13129,7 +13129,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13361,7 +13361,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H448" t="n">
         <v>43500</v>
@@ -13419,7 +13419,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G450" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G451" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H451" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H454" t="n">
         <v>22000</v>
@@ -13564,7 +13564,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H455" t="n">
         <v>3500</v>
@@ -13593,7 +13593,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G456" t="n">
-        <v>3.00786519050598</v>
+        <v>3.00786542892456</v>
       </c>
       <c r="H456" t="n">
         <v>17000</v>
@@ -13970,7 +13970,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H469" t="n">
         <v>19500</v>
@@ -13999,7 +13999,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H470" t="n">
         <v>500</v>
@@ -14289,7 +14289,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H480" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H481" t="n">
         <v>1000</v>
@@ -14347,7 +14347,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H486" t="n">
         <v>26000</v>
@@ -14521,7 +14521,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H488" t="n">
         <v>9500</v>
@@ -14637,7 +14637,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H492" t="n">
         <v>13500</v>
@@ -14695,7 +14695,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H494" t="n">
         <v>5500</v>
@@ -14840,7 +14840,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H499" t="n">
         <v>14000</v>
@@ -14898,7 +14898,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H501" t="n">
         <v>21500</v>
@@ -14956,7 +14956,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G503" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H503" t="n">
         <v>72000</v>
@@ -15304,7 +15304,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G515" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H515" t="n">
         <v>32500</v>
@@ -15391,7 +15391,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H518" t="n">
         <v>16500</v>
@@ -15420,7 +15420,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G519" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H519" t="n">
         <v>19000</v>
@@ -15449,7 +15449,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H520" t="n">
         <v>12000</v>
@@ -15594,7 +15594,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G525" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H525" t="n">
         <v>20500</v>
@@ -15710,7 +15710,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G529" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H529" t="n">
         <v>28000</v>
@@ -15768,7 +15768,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H531" t="n">
         <v>58000</v>
@@ -15884,7 +15884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H535" t="n">
         <v>24500</v>
@@ -15913,7 +15913,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H536" t="n">
         <v>1500</v>
@@ -15942,7 +15942,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H537" t="n">
         <v>21500</v>
@@ -16029,7 +16029,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G540" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H540" t="n">
         <v>16500</v>
@@ -16203,7 +16203,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G546" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H546" t="n">
         <v>20500</v>
@@ -16290,7 +16290,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G549" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H549" t="n">
         <v>1500</v>
@@ -16377,7 +16377,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G552" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H552" t="n">
         <v>11000</v>
@@ -16406,7 +16406,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G553" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H553" t="n">
         <v>25500</v>
@@ -16696,7 +16696,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G563" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H563" t="n">
         <v>37500</v>
@@ -16725,7 +16725,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H564" t="n">
         <v>10000</v>
@@ -16870,7 +16870,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.89056730270386</v>
+        <v>2.89056706428528</v>
       </c>
       <c r="H569" t="n">
         <v>4000</v>
@@ -16986,7 +16986,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G573" t="n">
-        <v>2.90732431411743</v>
+        <v>2.90732407569885</v>
       </c>
       <c r="H573" t="n">
         <v>8000</v>
@@ -17102,7 +17102,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H577" t="n">
         <v>25000</v>
@@ -17247,7 +17247,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H582" t="n">
         <v>42500</v>
@@ -17334,7 +17334,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H585" t="n">
         <v>3000</v>
@@ -17363,7 +17363,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>3.10840702056885</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H586" t="n">
         <v>9000</v>
@@ -17421,7 +17421,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G588" t="n">
-        <v>3.12516403198242</v>
+        <v>3.12516379356384</v>
       </c>
       <c r="H588" t="n">
         <v>4500</v>
@@ -17595,7 +17595,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>3.17543482780457</v>
+        <v>3.17543458938599</v>
       </c>
       <c r="H594" t="n">
         <v>10000</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.29273295402527</v>
+        <v>3.29273319244385</v>
       </c>
       <c r="H598" t="n">
         <v>15000</v>
@@ -17856,7 +17856,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>3.32624673843384</v>
+        <v>3.32624697685242</v>
       </c>
       <c r="H603" t="n">
         <v>21500</v>
@@ -18494,7 +18494,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G625" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H625" t="n">
         <v>7000</v>
@@ -18639,7 +18639,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H630" t="n">
         <v>8500</v>
@@ -18755,7 +18755,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H634" t="n">
         <v>3000</v>
@@ -18784,7 +18784,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H635" t="n">
         <v>11000</v>
@@ -18929,7 +18929,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H640" t="n">
         <v>10000</v>
@@ -18958,7 +18958,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.13634181022644</v>
+        <v>3.13634204864502</v>
       </c>
       <c r="H641" t="n">
         <v>8000</v>
@@ -18987,7 +18987,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H642" t="n">
         <v>67500</v>
@@ -19045,7 +19045,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G644" t="n">
-        <v>3.06645154953003</v>
+        <v>3.06645131111145</v>
       </c>
       <c r="H644" t="n">
         <v>10000</v>
@@ -19103,7 +19103,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H646" t="n">
         <v>7500</v>
@@ -19248,7 +19248,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G651" t="n">
-        <v>3.11886954307556</v>
+        <v>3.11886930465698</v>
       </c>
       <c r="H651" t="n">
         <v>17500</v>
@@ -19277,7 +19277,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G652" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H652" t="n">
         <v>22500</v>
@@ -19306,7 +19306,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>3.22370529174805</v>
+        <v>3.22370553016663</v>
       </c>
       <c r="H653" t="n">
         <v>23500</v>
@@ -19393,7 +19393,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>3.24117803573608</v>
+        <v>3.24117827415466</v>
       </c>
       <c r="H656" t="n">
         <v>35500</v>
@@ -19625,7 +19625,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G664" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H664" t="n">
         <v>13500</v>
@@ -19654,7 +19654,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>3.34601402282715</v>
+        <v>3.34601378440857</v>
       </c>
       <c r="H665" t="n">
         <v>6000</v>
@@ -19683,7 +19683,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>3.36348676681519</v>
+        <v>3.36348652839661</v>
       </c>
       <c r="H666" t="n">
         <v>31500</v>
@@ -19741,7 +19741,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H668" t="n">
         <v>21500</v>
@@ -19915,7 +19915,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H674" t="n">
         <v>52000</v>
@@ -19944,7 +19944,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H675" t="n">
         <v>9500</v>
@@ -19973,7 +19973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H676" t="n">
         <v>26000</v>
@@ -20089,7 +20089,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H680" t="n">
         <v>6500</v>
@@ -20408,7 +20408,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H691" t="n">
         <v>6500</v>
@@ -20437,7 +20437,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>3.31106877326965</v>
+        <v>3.31106853485107</v>
       </c>
       <c r="H692" t="n">
         <v>12500</v>
@@ -20988,7 +20988,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G711" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H711" t="n">
         <v>25000</v>
@@ -21075,7 +21075,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G714" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H714" t="n">
         <v>12500</v>
@@ -21162,7 +21162,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G717" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H717" t="n">
         <v>38000</v>
@@ -21307,7 +21307,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G722" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H722" t="n">
         <v>33500</v>
@@ -21423,7 +21423,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H726" t="n">
         <v>12500</v>
@@ -21481,7 +21481,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G728" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H728" t="n">
         <v>15000</v>
@@ -22873,7 +22873,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>3.53821349143982</v>
+        <v>3.53821325302124</v>
       </c>
       <c r="H776" t="n">
         <v>49000</v>
@@ -23221,7 +23221,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G788" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H788" t="n">
         <v>12500</v>
@@ -23250,7 +23250,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G789" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H789" t="n">
         <v>9500</v>
@@ -23395,7 +23395,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G794" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H794" t="n">
         <v>14500</v>
@@ -23511,7 +23511,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.59063148498535</v>
+        <v>3.59063124656677</v>
       </c>
       <c r="H798" t="n">
         <v>8000</v>
@@ -23569,7 +23569,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85272097587585</v>
+        <v>3.85272121429443</v>
       </c>
       <c r="H800" t="n">
         <v>42000</v>
@@ -23685,7 +23685,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G804" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H804" t="n">
         <v>13500</v>
@@ -23743,7 +23743,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G806" t="n">
-        <v>3.75662136077881</v>
+        <v>3.75662159919739</v>
       </c>
       <c r="H806" t="n">
         <v>12500</v>
@@ -23801,7 +23801,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>3.7915666103363</v>
+        <v>3.79156684875488</v>
       </c>
       <c r="H808" t="n">
         <v>3500</v>
@@ -23917,7 +23917,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G812" t="n">
-        <v>3.8352484703064</v>
+        <v>3.83524823188782</v>
       </c>
       <c r="H812" t="n">
         <v>18000</v>
@@ -24062,7 +24062,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G817" t="n">
-        <v>3.66052174568176</v>
+        <v>3.66052198410034</v>
       </c>
       <c r="H817" t="n">
         <v>36000</v>
@@ -24294,7 +24294,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>3.69546699523926</v>
+        <v>3.69546723365784</v>
       </c>
       <c r="H825" t="n">
         <v>17500</v>
@@ -24381,7 +24381,7 @@
         <v>4.25</v>
       </c>
       <c r="G828" t="n">
-        <v>3.71293973922729</v>
+        <v>3.71293997764587</v>
       </c>
       <c r="H828" t="n">
         <v>10000</v>
@@ -24410,7 +24410,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G829" t="n">
-        <v>3.70420336723328</v>
+        <v>3.7042031288147</v>
       </c>
       <c r="H829" t="n">
         <v>6500</v>
@@ -24700,7 +24700,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>4.32448291778564</v>
+        <v>4.32448244094849</v>
       </c>
       <c r="H839" t="n">
         <v>26000</v>
@@ -24990,7 +24990,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G849" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H849" t="n">
         <v>14000</v>
@@ -25048,7 +25048,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.4904727935791</v>
+        <v>4.49047327041626</v>
       </c>
       <c r="H851" t="n">
         <v>14000</v>
@@ -25106,7 +25106,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G853" t="n">
-        <v>4.52541828155518</v>
+        <v>4.52541780471802</v>
       </c>
       <c r="H853" t="n">
         <v>12000</v>
@@ -25222,7 +25222,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G857" t="n">
-        <v>4.6302547454834</v>
+        <v>4.63025426864624</v>
       </c>
       <c r="H857" t="n">
         <v>8500</v>
@@ -25309,7 +25309,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G860" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H860" t="n">
         <v>4000</v>
@@ -25396,7 +25396,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G863" t="n">
-        <v>4.73509073257446</v>
+        <v>4.7350902557373</v>
       </c>
       <c r="H863" t="n">
         <v>3500</v>
@@ -36103,6 +36103,35 @@
         <v>4500</v>
       </c>
       <c r="I1232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1233" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>7.73999977111816</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>7.55999994277954</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1233" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.3675000667572</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62516021728516</v>
+        <v>2.62516045570374</v>
       </c>
       <c r="H2" t="n">
         <v>1387000</v>
@@ -456,7 +456,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66764616966248</v>
+        <v>2.66764640808105</v>
       </c>
       <c r="H3" t="n">
         <v>383000</v>
@@ -485,7 +485,7 @@
         <v>4.17700004577637</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25621247291565</v>
+        <v>3.25621223449707</v>
       </c>
       <c r="H4" t="n">
         <v>912000</v>
@@ -514,7 +514,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805215835571</v>
+        <v>4.20805168151855</v>
       </c>
       <c r="H5" t="n">
         <v>1121500</v>
@@ -601,7 +601,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929111480713</v>
       </c>
       <c r="H8" t="n">
         <v>594000</v>
@@ -688,7 +688,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H11" t="n">
         <v>83500</v>
@@ -717,7 +717,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96794843673706</v>
+        <v>3.9679479598999</v>
       </c>
       <c r="H12" t="n">
         <v>65500</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136517524719</v>
+        <v>3.76136541366577</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -775,7 +775,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574400901794</v>
+        <v>3.97574329376221</v>
       </c>
       <c r="H14" t="n">
         <v>84000</v>
@@ -833,7 +833,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H16" t="n">
         <v>208500</v>
@@ -862,7 +862,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H17" t="n">
         <v>60000</v>
@@ -891,7 +891,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G18" t="n">
-        <v>4.27977132797241</v>
+        <v>4.27977180480957</v>
       </c>
       <c r="H18" t="n">
         <v>24500</v>
@@ -920,7 +920,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H19" t="n">
         <v>93500</v>
@@ -949,7 +949,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G20" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H20" t="n">
         <v>61500</v>
@@ -978,7 +978,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26417970657349</v>
+        <v>4.26418018341064</v>
       </c>
       <c r="H21" t="n">
         <v>24000</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756761550903</v>
+        <v>4.28756666183472</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1094,7 +1094,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G25" t="n">
-        <v>4.29536294937134</v>
+        <v>4.29536247253418</v>
       </c>
       <c r="H25" t="n">
         <v>60000</v>
@@ -1123,7 +1123,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.24858856201172</v>
+        <v>4.24858903884888</v>
       </c>
       <c r="H26" t="n">
         <v>26000</v>
@@ -1181,7 +1181,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961141586304</v>
+        <v>4.20961093902588</v>
       </c>
       <c r="H28" t="n">
         <v>43500</v>
@@ -1239,7 +1239,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929111480713</v>
       </c>
       <c r="H30" t="n">
         <v>54500</v>
@@ -1297,7 +1297,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929063796997</v>
+        <v>4.06929111480713</v>
       </c>
       <c r="H32" t="n">
         <v>11500</v>
@@ -1326,7 +1326,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G33" t="n">
-        <v>4.0069260597229</v>
+        <v>4.00692558288574</v>
       </c>
       <c r="H33" t="n">
         <v>16000</v>
@@ -1413,7 +1413,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1442,7 +1442,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H37" t="n">
         <v>39500</v>
@@ -1471,7 +1471,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G38" t="n">
-        <v>3.88999271392822</v>
+        <v>3.88999223709106</v>
       </c>
       <c r="H38" t="n">
         <v>32000</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676567077637</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676567077637</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1558,7 +1558,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219714164734</v>
+        <v>3.88219666481018</v>
       </c>
       <c r="H41" t="n">
         <v>10500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050366401672</v>
+        <v>3.87050342559814</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778828620911</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1645,7 +1645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.8510148525238</v>
+        <v>3.85101461410522</v>
       </c>
       <c r="H44" t="n">
         <v>25000</v>
@@ -1674,7 +1674,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711623191833</v>
       </c>
       <c r="H45" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>3.96015238761902</v>
+        <v>3.96015286445618</v>
       </c>
       <c r="H47" t="n">
         <v>30500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050366401672</v>
+        <v>3.87050342559814</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628569602966</v>
+        <v>3.72628617286682</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1819,7 +1819,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187684059143</v>
+        <v>3.74187707901001</v>
       </c>
       <c r="H50" t="n">
         <v>2500</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088472366333</v>
+        <v>3.55088520050049</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1877,7 +1877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G52" t="n">
-        <v>3.30922174453735</v>
+        <v>3.30922198295593</v>
       </c>
       <c r="H52" t="n">
         <v>36500</v>
@@ -1906,7 +1906,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704853057861</v>
+        <v>3.08704829216003</v>
       </c>
       <c r="H53" t="n">
         <v>44000</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.4573380947113</v>
+        <v>3.45733785629272</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2080,7 +2080,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.34430241584778</v>
+        <v>3.3443021774292</v>
       </c>
       <c r="H59" t="n">
         <v>18500</v>
@@ -2167,7 +2167,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.38328003883362</v>
+        <v>3.3832802772522</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2312,7 +2312,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G67" t="n">
-        <v>3.92117500305176</v>
+        <v>3.92117524147034</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133539199829</v>
+        <v>3.99133467674255</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2370,7 +2370,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.99913096427917</v>
+        <v>3.99913048744202</v>
       </c>
       <c r="H69" t="n">
         <v>13000</v>
@@ -2399,7 +2399,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>4.03810787200928</v>
+        <v>4.03810834884644</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456100463867</v>
+        <v>3.94456171989441</v>
       </c>
       <c r="H71" t="n">
         <v>13500</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676567077637</v>
+        <v>3.93676614761353</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2486,7 +2486,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337919235229</v>
+        <v>3.91337943077087</v>
       </c>
       <c r="H73" t="n">
         <v>6500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778828620911</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2573,7 +2573,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G76" t="n">
-        <v>3.82762718200684</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H76" t="n">
         <v>3500</v>
@@ -2602,7 +2602,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219714164734</v>
+        <v>3.88219666481018</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219714164734</v>
+        <v>3.88219666481018</v>
       </c>
       <c r="H81" t="n">
         <v>1500</v>
@@ -2747,7 +2747,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711623191833</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G83" t="n">
-        <v>3.88999271392822</v>
+        <v>3.88999223709106</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778828620911</v>
+        <v>3.89778804779053</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2834,7 +2834,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>3.81593465805054</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H85" t="n">
         <v>2500</v>
@@ -2863,7 +2863,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>3.84711670875549</v>
+        <v>3.84711623191833</v>
       </c>
       <c r="H86" t="n">
         <v>1000</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321928024292</v>
+        <v>3.84321880340576</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>3.82762718200684</v>
+        <v>3.82762789726257</v>
       </c>
       <c r="H90" t="n">
         <v>500</v>
@@ -3037,7 +3037,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G92" t="n">
-        <v>3.81593465805054</v>
+        <v>3.81593489646912</v>
       </c>
       <c r="H92" t="n">
         <v>6500</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983232498169</v>
+        <v>3.81983256340027</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3124,7 +3124,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.79644536972046</v>
+        <v>3.7964460849762</v>
       </c>
       <c r="H95" t="n">
         <v>7500</v>
@@ -3153,7 +3153,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459759712219</v>
+        <v>3.82459735870361</v>
       </c>
       <c r="H97" t="n">
         <v>2000</v>
@@ -3211,7 +3211,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88894414901733</v>
+        <v>3.88894391059875</v>
       </c>
       <c r="H98" t="n">
         <v>5000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111730575562</v>
+        <v>3.92111754417419</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.9372034072876</v>
+        <v>3.93720364570618</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3356,7 +3356,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.90503025054932</v>
+        <v>3.90503072738647</v>
       </c>
       <c r="H104" t="n">
         <v>17500</v>
@@ -3472,7 +3472,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709518432617</v>
+        <v>3.91709566116333</v>
       </c>
       <c r="H107" t="n">
         <v>21000</v>
@@ -3501,7 +3501,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G108" t="n">
-        <v>3.96535515785217</v>
+        <v>3.96535539627075</v>
       </c>
       <c r="H108" t="n">
         <v>10500</v>
@@ -3530,7 +3530,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>4.08600521087646</v>
+        <v>4.08600473403931</v>
       </c>
       <c r="H109" t="n">
         <v>17000</v>
@@ -3617,7 +3617,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G112" t="n">
-        <v>4.21469831466675</v>
+        <v>4.21469783782959</v>
       </c>
       <c r="H112" t="n">
         <v>17000</v>
@@ -3762,7 +3762,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209178924561</v>
+        <v>4.10209131240845</v>
       </c>
       <c r="H117" t="n">
         <v>11000</v>
@@ -3820,7 +3820,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383157730103</v>
+        <v>4.05383205413818</v>
       </c>
       <c r="H119" t="n">
         <v>3500</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133399009705</v>
+        <v>3.96133327484131</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.8768789768219</v>
+        <v>3.87687873840332</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -3965,7 +3965,7 @@
         <v>4.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82057547569275</v>
+        <v>3.82057571411133</v>
       </c>
       <c r="H124" t="n">
         <v>4500</v>
@@ -3994,7 +3994,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.80046725273132</v>
+        <v>3.8004674911499</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949300765991</v>
+        <v>3.61949253082275</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4139,7 +4139,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340595245361</v>
+        <v>3.60340619087219</v>
       </c>
       <c r="H130" t="n">
         <v>1500</v>
@@ -4197,7 +4197,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G132" t="n">
-        <v>3.73209881782532</v>
+        <v>3.7320990562439</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992566108704</v>
+        <v>3.69992589950562</v>
       </c>
       <c r="H133" t="n">
         <v>5000</v>
@@ -4255,7 +4255,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970945358276</v>
+        <v>3.65970921516418</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G136" t="n">
-        <v>3.5591676235199</v>
+        <v>3.55916786193848</v>
       </c>
       <c r="H136" t="n">
         <v>10500</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482083320618</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731961250305</v>
+        <v>3.58731937408447</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731961250305</v>
+        <v>3.58731937408447</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482107162476</v>
+        <v>3.49482083320618</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4661,7 +4661,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G148" t="n">
-        <v>3.5591676235199</v>
+        <v>3.55916786193848</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4719,7 +4719,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H150" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>3.57525444030762</v>
+        <v>3.5752546787262</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905940055847</v>
+        <v>3.53905963897705</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905940055847</v>
+        <v>3.53905963897705</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H154" t="n">
         <v>4000</v>
@@ -4922,7 +4922,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112433433533</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112433433533</v>
+        <v>3.55112457275391</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677778244019</v>
+        <v>3.48677802085876</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253993034363</v>
+        <v>3.44253969192505</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5096,7 +5096,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G163" t="n">
-        <v>3.40232348442078</v>
+        <v>3.4023232460022</v>
       </c>
       <c r="H163" t="n">
         <v>5500</v>
@@ -5125,7 +5125,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>3.41036605834961</v>
+        <v>3.41036629676819</v>
       </c>
       <c r="H164" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253993034363</v>
+        <v>3.44253969192505</v>
       </c>
       <c r="H166" t="n">
         <v>500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.49884271621704</v>
+        <v>3.4988431930542</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5241,7 +5241,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>3.49079990386963</v>
+        <v>3.49079966545105</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5270,7 +5270,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G169" t="n">
-        <v>3.45862674713135</v>
+        <v>3.45862650871277</v>
       </c>
       <c r="H169" t="n">
         <v>10500</v>
@@ -5386,7 +5386,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H173" t="n">
         <v>1500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>3.33797693252563</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H176" t="n">
         <v>2500</v>
@@ -5502,7 +5502,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.31384658813477</v>
+        <v>3.31384634971619</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.2334132194519</v>
+        <v>3.23341345787048</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5560,7 +5560,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H179" t="n">
         <v>3500</v>
@@ -5589,7 +5589,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H180" t="n">
         <v>2000</v>
@@ -5618,7 +5618,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H181" t="n">
         <v>2500</v>
@@ -5647,7 +5647,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711019515991</v>
+        <v>3.17711043357849</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H183" t="n">
         <v>21500</v>
@@ -5705,7 +5705,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>3.13689351081848</v>
+        <v>3.13689374923706</v>
       </c>
       <c r="H184" t="n">
         <v>13000</v>
@@ -5734,7 +5734,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08863377571106</v>
+        <v>3.08863353729248</v>
       </c>
       <c r="H185" t="n">
         <v>1000</v>
@@ -5821,7 +5821,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080693244934</v>
+        <v>3.12080717086792</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.0564603805542</v>
+        <v>3.05646061897278</v>
       </c>
       <c r="H189" t="n">
         <v>4000</v>
@@ -5937,7 +5937,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>3.03635239601135</v>
+        <v>3.03635215759277</v>
       </c>
       <c r="H192" t="n">
         <v>49500</v>
@@ -5966,7 +5966,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624369621277</v>
+        <v>3.01624393463135</v>
       </c>
       <c r="H193" t="n">
         <v>92500</v>
@@ -6024,7 +6024,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211406707764</v>
+        <v>2.99211382865906</v>
       </c>
       <c r="H195" t="n">
         <v>8500</v>
@@ -6111,7 +6111,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H199" t="n">
         <v>5500</v>
@@ -6198,7 +6198,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G201" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H201" t="n">
         <v>5000</v>
@@ -6227,7 +6227,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G202" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.71059775352478</v>
+        <v>2.7105975151062</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6517,7 +6517,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G212" t="n">
-        <v>2.74679255485535</v>
+        <v>2.74679279327393</v>
       </c>
       <c r="H212" t="n">
         <v>1500</v>
@@ -6604,7 +6604,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H215" t="n">
         <v>5500</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H216" t="n">
         <v>7500</v>
@@ -6662,7 +6662,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929085731506</v>
+        <v>2.83929109573364</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -6836,7 +6836,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331250190735</v>
+        <v>2.84331274032593</v>
       </c>
       <c r="H223" t="n">
         <v>1000</v>
@@ -6894,7 +6894,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H225" t="n">
         <v>4500</v>
@@ -6923,7 +6923,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G226" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H226" t="n">
         <v>2500</v>
@@ -6952,7 +6952,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G227" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H227" t="n">
         <v>3000</v>
@@ -6981,7 +6981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994067192078</v>
+        <v>2.95994091033936</v>
       </c>
       <c r="H228" t="n">
         <v>5000</v>
@@ -7010,7 +7010,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581104278564</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H229" t="n">
         <v>1500</v>
@@ -7068,7 +7068,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G231" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H231" t="n">
         <v>1500</v>
@@ -7126,7 +7126,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H233" t="n">
         <v>500</v>
@@ -7242,7 +7242,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G237" t="n">
-        <v>2.9277675151825</v>
+        <v>2.92776727676392</v>
       </c>
       <c r="H237" t="n">
         <v>1000</v>
@@ -7416,7 +7416,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G243" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H243" t="n">
         <v>500</v>
@@ -7445,7 +7445,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G244" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G246" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950754165649</v>
+        <v>2.87950730323792</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7590,7 +7590,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G249" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7619,7 +7619,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G250" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -7677,7 +7677,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559388160706</v>
+        <v>2.89559412002563</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7764,7 +7764,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581104278564</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374587059021</v>
+        <v>2.92374563217163</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559388160706</v>
+        <v>2.89559412002563</v>
       </c>
       <c r="H257" t="n">
         <v>5000</v>
@@ -7851,7 +7851,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G258" t="n">
-        <v>2.90363740921021</v>
+        <v>2.90363717079163</v>
       </c>
       <c r="H258" t="n">
         <v>1000</v>
@@ -7880,7 +7880,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H259" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H265" t="n">
         <v>500</v>
@@ -8083,7 +8083,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8112,7 +8112,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417900085449</v>
+        <v>3.00417876243591</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8141,7 +8141,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H268" t="n">
         <v>2000</v>
@@ -8170,7 +8170,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H269" t="n">
         <v>11500</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8228,7 +8228,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983244895935</v>
+        <v>2.93983221054077</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.94787573814392</v>
+        <v>2.94787549972534</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8344,7 +8344,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G275" t="n">
-        <v>2.94385385513306</v>
+        <v>2.94385409355164</v>
       </c>
       <c r="H275" t="n">
         <v>3500</v>
@@ -8373,7 +8373,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581104278564</v>
+        <v>2.93581080436707</v>
       </c>
       <c r="H276" t="n">
         <v>7000</v>
@@ -8402,7 +8402,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>2.91972422599792</v>
+        <v>2.91972398757935</v>
       </c>
       <c r="H277" t="n">
         <v>4000</v>
@@ -8518,7 +8518,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407077789307</v>
+        <v>2.98407053947449</v>
       </c>
       <c r="H281" t="n">
         <v>13500</v>
@@ -8576,7 +8576,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H283" t="n">
         <v>17500</v>
@@ -8605,7 +8605,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591926574707</v>
+        <v>2.95591878890991</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H285" t="n">
         <v>37500</v>
@@ -8663,7 +8663,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98809242248535</v>
+        <v>2.98809218406677</v>
       </c>
       <c r="H286" t="n">
         <v>33000</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917512893677</v>
+        <v>3.18917536735535</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8779,7 +8779,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G290" t="n">
-        <v>3.33797693252563</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H290" t="n">
         <v>14500</v>
@@ -8808,7 +8808,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047451972961</v>
+        <v>3.43047475814819</v>
       </c>
       <c r="H291" t="n">
         <v>70000</v>
@@ -8837,7 +8837,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.52699446678162</v>
+        <v>3.5269947052002</v>
       </c>
       <c r="H292" t="n">
         <v>17000</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656109809875</v>
+        <v>3.44656133651733</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9011,7 +9011,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>3.37015008926392</v>
+        <v>3.37014985084534</v>
       </c>
       <c r="H298" t="n">
         <v>4500</v>
@@ -9040,7 +9040,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G299" t="n">
-        <v>3.37015008926392</v>
+        <v>3.37014985084534</v>
       </c>
       <c r="H299" t="n">
         <v>1000</v>
@@ -9069,7 +9069,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>3.37015008926392</v>
+        <v>3.37014985084534</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.37417149543762</v>
+        <v>3.3741717338562</v>
       </c>
       <c r="H302" t="n">
         <v>7000</v>
@@ -9156,7 +9156,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>3.35004162788391</v>
+        <v>3.35004138946533</v>
       </c>
       <c r="H303" t="n">
         <v>1500</v>
@@ -9214,7 +9214,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.37417149543762</v>
+        <v>3.3741717338562</v>
       </c>
       <c r="H305" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9301,7 +9301,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G308" t="n">
-        <v>3.33797693252563</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H308" t="n">
         <v>4000</v>
@@ -9359,7 +9359,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H310" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253993034363</v>
+        <v>3.44253969192505</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547088623047</v>
+        <v>3.61547064781189</v>
       </c>
       <c r="H313" t="n">
         <v>9000</v>
@@ -9504,7 +9504,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>3.45862674713135</v>
+        <v>3.45862650871277</v>
       </c>
       <c r="H315" t="n">
         <v>500</v>
@@ -9533,7 +9533,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G316" t="n">
-        <v>3.20526170730591</v>
+        <v>3.20526194572449</v>
       </c>
       <c r="H316" t="n">
         <v>18000</v>
@@ -9591,7 +9591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819290161133</v>
+        <v>3.37819314002991</v>
       </c>
       <c r="H321" t="n">
         <v>8000</v>
@@ -9707,7 +9707,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.33797693252563</v>
+        <v>3.33797669410706</v>
       </c>
       <c r="H322" t="n">
         <v>8000</v>
@@ -9736,7 +9736,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H323" t="n">
         <v>7500</v>
@@ -9765,7 +9765,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H324" t="n">
         <v>6500</v>
@@ -9794,7 +9794,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754332542419</v>
+        <v>3.25754356384277</v>
       </c>
       <c r="H327" t="n">
         <v>2500</v>
@@ -10026,7 +10026,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10055,7 +10055,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H334" t="n">
         <v>4500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32189011573792</v>
+        <v>3.32188987731934</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993340492249</v>
+        <v>3.32993316650391</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29776000976562</v>
+        <v>3.29775977134705</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10200,7 +10200,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>3.31384658813477</v>
+        <v>3.31384634971619</v>
       </c>
       <c r="H339" t="n">
         <v>8000</v>
@@ -10229,7 +10229,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.30580353736877</v>
+        <v>3.3058032989502</v>
       </c>
       <c r="H340" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H342" t="n">
         <v>8000</v>
@@ -10316,7 +10316,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971672058105</v>
+        <v>3.28971695899963</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145674705505</v>
+        <v>3.24145698547363</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.24950003623962</v>
+        <v>3.24949979782104</v>
       </c>
       <c r="H346" t="n">
         <v>67500</v>
@@ -10432,7 +10432,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H347" t="n">
         <v>500</v>
@@ -10461,7 +10461,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.24950003623962</v>
+        <v>3.24949979782104</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732687950134</v>
+        <v>3.21732664108276</v>
       </c>
       <c r="H350" t="n">
         <v>3500</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H352" t="n">
         <v>500</v>
@@ -10722,7 +10722,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.25084066390991</v>
+        <v>3.25084090232849</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H359" t="n">
         <v>34500</v>
@@ -10809,7 +10809,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>3.34300374984741</v>
+        <v>3.34300351142883</v>
       </c>
       <c r="H360" t="n">
         <v>4000</v>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.3513822555542</v>
+        <v>3.35138201713562</v>
       </c>
       <c r="H361" t="n">
         <v>3500</v>
@@ -10867,7 +10867,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H362" t="n">
         <v>16500</v>
@@ -10896,7 +10896,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>3.38489603996277</v>
+        <v>3.38489580154419</v>
       </c>
       <c r="H367" t="n">
         <v>25000</v>
@@ -11070,7 +11070,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H369" t="n">
         <v>9000</v>
@@ -11099,7 +11099,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192384719849</v>
+        <v>3.45192337036133</v>
       </c>
       <c r="H370" t="n">
         <v>10500</v>
@@ -11128,7 +11128,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H372" t="n">
         <v>13500</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H373" t="n">
         <v>10500</v>
@@ -11215,7 +11215,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>3.4854371547699</v>
+        <v>3.48543739318848</v>
       </c>
       <c r="H374" t="n">
         <v>6000</v>
@@ -11244,7 +11244,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G375" t="n">
-        <v>3.53570795059204</v>
+        <v>3.53570818901062</v>
       </c>
       <c r="H375" t="n">
         <v>28000</v>
@@ -11273,7 +11273,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H376" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895093917847</v>
+        <v>3.51895117759705</v>
       </c>
       <c r="H377" t="n">
         <v>4000</v>
@@ -11331,7 +11331,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246472358704</v>
+        <v>3.55246496200562</v>
       </c>
       <c r="H378" t="n">
         <v>27000</v>
@@ -11360,7 +11360,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H379" t="n">
         <v>11500</v>
@@ -11476,7 +11476,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H383" t="n">
         <v>33500</v>
@@ -11505,7 +11505,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003436088562</v>
+        <v>3.72003412246704</v>
       </c>
       <c r="H384" t="n">
         <v>14000</v>
@@ -11534,7 +11534,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679137229919</v>
+        <v>3.73679113388062</v>
       </c>
       <c r="H385" t="n">
         <v>34000</v>
@@ -11621,7 +11621,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>3.64462804794312</v>
+        <v>3.64462828636169</v>
       </c>
       <c r="H388" t="n">
         <v>35500</v>
@@ -11737,7 +11737,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H392" t="n">
         <v>15500</v>
@@ -11766,7 +11766,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>3.46030235290527</v>
+        <v>3.46030211448669</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11795,7 +11795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H394" t="n">
         <v>16500</v>
@@ -11824,7 +11824,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H395" t="n">
         <v>10500</v>
@@ -11882,7 +11882,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H397" t="n">
         <v>14000</v>
@@ -11911,7 +11911,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H398" t="n">
         <v>15000</v>
@@ -11940,7 +11940,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>3.66138505935669</v>
+        <v>3.66138482093811</v>
       </c>
       <c r="H399" t="n">
         <v>25000</v>
@@ -12143,7 +12143,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>3.57760047912598</v>
+        <v>3.57760071754456</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12172,7 +12172,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>3.4854371547699</v>
+        <v>3.48543739318848</v>
       </c>
       <c r="H407" t="n">
         <v>10000</v>
@@ -12201,7 +12201,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>3.52732968330383</v>
+        <v>3.52732992172241</v>
       </c>
       <c r="H408" t="n">
         <v>5000</v>
@@ -12288,7 +12288,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H411" t="n">
         <v>14500</v>
@@ -12317,7 +12317,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.46868062019348</v>
+        <v>3.4686803817749</v>
       </c>
       <c r="H412" t="n">
         <v>27500</v>
@@ -12346,7 +12346,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.4435453414917</v>
+        <v>3.44354510307312</v>
       </c>
       <c r="H413" t="n">
         <v>8500</v>
@@ -12462,7 +12462,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516683578491</v>
+        <v>3.43516659736633</v>
       </c>
       <c r="H417" t="n">
         <v>10500</v>
@@ -12520,7 +12520,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219392776489</v>
+        <v>3.50219416618347</v>
       </c>
       <c r="H419" t="n">
         <v>9000</v>
@@ -12578,7 +12578,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H421" t="n">
         <v>28500</v>
@@ -12607,7 +12607,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435444831848</v>
+        <v>3.28435468673706</v>
       </c>
       <c r="H422" t="n">
         <v>11500</v>
@@ -12636,7 +12636,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H423" t="n">
         <v>57000</v>
@@ -12665,7 +12665,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G424" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H424" t="n">
         <v>9500</v>
@@ -12694,7 +12694,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840678215027</v>
       </c>
       <c r="H425" t="n">
         <v>9000</v>
@@ -12955,7 +12955,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H434" t="n">
         <v>19000</v>
@@ -13042,7 +13042,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840678215027</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13129,7 +13129,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840678215027</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13245,7 +13245,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>3.04137945175171</v>
+        <v>3.04137921333313</v>
       </c>
       <c r="H444" t="n">
         <v>7500</v>
@@ -13361,7 +13361,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840678215027</v>
       </c>
       <c r="H448" t="n">
         <v>43500</v>
@@ -13477,7 +13477,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G452" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H452" t="n">
         <v>55500</v>
@@ -13506,7 +13506,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G453" t="n">
-        <v>3.04137945175171</v>
+        <v>3.04137921333313</v>
       </c>
       <c r="H453" t="n">
         <v>18500</v>
@@ -13535,7 +13535,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.05813646316528</v>
+        <v>3.0581362247467</v>
       </c>
       <c r="H454" t="n">
         <v>22000</v>
@@ -13564,7 +13564,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.05813646316528</v>
+        <v>3.0581362247467</v>
       </c>
       <c r="H455" t="n">
         <v>3500</v>
@@ -13622,7 +13622,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G457" t="n">
-        <v>3.01624369621277</v>
+        <v>3.01624393463135</v>
       </c>
       <c r="H457" t="n">
         <v>1000</v>
@@ -13738,7 +13738,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H461" t="n">
         <v>20500</v>
@@ -13767,7 +13767,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H462" t="n">
         <v>12000</v>
@@ -13796,7 +13796,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H463" t="n">
         <v>26000</v>
@@ -14289,7 +14289,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353949546814</v>
+        <v>2.82353925704956</v>
       </c>
       <c r="H480" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353949546814</v>
+        <v>2.82353925704956</v>
       </c>
       <c r="H481" t="n">
         <v>1000</v>
@@ -14347,7 +14347,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029674530029</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029674530029</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H486" t="n">
         <v>26000</v>
@@ -14521,7 +14521,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H488" t="n">
         <v>9500</v>
@@ -14579,7 +14579,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H490" t="n">
         <v>13500</v>
@@ -14637,7 +14637,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353949546814</v>
+        <v>2.82353925704956</v>
       </c>
       <c r="H492" t="n">
         <v>13500</v>
@@ -14695,7 +14695,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H494" t="n">
         <v>5500</v>
@@ -14840,7 +14840,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>2.79002571105957</v>
+        <v>2.79002547264099</v>
       </c>
       <c r="H499" t="n">
         <v>14000</v>
@@ -14869,7 +14869,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G500" t="n">
-        <v>2.81516098976135</v>
+        <v>2.81516075134277</v>
       </c>
       <c r="H500" t="n">
         <v>23500</v>
@@ -14898,7 +14898,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029674530029</v>
+        <v>2.84029650688171</v>
       </c>
       <c r="H501" t="n">
         <v>21500</v>
@@ -15014,7 +15014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H505" t="n">
         <v>18000</v>
@@ -15130,7 +15130,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>2.8654317855835</v>
+        <v>2.86543202400208</v>
       </c>
       <c r="H509" t="n">
         <v>14000</v>
@@ -15159,7 +15159,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>2.8654317855835</v>
+        <v>2.86543202400208</v>
       </c>
       <c r="H510" t="n">
         <v>9500</v>
@@ -15304,7 +15304,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G515" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H515" t="n">
         <v>32500</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H516" t="n">
         <v>7500</v>
@@ -15362,7 +15362,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H517" t="n">
         <v>39500</v>
@@ -15478,7 +15478,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H521" t="n">
         <v>26500</v>
@@ -15507,7 +15507,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H522" t="n">
         <v>99000</v>
@@ -15536,7 +15536,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H523" t="n">
         <v>47500</v>
@@ -15652,7 +15652,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G527" t="n">
-        <v>2.97435164451599</v>
+        <v>2.97435188293457</v>
       </c>
       <c r="H527" t="n">
         <v>28000</v>
@@ -15681,7 +15681,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H528" t="n">
         <v>18500</v>
@@ -15710,7 +15710,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G529" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H529" t="n">
         <v>28000</v>
@@ -15768,7 +15768,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H531" t="n">
         <v>58000</v>
@@ -15826,7 +15826,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.95759463310242</v>
+        <v>2.957594871521</v>
       </c>
       <c r="H533" t="n">
         <v>500</v>
@@ -15855,7 +15855,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H534" t="n">
         <v>10000</v>
@@ -15884,7 +15884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H535" t="n">
         <v>24500</v>
@@ -15913,7 +15913,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H536" t="n">
         <v>1500</v>
@@ -15942,7 +15942,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H537" t="n">
         <v>21500</v>
@@ -16087,7 +16087,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H542" t="n">
         <v>8000</v>
@@ -16116,7 +16116,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H543" t="n">
         <v>7500</v>
@@ -16232,7 +16232,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H547" t="n">
         <v>5000</v>
@@ -16464,7 +16464,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H555" t="n">
         <v>15500</v>
@@ -16493,7 +16493,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H556" t="n">
         <v>500</v>
@@ -16522,7 +16522,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H557" t="n">
         <v>12500</v>
@@ -16638,7 +16638,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.8654317855835</v>
+        <v>2.86543202400208</v>
       </c>
       <c r="H561" t="n">
         <v>1500</v>
@@ -16783,7 +16783,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H566" t="n">
         <v>7500</v>
@@ -16841,7 +16841,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.89894580841064</v>
+        <v>2.89894556999207</v>
       </c>
       <c r="H568" t="n">
         <v>1500</v>
@@ -16899,7 +16899,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H570" t="n">
         <v>15500</v>
@@ -16928,7 +16928,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408084869385</v>
+        <v>2.92408108711243</v>
       </c>
       <c r="H572" t="n">
         <v>11500</v>
@@ -17044,7 +17044,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.97435164451599</v>
+        <v>2.97435188293457</v>
       </c>
       <c r="H575" t="n">
         <v>158500</v>
@@ -17102,7 +17102,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.94083762168884</v>
+        <v>2.94083786010742</v>
       </c>
       <c r="H577" t="n">
         <v>25000</v>
@@ -17131,7 +17131,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.97435164451599</v>
+        <v>2.97435188293457</v>
       </c>
       <c r="H578" t="n">
         <v>23000</v>
@@ -17160,7 +17160,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.9659731388092</v>
+        <v>2.96597337722778</v>
       </c>
       <c r="H579" t="n">
         <v>18000</v>
@@ -17218,7 +17218,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.04137945175171</v>
+        <v>3.04137921333313</v>
       </c>
       <c r="H581" t="n">
         <v>7000</v>
@@ -17247,7 +17247,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840678215027</v>
       </c>
       <c r="H582" t="n">
         <v>42500</v>
@@ -17276,7 +17276,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G583" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H583" t="n">
         <v>7500</v>
@@ -17363,7 +17363,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>3.10840725898743</v>
+        <v>3.10840678215027</v>
       </c>
       <c r="H586" t="n">
         <v>9000</v>
@@ -17392,7 +17392,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G587" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H587" t="n">
         <v>13500</v>
@@ -17450,7 +17450,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H589" t="n">
         <v>20000</v>
@@ -17508,7 +17508,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>3.13354253768921</v>
+        <v>3.13354229927063</v>
       </c>
       <c r="H591" t="n">
         <v>7000</v>
@@ -17566,7 +17566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.16705632209778</v>
+        <v>3.1670560836792</v>
       </c>
       <c r="H593" t="n">
         <v>20500</v>
@@ -17653,7 +17653,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G596" t="n">
-        <v>3.2592191696167</v>
+        <v>3.25921940803528</v>
       </c>
       <c r="H596" t="n">
         <v>13000</v>
@@ -17740,7 +17740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30948996543884</v>
+        <v>3.30949020385742</v>
       </c>
       <c r="H599" t="n">
         <v>10000</v>
@@ -17769,7 +17769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H600" t="n">
         <v>29000</v>
@@ -17798,7 +17798,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H601" t="n">
         <v>13000</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786823272705</v>
+        <v>3.31786847114563</v>
       </c>
       <c r="H602" t="n">
         <v>20500</v>
@@ -17856,7 +17856,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>3.32624697685242</v>
+        <v>3.32624673843384</v>
       </c>
       <c r="H603" t="n">
         <v>21500</v>
@@ -18001,7 +18001,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705888748169</v>
+        <v>3.47705912590027</v>
       </c>
       <c r="H608" t="n">
         <v>67000</v>
@@ -36132,6 +36132,35 @@
         <v>10500</v>
       </c>
       <c r="I1233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1234" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>7.65999984741211</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>7.57999992370605</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>7.6399998664856</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>4250</v>
+      </c>
+      <c r="I1234" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/D.MI.xlsx
+++ b/data/D.MI.xlsx
@@ -514,7 +514,7 @@
         <v>5.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>4.20805168151855</v>
+        <v>4.20805215835571</v>
       </c>
       <c r="H5" t="n">
         <v>1121500</v>
@@ -572,7 +572,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45906925201416</v>
+        <v>4.45906972885132</v>
       </c>
       <c r="H7" t="n">
         <v>476500</v>
@@ -601,7 +601,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G8" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H8" t="n">
         <v>594000</v>
@@ -630,7 +630,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G9" t="n">
-        <v>3.90558409690857</v>
+        <v>3.90558362007141</v>
       </c>
       <c r="H9" t="n">
         <v>388500</v>
@@ -688,7 +688,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H11" t="n">
         <v>83500</v>
@@ -746,7 +746,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>3.76136541366577</v>
+        <v>3.76136565208435</v>
       </c>
       <c r="H13" t="n">
         <v>173000</v>
@@ -775,7 +775,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.97574329376221</v>
+        <v>3.97574400901794</v>
       </c>
       <c r="H14" t="n">
         <v>84000</v>
@@ -804,7 +804,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G15" t="n">
-        <v>4.35772752761841</v>
+        <v>4.35772705078125</v>
       </c>
       <c r="H15" t="n">
         <v>539000</v>
@@ -862,7 +862,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H17" t="n">
         <v>60000</v>
@@ -920,7 +920,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H19" t="n">
         <v>93500</v>
@@ -978,7 +978,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>4.26418018341064</v>
+        <v>4.26417970657349</v>
       </c>
       <c r="H21" t="n">
         <v>24000</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="G24" t="n">
-        <v>4.28756666183472</v>
+        <v>4.28756713867188</v>
       </c>
       <c r="H24" t="n">
         <v>55000</v>
@@ -1181,7 +1181,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>4.20961093902588</v>
+        <v>4.20961141586304</v>
       </c>
       <c r="H28" t="n">
         <v>43500</v>
@@ -1210,7 +1210,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G29" t="n">
-        <v>4.16283798217773</v>
+        <v>4.16283750534058</v>
       </c>
       <c r="H29" t="n">
         <v>15500</v>
@@ -1239,7 +1239,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G30" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H30" t="n">
         <v>54500</v>
@@ -1297,7 +1297,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06929111480713</v>
+        <v>4.06929063796997</v>
       </c>
       <c r="H32" t="n">
         <v>11500</v>
@@ -1326,7 +1326,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G33" t="n">
-        <v>4.00692558288574</v>
+        <v>4.00692653656006</v>
       </c>
       <c r="H33" t="n">
         <v>16000</v>
@@ -1413,7 +1413,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G36" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1442,7 +1442,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G37" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H37" t="n">
         <v>39500</v>
@@ -1500,7 +1500,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G39" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676567077637</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676567077637</v>
       </c>
       <c r="H40" t="n">
         <v>21500</v>
@@ -1558,7 +1558,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G41" t="n">
-        <v>3.88219666481018</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H41" t="n">
         <v>10500</v>
@@ -1587,7 +1587,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G42" t="n">
-        <v>3.87050342559814</v>
+        <v>3.87050366401672</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H43" t="n">
         <v>25500</v>
@@ -1645,7 +1645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>3.85101461410522</v>
+        <v>3.85101532936096</v>
       </c>
       <c r="H44" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>4.875</v>
       </c>
       <c r="G46" t="n">
-        <v>3.80034375190735</v>
+        <v>3.80034327507019</v>
       </c>
       <c r="H46" t="n">
         <v>82500</v>
@@ -1761,7 +1761,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G48" t="n">
-        <v>3.87050342559814</v>
+        <v>3.87050366401672</v>
       </c>
       <c r="H48" t="n">
         <v>17000</v>
@@ -1790,7 +1790,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.72628617286682</v>
+        <v>3.72628545761108</v>
       </c>
       <c r="H49" t="n">
         <v>9000</v>
@@ -1819,7 +1819,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G50" t="n">
-        <v>3.74187707901001</v>
+        <v>3.74187684059143</v>
       </c>
       <c r="H50" t="n">
         <v>2500</v>
@@ -1848,7 +1848,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G51" t="n">
-        <v>3.55088520050049</v>
+        <v>3.55088472366333</v>
       </c>
       <c r="H51" t="n">
         <v>20000</v>
@@ -1906,7 +1906,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G53" t="n">
-        <v>3.08704829216003</v>
+        <v>3.08704781532288</v>
       </c>
       <c r="H53" t="n">
         <v>44000</v>
@@ -1935,7 +1935,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>3.23516440391541</v>
+        <v>3.23516416549683</v>
       </c>
       <c r="H54" t="n">
         <v>7500</v>
@@ -1993,7 +1993,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>3.24685764312744</v>
+        <v>3.24685740470886</v>
       </c>
       <c r="H56" t="n">
         <v>8000</v>
@@ -2022,7 +2022,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G57" t="n">
-        <v>3.45733785629272</v>
+        <v>3.45733833312988</v>
       </c>
       <c r="H57" t="n">
         <v>13000</v>
@@ -2051,7 +2051,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.50021362304688</v>
+        <v>3.5002133846283</v>
       </c>
       <c r="H58" t="n">
         <v>8000</v>
@@ -2167,7 +2167,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G62" t="n">
-        <v>3.3832802772522</v>
+        <v>3.38328003883362</v>
       </c>
       <c r="H62" t="n">
         <v>10000</v>
@@ -2225,7 +2225,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>3.53529357910156</v>
+        <v>3.53529381752014</v>
       </c>
       <c r="H64" t="n">
         <v>3500</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.54698729515076</v>
+        <v>3.54698753356934</v>
       </c>
       <c r="H65" t="n">
         <v>3500</v>
@@ -2283,7 +2283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.83542370796204</v>
+        <v>3.8354229927063</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2341,7 +2341,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G68" t="n">
-        <v>3.99133467674255</v>
+        <v>3.99133443832397</v>
       </c>
       <c r="H68" t="n">
         <v>49500</v>
@@ -2370,7 +2370,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>3.99913048744202</v>
+        <v>3.99913024902344</v>
       </c>
       <c r="H69" t="n">
         <v>13000</v>
@@ -2399,7 +2399,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G70" t="n">
-        <v>4.03810834884644</v>
+        <v>4.03810787200928</v>
       </c>
       <c r="H70" t="n">
         <v>3000</v>
@@ -2428,7 +2428,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.94456171989441</v>
+        <v>3.94456195831299</v>
       </c>
       <c r="H71" t="n">
         <v>13500</v>
@@ -2457,7 +2457,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>3.93676614761353</v>
+        <v>3.93676567077637</v>
       </c>
       <c r="H72" t="n">
         <v>1500</v>
@@ -2486,7 +2486,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G73" t="n">
-        <v>3.91337943077087</v>
+        <v>3.91337966918945</v>
       </c>
       <c r="H73" t="n">
         <v>6500</v>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H74" t="n">
         <v>3500</v>
@@ -2602,7 +2602,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.88219666481018</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H77" t="n">
         <v>2000</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>3.83542370796204</v>
+        <v>3.8354229927063</v>
       </c>
       <c r="H78" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H79" t="n">
         <v>2500</v>
@@ -2689,7 +2689,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H80" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>3.88219666481018</v>
+        <v>3.88219714164734</v>
       </c>
       <c r="H81" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>3.89778804779053</v>
+        <v>3.89778828620911</v>
       </c>
       <c r="H84" t="n">
         <v>9500</v>
@@ -2892,7 +2892,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G87" t="n">
-        <v>3.84321880340576</v>
+        <v>3.84321928024292</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>3.73797869682312</v>
+        <v>3.7379789352417</v>
       </c>
       <c r="H88" t="n">
         <v>36500</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>3.83542370796204</v>
+        <v>3.8354229927063</v>
       </c>
       <c r="H91" t="n">
         <v>10000</v>
@@ -3066,7 +3066,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H93" t="n">
         <v>11500</v>
@@ -3095,7 +3095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>3.81983256340027</v>
+        <v>3.81983232498169</v>
       </c>
       <c r="H94" t="n">
         <v>6500</v>
@@ -3124,7 +3124,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>3.7964460849762</v>
+        <v>3.79644536972046</v>
       </c>
       <c r="H95" t="n">
         <v>7500</v>
@@ -3153,7 +3153,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G97" t="n">
-        <v>3.82459735870361</v>
+        <v>3.82459712028503</v>
       </c>
       <c r="H97" t="n">
         <v>2000</v>
@@ -3211,7 +3211,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G98" t="n">
-        <v>3.88894391059875</v>
+        <v>3.88894414901733</v>
       </c>
       <c r="H98" t="n">
         <v>5000</v>
@@ -3240,7 +3240,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>3.80448913574219</v>
+        <v>3.80448889732361</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>4.875</v>
       </c>
       <c r="G100" t="n">
-        <v>3.92111754417419</v>
+        <v>3.92111682891846</v>
       </c>
       <c r="H100" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>3.93720364570618</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H101" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>3.93720364570618</v>
+        <v>3.93720388412476</v>
       </c>
       <c r="H102" t="n">
         <v>6500</v>
@@ -3356,7 +3356,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G103" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G104" t="n">
-        <v>3.90503072738647</v>
+        <v>3.90503025054932</v>
       </c>
       <c r="H104" t="n">
         <v>17500</v>
@@ -3414,7 +3414,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666181564331</v>
       </c>
       <c r="H105" t="n">
         <v>10000</v>
@@ -3443,7 +3443,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G106" t="n">
-        <v>3.83666229248047</v>
+        <v>3.83666181564331</v>
       </c>
       <c r="H106" t="n">
         <v>3500</v>
@@ -3472,7 +3472,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G107" t="n">
-        <v>3.91709566116333</v>
+        <v>3.91709518432617</v>
       </c>
       <c r="H107" t="n">
         <v>21000</v>
@@ -3530,7 +3530,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>4.08600473403931</v>
+        <v>4.08600521087646</v>
       </c>
       <c r="H109" t="n">
         <v>17000</v>
@@ -3762,7 +3762,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>4.10209131240845</v>
+        <v>4.10209178924561</v>
       </c>
       <c r="H117" t="n">
         <v>11000</v>
@@ -3820,7 +3820,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>4.05383205413818</v>
+        <v>4.05383157730103</v>
       </c>
       <c r="H119" t="n">
         <v>3500</v>
@@ -3849,7 +3849,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96133327484131</v>
+        <v>3.96133399009705</v>
       </c>
       <c r="H120" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G123" t="n">
-        <v>3.87687873840332</v>
+        <v>3.8768789768219</v>
       </c>
       <c r="H123" t="n">
         <v>5000</v>
@@ -3965,7 +3965,7 @@
         <v>4.75</v>
       </c>
       <c r="G124" t="n">
-        <v>3.82057571411133</v>
+        <v>3.82057523727417</v>
       </c>
       <c r="H124" t="n">
         <v>4500</v>
@@ -3994,7 +3994,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G125" t="n">
-        <v>3.8004674911499</v>
+        <v>3.80046725273132</v>
       </c>
       <c r="H125" t="n">
         <v>1500</v>
@@ -4052,7 +4052,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>3.63960099220276</v>
+        <v>3.63960123062134</v>
       </c>
       <c r="H127" t="n">
         <v>9000</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>3.61949253082275</v>
+        <v>3.61949276924133</v>
       </c>
       <c r="H128" t="n">
         <v>1500</v>
@@ -4139,7 +4139,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>3.60340619087219</v>
+        <v>3.60340595245361</v>
       </c>
       <c r="H130" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>3.69992589950562</v>
+        <v>3.69992566108704</v>
       </c>
       <c r="H133" t="n">
         <v>5000</v>
@@ -4255,7 +4255,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G134" t="n">
-        <v>3.65970921516418</v>
+        <v>3.65970945358276</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G135" t="n">
-        <v>3.66775226593018</v>
+        <v>3.66775250434875</v>
       </c>
       <c r="H135" t="n">
         <v>3000</v>
@@ -4371,7 +4371,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G138" t="n">
-        <v>3.49482083320618</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H138" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H141" t="n">
         <v>5500</v>
@@ -4487,7 +4487,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G142" t="n">
-        <v>3.58731937408447</v>
+        <v>3.58731961250305</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4545,7 +4545,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G144" t="n">
-        <v>3.39025807380676</v>
+        <v>3.39025831222534</v>
       </c>
       <c r="H144" t="n">
         <v>4500</v>
@@ -4632,7 +4632,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G147" t="n">
-        <v>3.49482083320618</v>
+        <v>3.49482107162476</v>
       </c>
       <c r="H147" t="n">
         <v>16500</v>
@@ -4719,7 +4719,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G150" t="n">
-        <v>3.5752546787262</v>
+        <v>3.57525444030762</v>
       </c>
       <c r="H150" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G151" t="n">
-        <v>3.5752546787262</v>
+        <v>3.57525444030762</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G152" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H152" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G153" t="n">
-        <v>3.53905963897705</v>
+        <v>3.53905940055847</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.5269947052002</v>
+        <v>3.52699446678162</v>
       </c>
       <c r="H154" t="n">
         <v>4000</v>
@@ -4922,7 +4922,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G157" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112409591675</v>
       </c>
       <c r="H157" t="n">
         <v>500</v>
@@ -4951,7 +4951,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G158" t="n">
-        <v>3.55112457275391</v>
+        <v>3.55112409591675</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>3.48677802085876</v>
+        <v>3.48677778244019</v>
       </c>
       <c r="H159" t="n">
         <v>6500</v>
@@ -5038,7 +5038,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G161" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H161" t="n">
         <v>3000</v>
@@ -5183,7 +5183,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G166" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H166" t="n">
         <v>500</v>
@@ -5212,7 +5212,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.4988431930542</v>
+        <v>3.49884295463562</v>
       </c>
       <c r="H167" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G173" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H173" t="n">
         <v>1500</v>
@@ -5415,7 +5415,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G174" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H174" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G175" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.31384634971619</v>
+        <v>3.31384682655334</v>
       </c>
       <c r="H177" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>3.23341345787048</v>
+        <v>3.2334132194519</v>
       </c>
       <c r="H178" t="n">
         <v>2500</v>
@@ -5560,7 +5560,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H179" t="n">
         <v>3500</v>
@@ -5589,7 +5589,7 @@
         <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3.21732664108276</v>
+        <v>3.21732687950134</v>
       </c>
       <c r="H180" t="n">
         <v>2000</v>
@@ -5618,7 +5618,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G181" t="n">
-        <v>3.17711043357849</v>
+        <v>3.17711019515991</v>
       </c>
       <c r="H181" t="n">
         <v>2500</v>
@@ -5647,7 +5647,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>3.17711043357849</v>
+        <v>3.17711019515991</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G183" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H183" t="n">
         <v>21500</v>
@@ -5734,7 +5734,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08863353729248</v>
+        <v>3.08863377571106</v>
       </c>
       <c r="H185" t="n">
         <v>1000</v>
@@ -5821,7 +5821,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>3.12080717086792</v>
+        <v>3.12080693244934</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>3.05646061897278</v>
+        <v>3.0564603805542</v>
       </c>
       <c r="H189" t="n">
         <v>4000</v>
@@ -5879,7 +5879,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>3.01222229003906</v>
+        <v>3.01222205162048</v>
       </c>
       <c r="H190" t="n">
         <v>2500</v>
@@ -5937,7 +5937,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>3.03635215759277</v>
+        <v>3.03635239601135</v>
       </c>
       <c r="H192" t="n">
         <v>49500</v>
@@ -5966,7 +5966,7 @@
         <v>3.75</v>
       </c>
       <c r="G193" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H193" t="n">
         <v>92500</v>
@@ -6024,7 +6024,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G195" t="n">
-        <v>2.99211382865906</v>
+        <v>2.99211406707764</v>
       </c>
       <c r="H195" t="n">
         <v>8500</v>
@@ -6111,7 +6111,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6256,7 +6256,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G203" t="n">
-        <v>2.97200560569763</v>
+        <v>2.97200584411621</v>
       </c>
       <c r="H203" t="n">
         <v>500</v>
@@ -6314,7 +6314,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97200560569763</v>
+        <v>2.97200584411621</v>
       </c>
       <c r="H205" t="n">
         <v>1000</v>
@@ -6343,7 +6343,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>2.87146425247192</v>
+        <v>2.87146401405334</v>
       </c>
       <c r="H206" t="n">
         <v>5500</v>
@@ -6401,7 +6401,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G208" t="n">
-        <v>2.7266845703125</v>
+        <v>2.72668480873108</v>
       </c>
       <c r="H208" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G209" t="n">
-        <v>2.7266845703125</v>
+        <v>2.72668480873108</v>
       </c>
       <c r="H209" t="n">
         <v>2000</v>
@@ -6459,7 +6459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.7105975151062</v>
+        <v>2.71059799194336</v>
       </c>
       <c r="H210" t="n">
         <v>2000</v>
@@ -6488,7 +6488,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G211" t="n">
-        <v>2.7266845703125</v>
+        <v>2.72668480873108</v>
       </c>
       <c r="H211" t="n">
         <v>5500</v>
@@ -6604,7 +6604,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G215" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H215" t="n">
         <v>5500</v>
@@ -6633,7 +6633,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G216" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H216" t="n">
         <v>7500</v>
@@ -6662,7 +6662,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H217" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H220" t="n">
         <v>1500</v>
@@ -6778,7 +6778,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>2.84733438491821</v>
+        <v>2.84733414649963</v>
       </c>
       <c r="H221" t="n">
         <v>41000</v>
@@ -6807,7 +6807,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G222" t="n">
-        <v>2.83929109573364</v>
+        <v>2.83929085731506</v>
       </c>
       <c r="H222" t="n">
         <v>8000</v>
@@ -6836,7 +6836,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.84331274032593</v>
+        <v>2.84331250190735</v>
       </c>
       <c r="H223" t="n">
         <v>1000</v>
@@ -6865,7 +6865,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.84733438491821</v>
+        <v>2.84733414649963</v>
       </c>
       <c r="H224" t="n">
         <v>7500</v>
@@ -6894,7 +6894,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H225" t="n">
         <v>4500</v>
@@ -6923,7 +6923,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G226" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H226" t="n">
         <v>2500</v>
@@ -6952,7 +6952,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G227" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H227" t="n">
         <v>3000</v>
@@ -6981,7 +6981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>2.95994091033936</v>
+        <v>2.95994067192078</v>
       </c>
       <c r="H228" t="n">
         <v>5000</v>
@@ -7010,7 +7010,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H229" t="n">
         <v>1500</v>
@@ -7532,7 +7532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>2.87950730323792</v>
+        <v>2.87950754165649</v>
       </c>
       <c r="H247" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G251" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -7677,7 +7677,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G252" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7735,7 +7735,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.94787549972534</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H254" t="n">
         <v>3000</v>
@@ -7764,7 +7764,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G255" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H255" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G256" t="n">
-        <v>2.92374563217163</v>
+        <v>2.92374587059021</v>
       </c>
       <c r="H256" t="n">
         <v>4000</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>2.89559412002563</v>
+        <v>2.89559388160706</v>
       </c>
       <c r="H257" t="n">
         <v>5000</v>
@@ -7880,7 +7880,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G259" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H259" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G265" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H265" t="n">
         <v>500</v>
@@ -8083,7 +8083,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8112,7 +8112,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G267" t="n">
-        <v>3.00417876243591</v>
+        <v>3.00417900085449</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8170,7 +8170,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G269" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H269" t="n">
         <v>11500</v>
@@ -8199,7 +8199,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>2.94787549972534</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H270" t="n">
         <v>15000</v>
@@ -8228,7 +8228,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G271" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H271" t="n">
         <v>21000</v>
@@ -8257,7 +8257,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>2.93983221054077</v>
+        <v>2.93983244895935</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>2.94787549972534</v>
+        <v>2.94787573814392</v>
       </c>
       <c r="H273" t="n">
         <v>7000</v>
@@ -8373,7 +8373,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G276" t="n">
-        <v>2.93581080436707</v>
+        <v>2.93581104278564</v>
       </c>
       <c r="H276" t="n">
         <v>7000</v>
@@ -8402,7 +8402,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>2.91972398757935</v>
+        <v>2.91972422599792</v>
       </c>
       <c r="H277" t="n">
         <v>4000</v>
@@ -8518,7 +8518,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G281" t="n">
-        <v>2.98407053947449</v>
+        <v>2.98407077789307</v>
       </c>
       <c r="H281" t="n">
         <v>13500</v>
@@ -8576,7 +8576,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G283" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H283" t="n">
         <v>17500</v>
@@ -8605,7 +8605,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G284" t="n">
-        <v>2.95591878890991</v>
+        <v>2.95591902732849</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8750,7 +8750,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G289" t="n">
-        <v>3.18917536735535</v>
+        <v>3.18917512893677</v>
       </c>
       <c r="H289" t="n">
         <v>22000</v>
@@ -8808,7 +8808,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G291" t="n">
-        <v>3.43047475814819</v>
+        <v>3.43047451972961</v>
       </c>
       <c r="H291" t="n">
         <v>70000</v>
@@ -8837,7 +8837,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G292" t="n">
-        <v>3.5269947052002</v>
+        <v>3.52699446678162</v>
       </c>
       <c r="H292" t="n">
         <v>17000</v>
@@ -8866,7 +8866,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G293" t="n">
-        <v>3.44656133651733</v>
+        <v>3.44656109809875</v>
       </c>
       <c r="H293" t="n">
         <v>26000</v>
@@ -8982,7 +8982,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G297" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H297" t="n">
         <v>6000</v>
@@ -9011,7 +9011,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H298" t="n">
         <v>4500</v>
@@ -9040,7 +9040,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G299" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H299" t="n">
         <v>1000</v>
@@ -9069,7 +9069,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G300" t="n">
-        <v>3.37014985084534</v>
+        <v>3.37015008926392</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G301" t="n">
-        <v>3.3259117603302</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H301" t="n">
         <v>3500</v>
@@ -9127,7 +9127,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G302" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H302" t="n">
         <v>7000</v>
@@ -9185,7 +9185,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G304" t="n">
-        <v>3.3259117603302</v>
+        <v>3.32591152191162</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9214,7 +9214,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G305" t="n">
-        <v>3.3741717338562</v>
+        <v>3.37417149543762</v>
       </c>
       <c r="H305" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G307" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H307" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H310" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G311" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>3.44253969192505</v>
+        <v>3.44253993034363</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G313" t="n">
-        <v>3.61547064781189</v>
+        <v>3.61547088623047</v>
       </c>
       <c r="H313" t="n">
         <v>9000</v>
@@ -9533,7 +9533,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G316" t="n">
-        <v>3.20526194572449</v>
+        <v>3.20526170730591</v>
       </c>
       <c r="H316" t="n">
         <v>18000</v>
@@ -9591,7 +9591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>3.37819314002991</v>
+        <v>3.37819290161133</v>
       </c>
       <c r="H321" t="n">
         <v>8000</v>
@@ -9736,7 +9736,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H323" t="n">
         <v>7500</v>
@@ -9765,7 +9765,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H324" t="n">
         <v>6500</v>
@@ -9794,7 +9794,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>3.25754356384277</v>
+        <v>3.25754332542419</v>
       </c>
       <c r="H327" t="n">
         <v>2500</v>
@@ -9881,7 +9881,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G328" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H328" t="n">
         <v>4000</v>
@@ -9910,7 +9910,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G329" t="n">
-        <v>3.29373812675476</v>
+        <v>3.29373788833618</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G333" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H333" t="n">
         <v>4500</v>
@@ -10055,7 +10055,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G334" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H334" t="n">
         <v>4500</v>
@@ -10084,7 +10084,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G335" t="n">
-        <v>3.32188987731934</v>
+        <v>3.32189011573792</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10113,7 +10113,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G336" t="n">
-        <v>3.32993316650391</v>
+        <v>3.32993340492249</v>
       </c>
       <c r="H336" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G337" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H337" t="n">
         <v>8000</v>
@@ -10171,7 +10171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.29775977134705</v>
+        <v>3.29776000976562</v>
       </c>
       <c r="H338" t="n">
         <v>11000</v>
@@ -10200,7 +10200,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G339" t="n">
-        <v>3.31384634971619</v>
+        <v>3.31384682655334</v>
       </c>
       <c r="H339" t="n">
         <v>8000</v>
@@ -10229,7 +10229,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.3058032989502</v>
+        <v>3.30580353736877</v>
       </c>
       <c r="H340" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H342" t="n">
         <v>8000</v>
@@ -10316,7 +10316,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G343" t="n">
-        <v>3.28971695899963</v>
+        <v>3.28971672058105</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G344" t="n">
-        <v>3.24145698547363</v>
+        <v>3.24145674705505</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>3.24949979782104</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H346" t="n">
         <v>67500</v>
@@ -10432,7 +10432,7 @@
         <v>4</v>
       </c>
       <c r="G347" t="n">
-        <v>3.21732664108276</v>
+        <v>3.21732687950134</v>
       </c>
       <c r="H347" t="n">
         <v>500</v>
@@ -10461,7 +10461,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.24949979782104</v>
+        <v>3.24950003623962</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -10519,7 +10519,7 @@
         <v>4</v>
       </c>
       <c r="G350" t="n">
-        <v>3.21732664108276</v>
+        <v>3.21732687950134</v>
       </c>
       <c r="H350" t="n">
         <v>3500</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H351" t="n">
         <v>4500</v>
@@ -10577,7 +10577,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G352" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H352" t="n">
         <v>500</v>
@@ -10722,7 +10722,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G357" t="n">
-        <v>3.25084090232849</v>
+        <v>3.25084066390991</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.35138201713562</v>
+        <v>3.3513822555542</v>
       </c>
       <c r="H359" t="n">
         <v>34500</v>
@@ -10809,7 +10809,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>3.34300351142883</v>
+        <v>3.34300374984741</v>
       </c>
       <c r="H360" t="n">
         <v>4000</v>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
       <c r="G361" t="n">
-        <v>3.35138201713562</v>
+        <v>3.3513822555542</v>
       </c>
       <c r="H361" t="n">
         <v>3500</v>
@@ -10867,7 +10867,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H362" t="n">
         <v>16500</v>
@@ -10896,7 +10896,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>3.38489580154419</v>
+        <v>3.38489603996277</v>
       </c>
       <c r="H367" t="n">
         <v>25000</v>
@@ -11070,7 +11070,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G369" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H369" t="n">
         <v>9000</v>
@@ -11099,7 +11099,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.45192337036133</v>
+        <v>3.45192384719849</v>
       </c>
       <c r="H370" t="n">
         <v>10500</v>
@@ -11128,7 +11128,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G371" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H371" t="n">
         <v>11000</v>
@@ -11157,7 +11157,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G372" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H372" t="n">
         <v>13500</v>
@@ -11186,7 +11186,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G373" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H373" t="n">
         <v>10500</v>
@@ -11215,7 +11215,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>3.48543739318848</v>
+        <v>3.4854371547699</v>
       </c>
       <c r="H374" t="n">
         <v>6000</v>
@@ -11244,7 +11244,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G375" t="n">
-        <v>3.53570818901062</v>
+        <v>3.53570795059204</v>
       </c>
       <c r="H375" t="n">
         <v>28000</v>
@@ -11273,7 +11273,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.52732992172241</v>
+        <v>3.52732968330383</v>
       </c>
       <c r="H376" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G377" t="n">
-        <v>3.51895117759705</v>
+        <v>3.51895093917847</v>
       </c>
       <c r="H377" t="n">
         <v>4000</v>
@@ -11331,7 +11331,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G378" t="n">
-        <v>3.55246496200562</v>
+        <v>3.55246472358704</v>
       </c>
       <c r="H378" t="n">
         <v>27000</v>
@@ -11360,7 +11360,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H379" t="n">
         <v>11500</v>
@@ -11476,7 +11476,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G383" t="n">
-        <v>3.72003412246704</v>
+        <v>3.72003436088562</v>
       </c>
       <c r="H383" t="n">
         <v>33500</v>
@@ -11505,7 +11505,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>3.72003412246704</v>
+        <v>3.72003436088562</v>
       </c>
       <c r="H384" t="n">
         <v>14000</v>
@@ -11534,7 +11534,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>3.73679113388062</v>
+        <v>3.73679137229919</v>
       </c>
       <c r="H385" t="n">
         <v>34000</v>
@@ -11621,7 +11621,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G388" t="n">
-        <v>3.64462828636169</v>
+        <v>3.64462804794312</v>
       </c>
       <c r="H388" t="n">
         <v>35500</v>
@@ -11737,7 +11737,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G392" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H392" t="n">
         <v>15500</v>
@@ -11766,7 +11766,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G393" t="n">
-        <v>3.46030211448669</v>
+        <v>3.46030235290527</v>
       </c>
       <c r="H393" t="n">
         <v>7000</v>
@@ -11795,7 +11795,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H394" t="n">
         <v>16500</v>
@@ -11824,7 +11824,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>3.52732992172241</v>
+        <v>3.52732968330383</v>
       </c>
       <c r="H395" t="n">
         <v>10500</v>
@@ -11882,7 +11882,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G397" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H397" t="n">
         <v>14000</v>
@@ -11911,7 +11911,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H398" t="n">
         <v>15000</v>
@@ -11940,7 +11940,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G399" t="n">
-        <v>3.66138482093811</v>
+        <v>3.66138505935669</v>
       </c>
       <c r="H399" t="n">
         <v>25000</v>
@@ -12143,7 +12143,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>3.57760071754456</v>
+        <v>3.57760047912598</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12172,7 +12172,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>3.48543739318848</v>
+        <v>3.4854371547699</v>
       </c>
       <c r="H407" t="n">
         <v>10000</v>
@@ -12201,7 +12201,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>3.52732992172241</v>
+        <v>3.52732968330383</v>
       </c>
       <c r="H408" t="n">
         <v>5000</v>
@@ -12288,7 +12288,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G411" t="n">
-        <v>3.44354510307312</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H411" t="n">
         <v>14500</v>
@@ -12317,7 +12317,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G412" t="n">
-        <v>3.4686803817749</v>
+        <v>3.46868062019348</v>
       </c>
       <c r="H412" t="n">
         <v>27500</v>
@@ -12346,7 +12346,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G413" t="n">
-        <v>3.44354510307312</v>
+        <v>3.4435453414917</v>
       </c>
       <c r="H413" t="n">
         <v>8500</v>
@@ -12462,7 +12462,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>3.43516659736633</v>
+        <v>3.43516683578491</v>
       </c>
       <c r="H417" t="n">
         <v>10500</v>
@@ -12520,7 +12520,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G419" t="n">
-        <v>3.50219416618347</v>
+        <v>3.50219392776489</v>
       </c>
       <c r="H419" t="n">
         <v>9000</v>
@@ -12578,7 +12578,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>3.28435468673706</v>
+        <v>3.28435444831848</v>
       </c>
       <c r="H421" t="n">
         <v>28500</v>
@@ -12607,7 +12607,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>3.28435468673706</v>
+        <v>3.28435444831848</v>
       </c>
       <c r="H422" t="n">
         <v>11500</v>
@@ -12636,7 +12636,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H423" t="n">
         <v>57000</v>
@@ -12665,7 +12665,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G424" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H424" t="n">
         <v>9500</v>
@@ -12694,7 +12694,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>3.10840678215027</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H425" t="n">
         <v>9000</v>
@@ -12955,7 +12955,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H434" t="n">
         <v>19000</v>
@@ -13042,7 +13042,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G437" t="n">
-        <v>3.10840678215027</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H437" t="n">
         <v>4500</v>
@@ -13129,7 +13129,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G440" t="n">
-        <v>3.10840678215027</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H440" t="n">
         <v>1500</v>
@@ -13245,7 +13245,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>3.04137921333313</v>
+        <v>3.04137945175171</v>
       </c>
       <c r="H444" t="n">
         <v>7500</v>
@@ -13361,7 +13361,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.10840678215027</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H448" t="n">
         <v>43500</v>
@@ -13477,7 +13477,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G452" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H452" t="n">
         <v>55500</v>
@@ -13506,7 +13506,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G453" t="n">
-        <v>3.04137921333313</v>
+        <v>3.04137945175171</v>
       </c>
       <c r="H453" t="n">
         <v>18500</v>
@@ -13535,7 +13535,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G454" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H454" t="n">
         <v>22000</v>
@@ -13564,7 +13564,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G455" t="n">
-        <v>3.0581362247467</v>
+        <v>3.05813646316528</v>
       </c>
       <c r="H455" t="n">
         <v>3500</v>
@@ -13622,7 +13622,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G457" t="n">
-        <v>3.01624393463135</v>
+        <v>3.01624369621277</v>
       </c>
       <c r="H457" t="n">
         <v>1000</v>
@@ -13738,7 +13738,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H461" t="n">
         <v>20500</v>
@@ -13767,7 +13767,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G462" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H462" t="n">
         <v>12000</v>
@@ -13796,7 +13796,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G463" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H463" t="n">
         <v>26000</v>
@@ -14289,7 +14289,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H480" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G481" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H481" t="n">
         <v>1000</v>
@@ -14347,7 +14347,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H486" t="n">
         <v>26000</v>
@@ -14521,7 +14521,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H488" t="n">
         <v>9500</v>
@@ -14579,7 +14579,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G490" t="n">
-        <v>2.81516075134277</v>
+        <v>2.81516098976135</v>
       </c>
       <c r="H490" t="n">
         <v>13500</v>
@@ -14637,7 +14637,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G492" t="n">
-        <v>2.82353925704956</v>
+        <v>2.82353949546814</v>
       </c>
       <c r="H492" t="n">
         <v>13500</v>
@@ -14695,7 +14695,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G494" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H494" t="n">
         <v>5500</v>
@@ -14840,7 +14840,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>2.79002547264099</v>
+        <v>2.79002571105957</v>
       </c>
       <c r="H499" t="n">
         <v>14000</v>
@@ -14869,7 +14869,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G500" t="n">
-        <v>2.81516075134277</v>
+        <v>2.81516098976135</v>
       </c>
       <c r="H500" t="n">
         <v>23500</v>
@@ -14898,7 +14898,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G501" t="n">
-        <v>2.84029650688171</v>
+        <v>2.84029674530029</v>
       </c>
       <c r="H501" t="n">
         <v>21500</v>
@@ -15014,7 +15014,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H505" t="n">
         <v>18000</v>
@@ -15130,7 +15130,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G509" t="n">
-        <v>2.86543202400208</v>
+        <v>2.8654317855835</v>
       </c>
       <c r="H509" t="n">
         <v>14000</v>
@@ -15159,7 +15159,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>2.86543202400208</v>
+        <v>2.8654317855835</v>
       </c>
       <c r="H510" t="n">
         <v>9500</v>
@@ -15304,7 +15304,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G515" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H515" t="n">
         <v>32500</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H516" t="n">
         <v>7500</v>
@@ -15362,7 +15362,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G517" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H517" t="n">
         <v>39500</v>
@@ -15478,7 +15478,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G521" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H521" t="n">
         <v>26500</v>
@@ -15507,7 +15507,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G522" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H522" t="n">
         <v>99000</v>
@@ -15536,7 +15536,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G523" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H523" t="n">
         <v>47500</v>
@@ -15652,7 +15652,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G527" t="n">
-        <v>2.97435188293457</v>
+        <v>2.97435164451599</v>
       </c>
       <c r="H527" t="n">
         <v>28000</v>
@@ -15681,7 +15681,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H528" t="n">
         <v>18500</v>
@@ -15710,7 +15710,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G529" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H529" t="n">
         <v>28000</v>
@@ -15768,7 +15768,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G531" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H531" t="n">
         <v>58000</v>
@@ -15826,7 +15826,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>2.957594871521</v>
+        <v>2.95759463310242</v>
       </c>
       <c r="H533" t="n">
         <v>500</v>
@@ -15855,7 +15855,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H534" t="n">
         <v>10000</v>
@@ -15884,7 +15884,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H535" t="n">
         <v>24500</v>
@@ -15913,7 +15913,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H536" t="n">
         <v>1500</v>
@@ -15942,7 +15942,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G537" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H537" t="n">
         <v>21500</v>
@@ -16087,7 +16087,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G542" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H542" t="n">
         <v>8000</v>
@@ -16116,7 +16116,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G543" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H543" t="n">
         <v>7500</v>
@@ -16232,7 +16232,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G547" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H547" t="n">
         <v>5000</v>
@@ -16464,7 +16464,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H555" t="n">
         <v>15500</v>
@@ -16493,7 +16493,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H556" t="n">
         <v>500</v>
@@ -16522,7 +16522,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H557" t="n">
         <v>12500</v>
@@ -16638,7 +16638,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G561" t="n">
-        <v>2.86543202400208</v>
+        <v>2.8654317855835</v>
       </c>
       <c r="H561" t="n">
         <v>1500</v>
@@ -16783,7 +16783,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G566" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H566" t="n">
         <v>7500</v>
@@ -16841,7 +16841,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.89894556999207</v>
+        <v>2.89894580841064</v>
       </c>
       <c r="H568" t="n">
         <v>1500</v>
@@ -16899,7 +16899,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G570" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H570" t="n">
         <v>15500</v>
@@ -16928,7 +16928,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G571" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>2.92408108711243</v>
+        <v>2.92408084869385</v>
       </c>
       <c r="H572" t="n">
         <v>11500</v>
@@ -17044,7 +17044,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.97435188293457</v>
+        <v>2.97435164451599</v>
       </c>
       <c r="H575" t="n">
         <v>158500</v>
@@ -17102,7 +17102,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.94083786010742</v>
+        <v>2.94083762168884</v>
       </c>
       <c r="H577" t="n">
         <v>25000</v>
@@ -17131,7 +17131,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.97435188293457</v>
+        <v>2.97435164451599</v>
       </c>
       <c r="H578" t="n">
         <v>23000</v>
@@ -17160,7 +17160,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>2.96597337722778</v>
+        <v>2.9659731388092</v>
       </c>
       <c r="H579" t="n">
         <v>18000</v>
@@ -17218,7 +17218,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>3.04137921333313</v>
+        <v>3.04137945175171</v>
       </c>
       <c r="H581" t="n">
         <v>7000</v>
@@ -17247,7 +17247,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>3.10840678215027</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H582" t="n">
         <v>42500</v>
@@ -17276,7 +17276,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G583" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H583" t="n">
         <v>7500</v>
@@ -17363,7 +17363,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>3.10840678215027</v>
+        <v>3.10840725898743</v>
       </c>
       <c r="H586" t="n">
         <v>9000</v>
@@ -17392,7 +17392,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G587" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H587" t="n">
         <v>13500</v>
@@ -17450,7 +17450,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H589" t="n">
         <v>20000</v>
@@ -17508,7 +17508,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G591" t="n">
-        <v>3.13354229927063</v>
+        <v>3.13354253768921</v>
       </c>
       <c r="H591" t="n">
         <v>7000</v>
@@ -17566,7 +17566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>3.1670560836792</v>
+        <v>3.16705632209778</v>
       </c>
       <c r="H593" t="n">
         <v>20500</v>
@@ -17653,7 +17653,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G596" t="n">
-        <v>3.25921940803528</v>
+        <v>3.2592191696167</v>
       </c>
       <c r="H596" t="n">
         <v>13000</v>
@@ -17740,7 +17740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>3.30949020385742</v>
+        <v>3.30948996543884</v>
       </c>
       <c r="H599" t="n">
         <v>10000</v>
@@ -17769,7 +17769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H600" t="n">
         <v>29000</v>
@@ -17798,7 +17798,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H601" t="n">
         <v>13000</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.31786847114563</v>
+        <v>3.31786823272705</v>
       </c>
       <c r="H602" t="n">
         <v>20500</v>
@@ -17856,7 +17856,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>3.32624673843384</v>
+        <v>3.32624697685242</v>
       </c>
       <c r="H603" t="n">
         <v>21500</v>
@@ -18001,7 +18001,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>3.47705912590027</v>
+        <v>3.47705888748169</v>
       </c>
       <c r="H608" t="n">
         <v>67000</v>
@@ -36161,6 +36161,35 @@
         <v>4250</v>
       </c>
       <c r="I1234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1235" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>7.78000020980835</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>7.59999990463257</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>7.76000022888184</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1235" t="s">
         <v>9</v>
       </c>
     </row>
